--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Customer_Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Customer_Trips_Per_Day" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Audit_Log" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trip_Detail" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Trips_Pricing_All" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Unmatched_Log" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Daily_Activity" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Daily_Time_24h_Check" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Plate_DestDay" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Surcharge_50pct_1Trip" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Manual_Extra_Trips" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Manual_Return_Trips" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="NoWork_Outbound_50pct" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Phantom_Trip_Candidates" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Hints_DoubleOrigin" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer_Trips_Per_Day" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit_Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trip_Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trips_Pricing_All" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Activity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Time_24h_Check" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plate_DestDay" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surcharge_50pct_1Trip" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Extra_Trips" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Return_Trips" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NoWork_Outbound_50pct" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phantom_Trip_Candidates" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hints_DoubleOrigin" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$8</definedName>
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05 20:19</t>
+          <t>2026-05-08 15:11</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-12–2026-04-15=8,000 / ปกติ=7,500</t>
+          <t>2026-05-01–2026-05-31=6,500 @31.00-31.99, step 1.50%/฿ / 2026-04-12–2026-04-15=8,000 @50.00-50.99, step 1.50%/฿, floor 6,500 / 2026-04-01–2026-04-30=7,500 @50.00-50.99, step 1.50%/฿, floor 6,500 / ปกติ=7,500 @50.00-50.99, step 1.50%/฿</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>811000</v>
+        <v>808500</v>
       </c>
     </row>
     <row r="14">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="16">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>164500</v>
+        <v>163500</v>
       </c>
     </row>
     <row r="21">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1013000</v>
+        <v>1005750</v>
       </c>
     </row>
   </sheetData>
@@ -2837,10 +2837,10 @@
         <v>3750</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>26250</v>
+        <v>18750</v>
       </c>
     </row>
     <row r="62">
@@ -3323,19 +3323,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="77">
@@ -3356,19 +3356,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
   </sheetData>
@@ -4968,10 +4968,10 @@
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="38">
@@ -5010,10 +5010,10 @@
       </c>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="39">
@@ -5245,7 +5245,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5280,11 +5280,11 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ค่าขนส่งงานขากลับ (manual — ไม่มีใน GPS)</t>
+          <t>ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>811000</v>
+        <v>808500</v>
       </c>
     </row>
     <row r="3">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="5">
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>164500</v>
+        <v>163500</v>
       </c>
     </row>
     <row r="7">
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1013000</v>
+        <v>1005750</v>
       </c>
     </row>
   </sheetData>
@@ -8323,14 +8323,14 @@
         <v>3750</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>26250</v>
+        <v>22500</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ (manual — ไม่มีใน GPS) (+7,500฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,750฿)</t>
         </is>
       </c>
     </row>
@@ -8770,19 +8770,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -8808,19 +8808,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="W16" s="6" t="n">
         <v>4000</v>
@@ -10488,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="W18" s="6" t="n">
         <v>0</v>
@@ -10576,7 +10576,7 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="W19" s="7" t="n">
         <v>4000</v>
@@ -10664,7 +10664,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="W20" s="6" t="n">
         <v>4000</v>
@@ -13132,7 +13132,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="W48" s="6" t="n">
         <v>0</v>
@@ -13312,7 +13312,7 @@
         <v>1</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="W50" s="6" t="n">
         <v>3750</v>
@@ -13488,7 +13488,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="W52" s="6" t="n">
         <v>3750</v>
@@ -16776,7 +16776,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="7" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="90">
@@ -18176,10 +18176,10 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
@@ -18264,10 +18264,10 @@
         <v>1</v>
       </c>
       <c r="V106" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W106" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X106" s="6" t="n">
         <v>0</v>
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>4000</v>
@@ -18750,7 +18750,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>0</v>
@@ -18775,7 +18775,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>4000</v>
@@ -18800,7 +18800,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>4000</v>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>0</v>
@@ -19550,7 +19550,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>3750</v>
@@ -19600,7 +19600,7 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="D52" s="6" t="n">
         <v>3750</v>
@@ -20537,7 +20537,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="90">
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
@@ -20950,10 +20950,10 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E106" s="6" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 15:11</t>
+          <t>2026-05-08 15:54</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>808500</v>
+        <v>733061</v>
       </c>
     </row>
     <row r="14">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="16">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>163500</v>
+        <v>147134</v>
       </c>
     </row>
     <row r="21">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>30000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="22">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1005750</v>
+        <v>909445</v>
       </c>
     </row>
   </sheetData>
@@ -881,10 +881,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
     </row>
     <row r="3">
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
     </row>
     <row r="4">
@@ -947,10 +947,10 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
     </row>
     <row r="5">
@@ -980,10 +980,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
     </row>
     <row r="7">
@@ -1046,19 +1046,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11250</v>
+        <v>10913</v>
       </c>
     </row>
     <row r="8">
@@ -1079,19 +1079,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
     </row>
     <row r="9">
@@ -1112,10 +1112,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="10">
@@ -1145,10 +1145,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="12">
@@ -1211,19 +1211,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
     </row>
     <row r="13">
@@ -1244,19 +1244,19 @@
         <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>20000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="14">
@@ -1277,10 +1277,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="15">
@@ -1310,19 +1310,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="16">
@@ -1343,19 +1343,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="17">
@@ -1376,19 +1376,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="18">
@@ -1409,19 +1409,19 @@
         <v>2</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>20000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="19">
@@ -1442,10 +1442,10 @@
         <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
     </row>
     <row r="20">
@@ -1475,19 +1475,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="21">
@@ -1508,19 +1508,19 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>20000</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="22">
@@ -1541,19 +1541,19 @@
         <v>3</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>28000</v>
+        <v>25480</v>
       </c>
     </row>
     <row r="23">
@@ -1574,10 +1574,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="24">
@@ -1607,19 +1607,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="25">
@@ -1640,10 +1640,10 @@
         <v>3</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
     </row>
     <row r="26">
@@ -1673,10 +1673,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
     </row>
     <row r="27">
@@ -1706,19 +1706,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="28">
@@ -1739,19 +1739,19 @@
         <v>3</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>28000</v>
+        <v>25480</v>
       </c>
     </row>
     <row r="29">
@@ -1772,19 +1772,19 @@
         <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="30">
@@ -1805,10 +1805,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="31">
@@ -1838,10 +1838,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
     </row>
     <row r="32">
@@ -1871,19 +1871,19 @@
         <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
     </row>
     <row r="33">
@@ -1904,10 +1904,10 @@
         <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
     </row>
     <row r="34">
@@ -1937,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
     </row>
     <row r="35">
@@ -1970,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="36">
@@ -2003,19 +2003,19 @@
         <v>3</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>22500</v>
+        <v>20475</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>26250</v>
+        <v>23887</v>
       </c>
     </row>
     <row r="37">
@@ -2036,10 +2036,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
     </row>
     <row r="38">
@@ -2069,10 +2069,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="39">
@@ -2102,19 +2102,19 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="H39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>18750</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="40">
@@ -2135,10 +2135,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="41">
@@ -2168,10 +2168,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="42">
@@ -2201,10 +2201,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="43">
@@ -2234,10 +2234,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="44">
@@ -2267,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="45">
@@ -2300,10 +2300,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="46">
@@ -2333,10 +2333,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="47">
@@ -2366,19 +2366,19 @@
         <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>11250</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="48">
@@ -2399,10 +2399,10 @@
         <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="49">
@@ -2432,10 +2432,10 @@
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="50">
@@ -2465,10 +2465,10 @@
         <v>2</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="51">
@@ -2498,10 +2498,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="52">
@@ -2531,10 +2531,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="53">
@@ -2564,10 +2564,10 @@
         <v>2</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>0</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="54">
@@ -2597,19 +2597,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>15000</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="55">
@@ -2630,19 +2630,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>15000</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="56">
@@ -2663,19 +2663,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>15000</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="57">
@@ -2696,19 +2696,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="58">
@@ -2729,19 +2729,19 @@
         <v>2</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>22500</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="59">
@@ -2762,19 +2762,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="60">
@@ -2795,19 +2795,19 @@
         <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="61">
@@ -2828,19 +2828,19 @@
         <v>2</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>18750</v>
+        <v>17250</v>
       </c>
     </row>
     <row r="62">
@@ -2861,19 +2861,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="63">
@@ -2894,19 +2894,19 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="64">
@@ -2927,19 +2927,19 @@
         <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="65">
@@ -2960,19 +2960,19 @@
         <v>0</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="66">
@@ -2993,19 +2993,19 @@
         <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="67">
@@ -3026,10 +3026,10 @@
         <v>3</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>22500</v>
+        <v>19500</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>22500</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="68">
@@ -3059,10 +3059,10 @@
         <v>2</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>0</v>
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="69">
@@ -3092,19 +3092,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="70">
@@ -3125,19 +3125,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="71">
@@ -3158,19 +3158,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="72">
@@ -3191,19 +3191,19 @@
         <v>0</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="73">
@@ -3224,19 +3224,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="74">
@@ -3257,19 +3257,19 @@
         <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="H74" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="75">
@@ -3290,19 +3290,19 @@
         <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H75" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="76">
@@ -3323,19 +3323,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="H76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>9750</v>
+        <v>11067</v>
       </c>
     </row>
     <row r="77">
@@ -3356,19 +3356,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>9750</v>
+        <v>11067</v>
       </c>
     </row>
   </sheetData>
@@ -3498,10 +3498,10 @@
       </c>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="3">
@@ -3540,10 +3540,10 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="4">
@@ -3582,10 +3582,10 @@
       </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="5">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="6">
@@ -3666,10 +3666,10 @@
       </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="7">
@@ -3708,10 +3708,10 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="8">
@@ -3750,10 +3750,10 @@
       </c>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="9">
@@ -3792,10 +3792,10 @@
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="10">
@@ -3834,10 +3834,10 @@
       </c>
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="11">
@@ -3876,10 +3876,10 @@
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="12">
@@ -3918,10 +3918,10 @@
       </c>
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="13">
@@ -3960,10 +3960,10 @@
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="14">
@@ -4002,10 +4002,10 @@
       </c>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="15">
@@ -4044,10 +4044,10 @@
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="16">
@@ -4086,10 +4086,10 @@
       </c>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="17">
@@ -4128,10 +4128,10 @@
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="18">
@@ -4170,10 +4170,10 @@
       </c>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="19">
@@ -4212,10 +4212,10 @@
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="20">
@@ -4254,10 +4254,10 @@
       </c>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="21">
@@ -4296,10 +4296,10 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="22">
@@ -4338,10 +4338,10 @@
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="23">
@@ -4380,10 +4380,10 @@
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="24">
@@ -4422,10 +4422,10 @@
       </c>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="25">
@@ -4464,10 +4464,10 @@
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="26">
@@ -4506,10 +4506,10 @@
       </c>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="27">
@@ -4548,10 +4548,10 @@
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="28">
@@ -4590,10 +4590,10 @@
       </c>
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="29">
@@ -4632,10 +4632,10 @@
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="30">
@@ -4674,10 +4674,10 @@
       </c>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="31">
@@ -4716,10 +4716,10 @@
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="32">
@@ -4758,10 +4758,10 @@
       </c>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="33">
@@ -4800,10 +4800,10 @@
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="34">
@@ -4842,10 +4842,10 @@
       </c>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="35">
@@ -4884,10 +4884,10 @@
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="36">
@@ -4926,10 +4926,10 @@
       </c>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="37">
@@ -4968,10 +4968,10 @@
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="38">
@@ -5010,10 +5010,10 @@
       </c>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="6" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="39">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="K39" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="40">
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="41">
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
   </sheetData>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
@@ -5400,10 +5400,10 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -5462,10 +5462,10 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>8.6</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>808500</v>
+        <v>733061</v>
       </c>
     </row>
     <row r="3">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="5">
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>163500</v>
+        <v>147134</v>
       </c>
     </row>
     <row r="7">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>30000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="8">
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1005750</v>
+        <v>909445</v>
       </c>
     </row>
   </sheetData>
@@ -6224,10 +6224,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
@@ -6262,10 +6262,10 @@
         <v>2</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -6300,19 +6300,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
@@ -6338,10 +6338,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -6350,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>15000</v>
+        <v>14550</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -6452,19 +6452,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
@@ -6490,19 +6490,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>11250</v>
+        <v>10913</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -6528,19 +6528,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -6604,19 +6604,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
@@ -6642,19 +6642,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
@@ -6718,19 +6718,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -6756,19 +6756,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -6794,19 +6794,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -6832,19 +6832,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -6870,19 +6870,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -6908,10 +6908,10 @@
         <v>3</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
@@ -6946,19 +6946,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -6984,10 +6984,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
@@ -7022,10 +7022,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -7060,19 +7060,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -7098,19 +7098,19 @@
         <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -7136,10 +7136,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -7174,10 +7174,10 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -7212,19 +7212,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         <v>3</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -7262,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>24000</v>
+        <v>21840</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -7288,19 +7288,19 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
@@ -7326,19 +7326,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>11250</v>
+        <v>10237</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -7364,10 +7364,10 @@
         <v>2</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>16000</v>
+        <v>14560</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
@@ -7402,19 +7402,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>12000</v>
+        <v>10920</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
@@ -7478,19 +7478,19 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>11250</v>
+        <v>9900</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -7516,10 +7516,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
@@ -7528,7 +7528,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -7566,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -7592,10 +7592,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>15000</v>
+        <v>13650</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -7630,10 +7630,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -7718,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -7794,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -7820,10 +7820,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -7832,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
@@ -7858,19 +7858,19 @@
         <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>11250</v>
+        <v>9900</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -7896,10 +7896,10 @@
         <v>2</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -7934,10 +7934,10 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -7946,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -7972,19 +7972,19 @@
         <v>2</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>22500</v>
+        <v>19800</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -8010,19 +8010,19 @@
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>22500</v>
+        <v>19800</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -8048,19 +8048,19 @@
         <v>3</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>22500</v>
+        <v>19800</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>30000</v>
+        <v>26400</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -8086,19 +8086,19 @@
         <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -8124,19 +8124,19 @@
         <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
@@ -8162,19 +8162,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -8200,19 +8200,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
@@ -8238,19 +8238,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -8276,19 +8276,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
         <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>22500</v>
+        <v>20500</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,750฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250฿)</t>
         </is>
       </c>
     </row>
@@ -8352,10 +8352,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>0</v>
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
@@ -8390,19 +8390,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -8428,19 +8428,19 @@
         <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
@@ -8466,19 +8466,19 @@
         <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -8504,10 +8504,10 @@
         <v>2</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>0</v>
@@ -8516,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
@@ -8542,10 +8542,10 @@
         <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>0</v>
@@ -8554,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -8580,19 +8580,19 @@
         <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
@@ -8618,19 +8618,19 @@
         <v>1</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -8656,19 +8656,19 @@
         <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
@@ -8694,19 +8694,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -8732,19 +8732,19 @@
         <v>1</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>11250</v>
+        <v>9750</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
@@ -8770,19 +8770,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>9750</v>
+        <v>11067</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -8808,19 +8808,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>9750</v>
+        <v>11067</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W2" s="6" t="n">
         <v>0</v>
@@ -9164,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W3" s="7" t="n">
         <v>0</v>
@@ -9252,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W4" s="6" t="n">
         <v>0</v>
@@ -9340,7 +9340,7 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W5" s="7" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W6" s="6" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W7" s="7" t="n">
         <v>0</v>
@@ -9608,7 +9608,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W8" s="6" t="n">
         <v>0</v>
@@ -9696,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -9784,10 +9784,10 @@
         <v>1</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
       <c r="X10" s="6" t="n">
         <v>0</v>
@@ -9872,10 +9872,10 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
@@ -9960,7 +9960,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W12" s="6" t="n">
         <v>0</v>
@@ -10048,7 +10048,7 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W13" s="7" t="n">
         <v>0</v>
@@ -10136,7 +10136,7 @@
         <v>1</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W14" s="6" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
@@ -10312,10 +10312,10 @@
         <v>1</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X16" s="6" t="n">
         <v>0</v>
@@ -10400,7 +10400,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W17" s="7" t="n">
         <v>0</v>
@@ -10488,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W18" s="6" t="n">
         <v>0</v>
@@ -10576,10 +10576,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -10664,10 +10664,10 @@
         <v>1</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X20" s="6" t="n">
         <v>0</v>
@@ -10752,10 +10752,10 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>0</v>
@@ -10840,10 +10840,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X22" s="6" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W23" s="7" t="n">
         <v>0</v>
@@ -11016,7 +11016,7 @@
         <v>1</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W24" s="6" t="n">
         <v>0</v>
@@ -11104,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W25" s="7" t="n">
         <v>0</v>
@@ -11192,10 +11192,10 @@
         <v>1</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X26" s="6" t="n">
         <v>0</v>
@@ -11280,10 +11280,10 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>0</v>
@@ -11368,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W28" s="6" t="n">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>0</v>
@@ -11544,7 +11544,7 @@
         <v>1</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W30" s="6" t="n">
         <v>0</v>
@@ -11632,7 +11632,7 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W31" s="7" t="n">
         <v>0</v>
@@ -11720,7 +11720,7 @@
         <v>1</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W32" s="6" t="n">
         <v>0</v>
@@ -11812,10 +11812,10 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W33" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>0</v>
@@ -11900,7 +11900,7 @@
         <v>1</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W34" s="6" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -12076,7 +12076,7 @@
         <v>1</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W36" s="6" t="n">
         <v>0</v>
@@ -12164,7 +12164,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W38" s="6" t="n">
         <v>0</v>
@@ -12340,10 +12340,10 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>0</v>
@@ -12428,10 +12428,10 @@
         <v>1</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X40" s="6" t="n">
         <v>0</v>
@@ -12516,7 +12516,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -12604,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W42" s="6" t="n">
         <v>0</v>
@@ -12692,10 +12692,10 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W43" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>0</v>
@@ -12780,7 +12780,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W44" s="6" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W45" s="7" t="n">
         <v>0</v>
@@ -12956,7 +12956,7 @@
         <v>1</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W46" s="6" t="n">
         <v>0</v>
@@ -13044,10 +13044,10 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W47" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W48" s="6" t="n">
         <v>0</v>
@@ -13220,7 +13220,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -13312,10 +13312,10 @@
         <v>1</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W50" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X50" s="6" t="n">
         <v>0</v>
@@ -13400,7 +13400,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W51" s="7" t="n">
         <v>0</v>
@@ -13488,10 +13488,10 @@
         <v>1</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="W52" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="X52" s="6" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W53" s="7" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W54" s="6" t="n">
         <v>0</v>
@@ -13752,7 +13752,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W55" s="7" t="n">
         <v>0</v>
@@ -13840,7 +13840,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W56" s="6" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W57" s="7" t="n">
         <v>0</v>
@@ -14016,7 +14016,7 @@
         <v>1</v>
       </c>
       <c r="V58" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W58" s="6" t="n">
         <v>0</v>
@@ -14104,10 +14104,10 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W59" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>0</v>
@@ -14192,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="V60" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W60" s="6" t="n">
         <v>0</v>
@@ -14284,7 +14284,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>1</v>
       </c>
       <c r="V62" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W62" s="6" t="n">
         <v>0</v>
@@ -14460,7 +14460,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -14548,7 +14548,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W64" s="6" t="n">
         <v>0</v>
@@ -14636,7 +14636,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W66" s="6" t="n">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W67" s="7" t="n">
         <v>0</v>
@@ -14904,7 +14904,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W68" s="6" t="n">
         <v>0</v>
@@ -14992,7 +14992,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -15080,7 +15080,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W70" s="6" t="n">
         <v>0</v>
@@ -15168,10 +15168,10 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W71" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>0</v>
@@ -15256,7 +15256,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W72" s="6" t="n">
         <v>0</v>
@@ -15344,7 +15344,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W73" s="7" t="n">
         <v>0</v>
@@ -15432,7 +15432,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W74" s="6" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W75" s="7" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
         <v>1</v>
       </c>
       <c r="V76" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W76" s="6" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -15792,7 +15792,7 @@
         <v>1</v>
       </c>
       <c r="V78" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W78" s="6" t="n">
         <v>0</v>
@@ -15880,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W79" s="7" t="n">
         <v>0</v>
@@ -15968,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W80" s="6" t="n">
         <v>0</v>
@@ -16060,13 +16060,13 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X81" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="Y81" s="7" t="n">
         <v>0</v>
@@ -16148,13 +16148,13 @@
         <v>1</v>
       </c>
       <c r="V82" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X82" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="Y82" s="6" t="n">
         <v>0</v>
@@ -16236,13 +16236,13 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X83" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="Y83" s="7" t="n">
         <v>0</v>
@@ -16324,10 +16324,10 @@
         <v>1</v>
       </c>
       <c r="V84" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="W84" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X84" s="6" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W85" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
         <v>1</v>
       </c>
       <c r="V86" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W86" s="6" t="n">
         <v>0</v>
@@ -16588,10 +16588,10 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W87" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>0</v>
@@ -16676,10 +16676,10 @@
         <v>1</v>
       </c>
       <c r="V88" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W88" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X88" s="6" t="n">
         <v>0</v>
@@ -16764,10 +16764,10 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W89" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>0</v>
@@ -16776,7 +16776,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="90">
@@ -16852,10 +16852,10 @@
         <v>1</v>
       </c>
       <c r="V90" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W90" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X90" s="6" t="n">
         <v>0</v>
@@ -16940,7 +16940,7 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W91" s="7" t="n">
         <v>0</v>
@@ -16949,7 +16949,7 @@
         <v>0</v>
       </c>
       <c r="Y91" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z91" s="7" t="n">
         <v>0</v>
@@ -17028,16 +17028,16 @@
         <v>1</v>
       </c>
       <c r="V92" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W92" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y92" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z92" s="6" t="n">
         <v>0</v>
@@ -17116,16 +17116,16 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W93" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y93" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z93" s="7" t="n">
         <v>0</v>
@@ -17204,7 +17204,7 @@
         <v>1</v>
       </c>
       <c r="V94" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W94" s="6" t="n">
         <v>0</v>
@@ -17292,7 +17292,7 @@
         <v>1</v>
       </c>
       <c r="V95" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W95" s="7" t="n">
         <v>0</v>
@@ -17380,7 +17380,7 @@
         <v>1</v>
       </c>
       <c r="V96" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W96" s="6" t="n">
         <v>0</v>
@@ -17468,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="V97" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W97" s="7" t="n">
         <v>0</v>
@@ -17556,7 +17556,7 @@
         <v>1</v>
       </c>
       <c r="V98" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W98" s="6" t="n">
         <v>0</v>
@@ -17648,16 +17648,16 @@
         <v>1</v>
       </c>
       <c r="V99" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W99" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y99" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z99" s="7" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>1</v>
       </c>
       <c r="V100" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W100" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X100" s="6" t="n">
         <v>0</v>
@@ -17824,16 +17824,16 @@
         <v>1</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W101" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y101" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z101" s="7" t="n">
         <v>0</v>
@@ -17912,16 +17912,16 @@
         <v>1</v>
       </c>
       <c r="V102" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W102" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X102" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y102" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z102" s="6" t="n">
         <v>0</v>
@@ -18000,16 +18000,16 @@
         <v>1</v>
       </c>
       <c r="V103" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W103" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y103" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z103" s="7" t="n">
         <v>0</v>
@@ -18088,16 +18088,16 @@
         <v>1</v>
       </c>
       <c r="V104" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="W104" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="X104" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Y104" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="Z104" s="6" t="n">
         <v>0</v>
@@ -18176,10 +18176,10 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
@@ -18264,10 +18264,10 @@
         <v>1</v>
       </c>
       <c r="V106" s="6" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="W106" s="6" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="X106" s="6" t="n">
         <v>0</v>
@@ -18350,7 +18350,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>0</v>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>0</v>
@@ -18400,7 +18400,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>0</v>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
@@ -18475,7 +18475,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
@@ -18500,7 +18500,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -18525,7 +18525,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -18550,10 +18550,10 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -18575,10 +18575,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>0</v>
@@ -18675,10 +18675,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -18700,10 +18700,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -18750,7 +18750,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>0</v>
@@ -18775,10 +18775,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -18800,10 +18800,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -18850,10 +18850,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0</v>
@@ -18875,7 +18875,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>0</v>
@@ -18925,7 +18925,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
@@ -18950,10 +18950,10 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>0</v>
@@ -18975,10 +18975,10 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
@@ -19025,10 +19025,10 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>0</v>
@@ -19075,7 +19075,7 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
@@ -19100,7 +19100,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>0</v>
@@ -19125,10 +19125,10 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -19150,7 +19150,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>0</v>
@@ -19175,7 +19175,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -19200,7 +19200,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>0</v>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -19250,7 +19250,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0</v>
@@ -19275,10 +19275,10 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0</v>
@@ -19300,10 +19300,10 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>0</v>
@@ -19325,7 +19325,7 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -19350,7 +19350,7 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>0</v>
@@ -19375,10 +19375,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>0</v>
@@ -19400,7 +19400,7 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>0</v>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>0</v>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>0</v>
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -19550,10 +19550,10 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>0</v>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
@@ -19600,10 +19600,10 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D54" s="6" t="n">
         <v>0</v>
@@ -19675,7 +19675,7 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>0</v>
@@ -19700,7 +19700,7 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D56" s="6" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0</v>
@@ -19750,7 +19750,7 @@
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D58" s="6" t="n">
         <v>0</v>
@@ -19775,10 +19775,10 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>0</v>
@@ -19800,7 +19800,7 @@
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>0</v>
@@ -19825,7 +19825,7 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -19850,7 +19850,7 @@
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -19900,7 +19900,7 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>0</v>
@@ -19925,7 +19925,7 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -19950,7 +19950,7 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D66" s="6" t="n">
         <v>0</v>
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>0</v>
@@ -20000,7 +20000,7 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>0</v>
@@ -20025,7 +20025,7 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>0</v>
@@ -20100,7 +20100,7 @@
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D72" s="6" t="n">
         <v>0</v>
@@ -20125,7 +20125,7 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>0</v>
@@ -20175,7 +20175,7 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>0</v>
@@ -20200,7 +20200,7 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D76" s="6" t="n">
         <v>0</v>
@@ -20225,7 +20225,7 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D78" s="6" t="n">
         <v>0</v>
@@ -20275,7 +20275,7 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>0</v>
@@ -20300,7 +20300,7 @@
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>0</v>
@@ -20325,13 +20325,13 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F81" s="7" t="n">
         <v>0</v>
@@ -20350,13 +20350,13 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>0</v>
@@ -20375,13 +20375,13 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>0</v>
@@ -20400,10 +20400,10 @@
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E84" s="6" t="n">
         <v>0</v>
@@ -20425,10 +20425,10 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -20450,7 +20450,7 @@
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>0</v>
@@ -20475,10 +20475,10 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>0</v>
@@ -20500,10 +20500,10 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>0</v>
@@ -20525,10 +20525,10 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>0</v>
@@ -20537,7 +20537,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="90">
@@ -20550,10 +20550,10 @@
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E90" s="6" t="n">
         <v>0</v>
@@ -20575,7 +20575,7 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>0</v>
@@ -20584,7 +20584,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>0</v>
@@ -20600,16 +20600,16 @@
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>0</v>
@@ -20625,16 +20625,16 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>0</v>
@@ -20675,7 +20675,7 @@
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>0</v>
@@ -20700,7 +20700,7 @@
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>0</v>
@@ -20725,7 +20725,7 @@
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>0</v>
@@ -20750,7 +20750,7 @@
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>0</v>
@@ -20775,16 +20775,16 @@
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>0</v>
@@ -20800,10 +20800,10 @@
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -20825,16 +20825,16 @@
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>0</v>
@@ -20850,16 +20850,16 @@
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E102" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>0</v>
@@ -20875,16 +20875,16 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>0</v>
@@ -20900,16 +20900,16 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="E104" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>0</v>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
@@ -20950,10 +20950,10 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
       <c r="E106" s="6" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54</t>
+          <t>2026-05-08 15:56</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>
@@ -18297,9 +18297,9 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -18321,17 +18321,17 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Downtime_0_trip_baht</t>
+          <t>Downtime_50_baht</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Downtime_1_trip_baht</t>
+          <t>Downtime_100_baht</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Blank_run_baht</t>
+          <t>Blank_run_50_baht</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -135,10 +135,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01–2026-05-31=6,500 @31.00-31.99, step 1.50%/฿ / 2026-04-12–2026-04-15=8,000 @50.00-50.99, step 1.50%/฿, floor 6,500 / 2026-04-01–2026-04-30=7,500 @50.00-50.99, step 1.50%/฿, floor 6,500 / ปกติ=7,500 @50.00-50.99, step 1.50%/฿</t>
+          <t>2026-05-01–2026-05-31=6,500.00 @31.00-31.99, step 1.50%/฿ / 2026-04-12–2026-04-15=8,000.00 @50.00-50.99, step 1.50%/฿, floor 6,500.00 / 2026-04-01–2026-04-30=7,500.00 @50.00-50.99, step 1.50%/฿, floor 6,500.00 / ปกติ=7,500.00 @50.00-50.99, step 1.50%/฿</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>733061</v>
+        <v>735782.46</v>
       </c>
     </row>
     <row r="14">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3250</v>
+        <v>3273.09</v>
       </c>
     </row>
     <row r="16">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>147134</v>
+        <v>147751</v>
       </c>
     </row>
     <row r="21">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>909445</v>
+        <v>912806</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +813,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -881,10 +881,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
     </row>
     <row r="3">
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
     </row>
     <row r="4">
@@ -947,10 +947,10 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
     </row>
     <row r="5">
@@ -980,10 +980,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
     </row>
     <row r="7">
@@ -1046,10 +1046,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>3638</v>
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>10913</v>
+        <v>10914.69</v>
       </c>
     </row>
     <row r="8">
@@ -1079,19 +1079,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
     </row>
     <row r="9">
@@ -1112,10 +1112,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
     </row>
     <row r="10">
@@ -1145,10 +1145,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
     </row>
     <row r="11">
@@ -1178,10 +1178,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
     </row>
     <row r="12">
@@ -1211,19 +1211,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
     </row>
     <row r="13">
@@ -1244,19 +1244,19 @@
         <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>18200</v>
+        <v>18265.94</v>
       </c>
     </row>
     <row r="14">
@@ -1277,10 +1277,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
     </row>
     <row r="15">
@@ -1310,19 +1310,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="16">
@@ -1343,19 +1343,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="17">
@@ -1376,19 +1376,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="18">
@@ -1409,19 +1409,19 @@
         <v>2</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>18200</v>
+        <v>18265.94</v>
       </c>
     </row>
     <row r="19">
@@ -1442,10 +1442,10 @@
         <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
     </row>
     <row r="20">
@@ -1475,19 +1475,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="21">
@@ -1508,19 +1508,19 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>18200</v>
+        <v>18265.94</v>
       </c>
     </row>
     <row r="22">
@@ -1541,19 +1541,19 @@
         <v>3</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>25480</v>
+        <v>25572.41</v>
       </c>
     </row>
     <row r="23">
@@ -1574,10 +1574,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
     </row>
     <row r="24">
@@ -1607,19 +1607,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="25">
@@ -1640,10 +1640,10 @@
         <v>3</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
     </row>
     <row r="26">
@@ -1673,10 +1673,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
     </row>
     <row r="27">
@@ -1706,19 +1706,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="28">
@@ -1739,19 +1739,19 @@
         <v>3</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>25480</v>
+        <v>25572.41</v>
       </c>
     </row>
     <row r="29">
@@ -1772,19 +1772,19 @@
         <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="30">
@@ -1805,10 +1805,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
     </row>
     <row r="31">
@@ -1838,10 +1838,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
     </row>
     <row r="32">
@@ -1871,19 +1871,19 @@
         <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
     </row>
     <row r="33">
@@ -1904,10 +1904,10 @@
         <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
     </row>
     <row r="34">
@@ -1937,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
     </row>
     <row r="35">
@@ -1970,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
     </row>
     <row r="36">
@@ -2003,19 +2003,19 @@
         <v>3</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>20475</v>
+        <v>20549.43</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>23887</v>
+        <v>23974.43</v>
       </c>
     </row>
     <row r="37">
@@ -2036,10 +2036,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
     </row>
     <row r="38">
@@ -2069,10 +2069,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
     </row>
     <row r="39">
@@ -2102,19 +2102,19 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="H39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>16500</v>
+        <v>16614.72</v>
       </c>
     </row>
     <row r="40">
@@ -2135,10 +2135,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
     </row>
     <row r="41">
@@ -2168,10 +2168,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
     </row>
     <row r="42">
@@ -2201,10 +2201,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
     </row>
     <row r="43">
@@ -2234,10 +2234,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
     </row>
     <row r="44">
@@ -2267,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
     </row>
     <row r="45">
@@ -2300,10 +2300,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
     </row>
     <row r="46">
@@ -2333,10 +2333,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
     </row>
     <row r="47">
@@ -2366,19 +2366,19 @@
         <v>1</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>9900</v>
+        <v>9968.860000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2399,10 +2399,10 @@
         <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
     </row>
     <row r="49">
@@ -2432,10 +2432,10 @@
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
     </row>
     <row r="50">
@@ -2465,10 +2465,10 @@
         <v>2</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
     </row>
     <row r="51">
@@ -2498,10 +2498,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
     </row>
     <row r="52">
@@ -2531,10 +2531,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
     </row>
     <row r="53">
@@ -2564,10 +2564,10 @@
         <v>2</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>0</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
     </row>
     <row r="54">
@@ -2597,19 +2597,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>13100</v>
+        <v>13191.17</v>
       </c>
     </row>
     <row r="55">
@@ -2630,19 +2630,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>13100</v>
+        <v>13191.17</v>
       </c>
     </row>
     <row r="56">
@@ -2663,19 +2663,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>13100</v>
+        <v>13191.17</v>
       </c>
     </row>
     <row r="57">
@@ -2696,19 +2696,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
     </row>
     <row r="58">
@@ -2729,19 +2729,19 @@
         <v>2</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>13000</v>
+        <v>13092.34</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>6500</v>
+        <v>6546</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>19500</v>
+        <v>19638.34</v>
       </c>
     </row>
     <row r="59">
@@ -2762,19 +2762,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
     </row>
     <row r="60">
@@ -2795,19 +2795,19 @@
         <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
     </row>
     <row r="61">
@@ -2828,19 +2828,19 @@
         <v>2</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>14000</v>
+        <v>14046</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>17250</v>
+        <v>17319</v>
       </c>
     </row>
     <row r="62">
@@ -2861,19 +2861,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
     </row>
     <row r="63">
@@ -3323,19 +3323,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="H76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>11067</v>
+        <v>11148.03</v>
       </c>
     </row>
     <row r="77">
@@ -3356,19 +3356,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>11067</v>
+        <v>11148.03</v>
       </c>
     </row>
   </sheetData>
@@ -3498,10 +3498,10 @@
       </c>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="3">
@@ -3540,10 +3540,10 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="4">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>3638</v>
@@ -3624,10 +3624,10 @@
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="6">
@@ -3666,10 +3666,10 @@
       </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="7">
@@ -3708,10 +3708,10 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="8">
@@ -3750,10 +3750,10 @@
       </c>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="9">
@@ -3792,10 +3792,10 @@
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="10">
@@ -3834,10 +3834,10 @@
       </c>
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="11">
@@ -3876,10 +3876,10 @@
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="12">
@@ -3918,10 +3918,10 @@
       </c>
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="13">
@@ -3960,10 +3960,10 @@
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="14">
@@ -4002,10 +4002,10 @@
       </c>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="15">
@@ -4044,10 +4044,10 @@
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="16">
@@ -4086,10 +4086,10 @@
       </c>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="17">
@@ -4128,10 +4128,10 @@
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="18">
@@ -4170,10 +4170,10 @@
       </c>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="19">
@@ -4212,10 +4212,10 @@
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="20">
@@ -4254,10 +4254,10 @@
       </c>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="21">
@@ -4296,10 +4296,10 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="22">
@@ -4338,10 +4338,10 @@
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="23">
@@ -4380,10 +4380,10 @@
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="24">
@@ -4422,10 +4422,10 @@
       </c>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="25">
@@ -4464,10 +4464,10 @@
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="26">
@@ -4506,10 +4506,10 @@
       </c>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="27">
@@ -4548,10 +4548,10 @@
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="28">
@@ -4590,10 +4590,10 @@
       </c>
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="29">
@@ -4968,10 +4968,10 @@
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="38">
@@ -5010,10 +5010,10 @@
       </c>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="6" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="39">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="K39" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="40">
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="41">
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="K41" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
     </row>
   </sheetData>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3250</v>
+        <v>3273.09</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>733061</v>
+        <v>735782.46</v>
       </c>
     </row>
     <row r="3">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3250</v>
+        <v>3273.09</v>
       </c>
     </row>
     <row r="5">
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>147134</v>
+        <v>147751</v>
       </c>
     </row>
     <row r="7">
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>909445</v>
+        <v>912806</v>
       </c>
     </row>
   </sheetData>
@@ -6147,10 +6147,10 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -6224,10 +6224,10 @@
         <v>2</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
@@ -6262,10 +6262,10 @@
         <v>2</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -6300,19 +6300,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
@@ -6338,10 +6338,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
@@ -6350,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>14550</v>
+        <v>14553.38</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -6452,19 +6452,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
@@ -6490,10 +6490,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>3638</v>
@@ -6502,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>10913</v>
+        <v>10914.69</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -6528,19 +6528,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -6604,19 +6604,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
@@ -6642,19 +6642,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
@@ -6718,19 +6718,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -6756,19 +6756,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -6794,19 +6794,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -6832,19 +6832,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -6870,19 +6870,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -6908,10 +6908,10 @@
         <v>3</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
@@ -6946,19 +6946,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -6984,10 +6984,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
@@ -7022,10 +7022,10 @@
         <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -7060,19 +7060,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -7098,19 +7098,19 @@
         <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -7136,10 +7136,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -7174,10 +7174,10 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -7212,19 +7212,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         <v>3</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
@@ -7262,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>21840</v>
+        <v>21919.41</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -7288,19 +7288,19 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
@@ -7326,19 +7326,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10237</v>
+        <v>10274.81</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -7364,10 +7364,10 @@
         <v>2</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>14560</v>
+        <v>14612.94</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
@@ -7402,19 +7402,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10920</v>
+        <v>10959.47</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>0</v>
@@ -7452,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
@@ -7478,19 +7478,19 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>9900</v>
+        <v>9968.860000000001</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -7516,10 +7516,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
@@ -7528,7 +7528,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>0</v>
@@ -7566,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -7592,10 +7592,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
@@ -7604,7 +7604,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>13650</v>
+        <v>13699.62</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -7630,10 +7630,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -7718,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
@@ -7794,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -7820,10 +7820,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -7832,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
@@ -7858,19 +7858,19 @@
         <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>9900</v>
+        <v>9968.860000000001</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -7896,10 +7896,10 @@
         <v>2</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -7934,10 +7934,10 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -7946,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -7972,19 +7972,19 @@
         <v>2</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>19800</v>
+        <v>19936.72</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -8010,19 +8010,19 @@
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>13200</v>
+        <v>13291.72</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>19800</v>
+        <v>19936.72</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -8048,19 +8048,19 @@
         <v>3</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>19800</v>
+        <v>19937.58</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>26400</v>
+        <v>26582.58</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -8086,19 +8086,19 @@
         <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -8124,19 +8124,19 @@
         <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
@@ -8162,19 +8162,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -8200,19 +8200,19 @@
         <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
@@ -8238,19 +8238,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -8276,19 +8276,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>9750</v>
+        <v>9819.17</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
@@ -8314,23 +8314,23 @@
         <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>14000</v>
+        <v>14046</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>20500</v>
+        <v>20592</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,273.09฿)</t>
         </is>
       </c>
     </row>
@@ -8770,19 +8770,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11067</v>
+        <v>11148.03</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -8808,19 +8808,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>11067</v>
+        <v>11148.03</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W2" s="6" t="n">
         <v>0</v>
@@ -9164,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W3" s="7" t="n">
         <v>0</v>
@@ -9252,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W4" s="6" t="n">
         <v>0</v>
@@ -9340,7 +9340,7 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W5" s="7" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W6" s="6" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W7" s="7" t="n">
         <v>0</v>
@@ -9608,7 +9608,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W8" s="6" t="n">
         <v>0</v>
@@ -9696,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -9784,7 +9784,7 @@
         <v>1</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W10" s="6" t="n">
         <v>3638</v>
@@ -9872,10 +9872,10 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
@@ -9960,7 +9960,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W12" s="6" t="n">
         <v>0</v>
@@ -10048,7 +10048,7 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W13" s="7" t="n">
         <v>0</v>
@@ -10136,7 +10136,7 @@
         <v>1</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W14" s="6" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
@@ -10312,10 +10312,10 @@
         <v>1</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X16" s="6" t="n">
         <v>0</v>
@@ -10400,7 +10400,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W17" s="7" t="n">
         <v>0</v>
@@ -10488,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W18" s="6" t="n">
         <v>0</v>
@@ -10576,10 +10576,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -10664,10 +10664,10 @@
         <v>1</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X20" s="6" t="n">
         <v>0</v>
@@ -10752,10 +10752,10 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>0</v>
@@ -10840,10 +10840,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X22" s="6" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W23" s="7" t="n">
         <v>0</v>
@@ -11016,7 +11016,7 @@
         <v>1</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W24" s="6" t="n">
         <v>0</v>
@@ -11104,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W25" s="7" t="n">
         <v>0</v>
@@ -11192,10 +11192,10 @@
         <v>1</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X26" s="6" t="n">
         <v>0</v>
@@ -11280,10 +11280,10 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>0</v>
@@ -11368,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W28" s="6" t="n">
         <v>0</v>
@@ -11456,10 +11456,10 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>0</v>
@@ -11544,7 +11544,7 @@
         <v>1</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W30" s="6" t="n">
         <v>0</v>
@@ -11632,7 +11632,7 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W31" s="7" t="n">
         <v>0</v>
@@ -11720,7 +11720,7 @@
         <v>1</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W32" s="6" t="n">
         <v>0</v>
@@ -11812,10 +11812,10 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W33" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>0</v>
@@ -11900,7 +11900,7 @@
         <v>1</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W34" s="6" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -12076,7 +12076,7 @@
         <v>1</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W36" s="6" t="n">
         <v>0</v>
@@ -12164,7 +12164,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W38" s="6" t="n">
         <v>0</v>
@@ -12340,10 +12340,10 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X39" s="7" t="n">
         <v>0</v>
@@ -12428,10 +12428,10 @@
         <v>1</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W40" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X40" s="6" t="n">
         <v>0</v>
@@ -12516,7 +12516,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -12604,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W42" s="6" t="n">
         <v>0</v>
@@ -12692,10 +12692,10 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W43" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X43" s="7" t="n">
         <v>0</v>
@@ -12780,7 +12780,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W44" s="6" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W45" s="7" t="n">
         <v>0</v>
@@ -12956,7 +12956,7 @@
         <v>1</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W46" s="6" t="n">
         <v>0</v>
@@ -13044,10 +13044,10 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W47" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="X47" s="7" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W48" s="6" t="n">
         <v>0</v>
@@ -13220,7 +13220,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -13312,10 +13312,10 @@
         <v>1</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W50" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X50" s="6" t="n">
         <v>0</v>
@@ -13400,7 +13400,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W51" s="7" t="n">
         <v>0</v>
@@ -13488,10 +13488,10 @@
         <v>1</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="W52" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="X52" s="6" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W53" s="7" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W54" s="6" t="n">
         <v>0</v>
@@ -13752,7 +13752,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W55" s="7" t="n">
         <v>0</v>
@@ -13840,7 +13840,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W56" s="6" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W57" s="7" t="n">
         <v>0</v>
@@ -14016,7 +14016,7 @@
         <v>1</v>
       </c>
       <c r="V58" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W58" s="6" t="n">
         <v>0</v>
@@ -14104,10 +14104,10 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W59" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>0</v>
@@ -14192,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="V60" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W60" s="6" t="n">
         <v>0</v>
@@ -14284,7 +14284,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>1</v>
       </c>
       <c r="V62" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W62" s="6" t="n">
         <v>0</v>
@@ -14460,7 +14460,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -14548,7 +14548,7 @@
         <v>1</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W64" s="6" t="n">
         <v>0</v>
@@ -14636,7 +14636,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W66" s="6" t="n">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W67" s="7" t="n">
         <v>0</v>
@@ -14904,7 +14904,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W68" s="6" t="n">
         <v>0</v>
@@ -14992,7 +14992,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -15080,7 +15080,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W70" s="6" t="n">
         <v>0</v>
@@ -15168,10 +15168,10 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W71" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="X71" s="7" t="n">
         <v>0</v>
@@ -15256,7 +15256,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W72" s="6" t="n">
         <v>0</v>
@@ -15344,7 +15344,7 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W73" s="7" t="n">
         <v>0</v>
@@ -15432,7 +15432,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W74" s="6" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W75" s="7" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
         <v>1</v>
       </c>
       <c r="V76" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W76" s="6" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -15792,7 +15792,7 @@
         <v>1</v>
       </c>
       <c r="V78" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W78" s="6" t="n">
         <v>0</v>
@@ -15880,7 +15880,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W79" s="7" t="n">
         <v>0</v>
@@ -15968,7 +15968,7 @@
         <v>1</v>
       </c>
       <c r="V80" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W80" s="6" t="n">
         <v>0</v>
@@ -16060,13 +16060,13 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X81" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="Y81" s="7" t="n">
         <v>0</v>
@@ -16148,13 +16148,13 @@
         <v>1</v>
       </c>
       <c r="V82" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="X82" s="6" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="Y82" s="6" t="n">
         <v>0</v>
@@ -16236,13 +16236,13 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X83" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="Y83" s="7" t="n">
         <v>0</v>
@@ -16324,10 +16324,10 @@
         <v>1</v>
       </c>
       <c r="V84" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="W84" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X84" s="6" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W85" s="7" t="n">
-        <v>6500</v>
+        <v>6546</v>
       </c>
       <c r="X85" s="7" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
         <v>1</v>
       </c>
       <c r="V86" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W86" s="6" t="n">
         <v>0</v>
@@ -16588,10 +16588,10 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W87" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>0</v>
@@ -16676,10 +16676,10 @@
         <v>1</v>
       </c>
       <c r="V88" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W88" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X88" s="6" t="n">
         <v>0</v>
@@ -16764,10 +16764,10 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W89" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X89" s="7" t="n">
         <v>0</v>
@@ -16776,7 +16776,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="90">
@@ -16852,10 +16852,10 @@
         <v>1</v>
       </c>
       <c r="V90" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="W90" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="X90" s="6" t="n">
         <v>0</v>
@@ -18176,10 +18176,10 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="W105" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="X105" s="7" t="n">
         <v>0</v>
@@ -18264,10 +18264,10 @@
         <v>1</v>
       </c>
       <c r="V106" s="6" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="W106" s="6" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="X106" s="6" t="n">
         <v>0</v>
@@ -18350,7 +18350,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>0</v>
@@ -18375,7 +18375,7 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>0</v>
@@ -18400,7 +18400,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>0</v>
@@ -18425,7 +18425,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
@@ -18475,7 +18475,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>0</v>
@@ -18500,7 +18500,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -18525,7 +18525,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -18550,7 +18550,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>3638</v>
@@ -18575,10 +18575,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>0</v>
@@ -18675,10 +18675,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -18700,10 +18700,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -18750,7 +18750,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>0</v>
@@ -18775,10 +18775,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -18800,10 +18800,10 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -18825,10 +18825,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
@@ -18850,10 +18850,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0</v>
@@ -18875,7 +18875,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>0</v>
@@ -18925,7 +18925,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
@@ -18950,10 +18950,10 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>0</v>
@@ -18975,10 +18975,10 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>0</v>
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>0</v>
@@ -19025,10 +19025,10 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -19050,7 +19050,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>0</v>
@@ -19075,7 +19075,7 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>0</v>
@@ -19100,7 +19100,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>0</v>
@@ -19125,10 +19125,10 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -19150,7 +19150,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>0</v>
@@ -19175,7 +19175,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -19200,7 +19200,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>0</v>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -19250,7 +19250,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0</v>
@@ -19275,10 +19275,10 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>0</v>
@@ -19300,10 +19300,10 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>0</v>
@@ -19325,7 +19325,7 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -19350,7 +19350,7 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>0</v>
@@ -19375,10 +19375,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>0</v>
@@ -19400,7 +19400,7 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>0</v>
@@ -19475,10 +19475,10 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>0</v>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>0</v>
@@ -19525,7 +19525,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -19550,10 +19550,10 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>0</v>
@@ -19575,7 +19575,7 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
@@ -19600,10 +19600,10 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
@@ -19650,7 +19650,7 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D54" s="6" t="n">
         <v>0</v>
@@ -19675,7 +19675,7 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>0</v>
@@ -19700,7 +19700,7 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D56" s="6" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>0</v>
@@ -19750,7 +19750,7 @@
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D58" s="6" t="n">
         <v>0</v>
@@ -19775,10 +19775,10 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>0</v>
@@ -19800,7 +19800,7 @@
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>0</v>
@@ -19825,7 +19825,7 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -19850,7 +19850,7 @@
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -19900,7 +19900,7 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>0</v>
@@ -19925,7 +19925,7 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -19950,7 +19950,7 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D66" s="6" t="n">
         <v>0</v>
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>0</v>
@@ -20000,7 +20000,7 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>0</v>
@@ -20025,7 +20025,7 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -20050,7 +20050,7 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>0</v>
@@ -20100,7 +20100,7 @@
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D72" s="6" t="n">
         <v>0</v>
@@ -20125,7 +20125,7 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>0</v>
@@ -20175,7 +20175,7 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>0</v>
@@ -20200,7 +20200,7 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D76" s="6" t="n">
         <v>0</v>
@@ -20225,7 +20225,7 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D78" s="6" t="n">
         <v>0</v>
@@ -20275,7 +20275,7 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>0</v>
@@ -20300,7 +20300,7 @@
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>0</v>
@@ -20325,13 +20325,13 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="F81" s="7" t="n">
         <v>0</v>
@@ -20350,13 +20350,13 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>0</v>
@@ -20375,13 +20375,13 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>0</v>
@@ -20400,10 +20400,10 @@
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E84" s="6" t="n">
         <v>0</v>
@@ -20425,10 +20425,10 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>6500</v>
+        <v>6546</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -20450,7 +20450,7 @@
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>0</v>
@@ -20475,10 +20475,10 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>0</v>
@@ -20500,10 +20500,10 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>0</v>
@@ -20525,10 +20525,10 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>0</v>
@@ -20537,7 +20537,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="90">
@@ -20550,10 +20550,10 @@
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
       <c r="E90" s="6" t="n">
         <v>0</v>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0</v>
@@ -20950,10 +20950,10 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
       <c r="E106" s="6" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -26,19 +26,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Customer_Trips_Per_Day'!$A$1:$C$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Audit_Log'!$A$1:$J$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trips_Pricing_All'!$A$1:$G$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Customer_Trips_Per_Day'!$A$1:$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Audit_Log'!$A$1:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trips_Pricing_All'!$A$1:$G$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched_Log'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Daily_Activity'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Daily_Time_24h_Check'!$A$1:$M$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$77</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Daily_Activity'!$A$1:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Daily_Time_24h_Check'!$A$1:$M$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manual_Extra_Trips'!$A$1:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'NoWork_Outbound_50pct'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Phantom_Trip_Candidates'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Phantom_Trip_Candidates'!$A$1:$E$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Hints_DoubleOrigin'!$A$1:$D$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>735782.46</v>
+        <v>720918.4</v>
       </c>
     </row>
     <row r="14">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>147751</v>
+        <v>140319</v>
       </c>
     </row>
     <row r="21">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>912806</v>
+        <v>890510</v>
       </c>
     </row>
   </sheetData>
@@ -802,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3305,74 +3305,8 @@
         <v>9750</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="G76" s="6" t="n">
-        <v>3716</v>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="6" t="n">
-        <v>11148.03</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F77" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="G77" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="H77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="7" t="n">
-        <v>11148.03</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I77"/>
+  <autoFilter ref="A1:I75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3383,7 +3317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4934,21 +4868,21 @@
     </row>
     <row r="37">
       <c r="A37" s="9" t="n">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>midnight_full</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
@@ -4956,31 +4890,39 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (20.96h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
+          <t>2026-04-21 16:38:59</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:36:47</t>
+        </is>
+      </c>
       <c r="K37" s="7" t="n">
-        <v>7432.03</v>
+        <v>6645.86</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3716</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8681</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -4990,7 +4932,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>midnight_full</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -4998,22 +4940,30 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (21.30h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
+        </is>
+      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
+          <t>2026-04-21 13:37:02</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:55:11</t>
+        </is>
+      </c>
       <c r="K38" s="6" t="n">
-        <v>7432.03</v>
+        <v>6645.86</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>3716</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="39">
@@ -5022,7 +4972,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-9629</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -5046,17 +4996,17 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (20.96h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
+          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (18.79h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21 16:38:59</t>
+          <t>2026-04-21 09:15:51</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22 13:36:47</t>
+          <t>2026-04-22 04:03:28</t>
         </is>
       </c>
       <c r="K39" s="7" t="n">
@@ -5066,108 +5016,8 @@
         <v>6645</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>71-8681</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>midnight_full</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (21.30h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-21 13:37:02</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22 10:55:11</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>6645.86</v>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>6645</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>71-9629</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>midnight_full</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (18.79h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-21 09:15:51</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-22 04:03:28</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>6645.86</v>
-      </c>
-      <c r="L41" s="7" t="n">
-        <v>6645</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:L39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5609,7 +5459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5667,8 +5517,50 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>7432.03</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>No matched trip on this trip_date; OAT rule: charge 1 full trip (review before adding to grand total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7432.03</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>No matched trip on this trip_date; OAT rule: charge 1 full trip (review before adding to grand total)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5777,7 +5669,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>735782.46</v>
+        <v>720918.4</v>
       </c>
     </row>
     <row r="3">
@@ -5837,7 +5729,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>147751</v>
+        <v>140319</v>
       </c>
     </row>
     <row r="7">
@@ -5867,7 +5759,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>912806</v>
+        <v>890510</v>
       </c>
     </row>
   </sheetData>
@@ -5882,7 +5774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6116,19 +6008,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C21"/>
+  <autoFilter ref="A1:C20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6139,7 +6020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8752,84 +8633,8 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F69" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="G69" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="H69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="7" t="n">
-        <v>11148.03</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="6" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="G70" s="6" t="n">
-        <v>3716</v>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="6" t="n">
-        <v>11148.03</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J70"/>
+  <autoFilter ref="A1:J68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8840,7 +8645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z106"/>
+  <dimension ref="A1:Z104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18103,184 +17908,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B105" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C105" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
-      </c>
-      <c r="I105" s="11" t="n">
-        <v>46143.26266203704</v>
-      </c>
-      <c r="J105" s="11" t="n">
-        <v>46143.48762731482</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L105" s="11" t="n">
-        <v>46143.56759259259</v>
-      </c>
-      <c r="M105" s="11" t="n">
-        <v>46143.6196875</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O105" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P105" s="2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="2" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="S105" s="2" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="T105" s="2" t="n"/>
-      <c r="U105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V105" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="W105" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="X105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z105" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B106" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C106" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>7.14</t>
-        </is>
-      </c>
-      <c r="H106" s="5" t="inlineStr">
-        <is>
-          <t>7.14</t>
-        </is>
-      </c>
-      <c r="I106" s="10" t="n">
-        <v>46143.82527777777</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>46143.89219907407</v>
-      </c>
-      <c r="K106" s="5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="L106" s="10" t="n">
-        <v>46143.96318287037</v>
-      </c>
-      <c r="M106" s="10" t="n">
-        <v>46143.97673611111</v>
-      </c>
-      <c r="N106" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O106" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P106" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Q106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" s="5" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="S106" s="5" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="T106" s="5" t="n"/>
-      <c r="U106" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V106" s="6" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="W106" s="6" t="n">
-        <v>3716</v>
-      </c>
-      <c r="X106" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z106"/>
+  <autoFilter ref="A1:Z104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18291,7 +17920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20915,58 +20544,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="D105" s="7" t="n">
-        <v>3716</v>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="n">
-        <v>7432.03</v>
-      </c>
-      <c r="D106" s="6" t="n">
-        <v>3716</v>
-      </c>
-      <c r="E106" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G106"/>
+  <autoFilter ref="A1:G104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21524,7 +21103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22136,37 +21715,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:I20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22177,7 +21727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -25552,102 +25102,8 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v>15.43</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>20.37</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M73"/>
+  <autoFilter ref="A1:M71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -25,7 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hints_DoubleOrigin" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Customer_Trips_Per_Day'!$A$1:$C$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Audit_Log'!$A$1:$J$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$104</definedName>
@@ -35,7 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Daily_Time_24h_Check'!$A$1:$M$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manual_Extra_Trips'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manual_Extra_Trips'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'NoWork_Outbound_50pct'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Phantom_Trip_Candidates'!$A$1:$E$4</definedName>
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>720918.4</v>
+        <v>713418.4</v>
       </c>
     </row>
     <row r="14">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>890510</v>
+        <v>883010</v>
       </c>
     </row>
   </sheetData>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
         <v>6546.17</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>14046</v>
+        <v>6546.17</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>3273</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>17319</v>
+        <v>9819</v>
       </c>
     </row>
     <row r="62">
@@ -5028,13 +5028,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5059,26 +5059,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5632,7 +5614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5669,101 +5651,86 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>720918.4</v>
+        <v>713418.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ในนั้น: เที่ยวเพิ่ม (manual_extra_trips ไม่มีใน GPS)</t>
+          <t>ค่าขนส่งขากลับ (manual_return_trips — ไม่เพิ่มจำนวน matched)</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>7500</v>
+        <v>3273.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ค่าขนส่งขากลับ (manual_return_trips — ไม่เพิ่มจำนวน matched)</t>
+          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>3273.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
+          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0</v>
+        <v>140319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
+          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>140319</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
+          <t>Grand (A+C+D+R)</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Grand (A+C+D+R)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>890510</v>
+        <v>883010</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8"/>
+  <autoFilter ref="A1:C7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5947,7 +5914,7 @@
         <v>46134</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>4</v>
@@ -8192,13 +8159,13 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>6546.17</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>14046</v>
+        <v>6546.17</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>3273</v>
@@ -8207,11 +8174,11 @@
         <v>3273</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>20592</v>
+        <v>13092</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | เที่ยวเพิ่ม (ไม่มีใน GPS): P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS) (+7,500.00฿) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,273.09฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (วันงาน 1 เที่ยว) | ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,273.09฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:46</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>พ.ค. 2569: ฐาน 6,500 บาท (แถบน้ำมัน 31.00–31.99 บ./ล.) ปรับ +1.5% ต่อ 1 บาท จากราคาบางจาก ไฮดีเซล S (คอลัมน์ที่ 2)</t>
+          <t>พ.ค. 2569: ฐาน 6,400 บาท (แถบน้ำมัน 31.00–31.99 บ./ล.) ปรับ +1.5% ต่อ 1 บาท (linear จากฐาน) อ้างอิงบางจาก ไฮดีเซล S (คอลัมน์ที่ 2)</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1147055</v>
+        <v>1129408</v>
       </c>
     </row>
     <row r="14">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>275659</v>
+        <v>271408</v>
       </c>
     </row>
     <row r="21">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1425964</v>
+        <v>1404066</v>
       </c>
     </row>
   </sheetData>
@@ -914,19 +914,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="4">
@@ -947,19 +947,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="5">
@@ -980,19 +980,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="6">
@@ -1013,19 +1013,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="7">
@@ -1046,19 +1046,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="8">
@@ -1079,19 +1079,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="9">
@@ -1112,19 +1112,19 @@
         <v>2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>22133</v>
+        <v>21792</v>
       </c>
     </row>
     <row r="10">
@@ -1145,19 +1145,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="11">
@@ -1178,19 +1178,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="12">
@@ -1211,19 +1211,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="13">
@@ -1244,19 +1244,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="14">
@@ -1277,19 +1277,19 @@
         <v>2</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>18444</v>
+        <v>18160</v>
       </c>
     </row>
     <row r="15">
@@ -1310,19 +1310,19 @@
         <v>2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>18444</v>
+        <v>18160</v>
       </c>
     </row>
     <row r="16">
@@ -1343,19 +1343,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="17">
@@ -1376,19 +1376,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="18">
@@ -1409,10 +1409,10 @@
         <v>2</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="19">
@@ -1442,19 +1442,19 @@
         <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>18444</v>
+        <v>18160</v>
       </c>
     </row>
     <row r="20">
@@ -1475,19 +1475,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="21">
@@ -1508,10 +1508,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="22">
@@ -1541,10 +1541,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
     </row>
     <row r="23">
@@ -1574,19 +1574,19 @@
         <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="24">
@@ -1607,19 +1607,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="25">
@@ -1640,10 +1640,10 @@
         <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
     </row>
     <row r="26">
@@ -1673,19 +1673,19 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>18200</v>
+        <v>17920</v>
       </c>
     </row>
     <row r="27">
@@ -1706,19 +1706,19 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>21840</v>
+        <v>21504</v>
       </c>
     </row>
     <row r="28">
@@ -1739,10 +1739,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
     </row>
     <row r="29">
@@ -1772,19 +1772,19 @@
         <v>2</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>21840</v>
+        <v>21504</v>
       </c>
     </row>
     <row r="30">
@@ -1805,10 +1805,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
     </row>
     <row r="31">
@@ -1838,10 +1838,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="32">
@@ -1871,10 +1871,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
     </row>
     <row r="33">
@@ -1904,19 +1904,19 @@
         <v>2</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>18200</v>
+        <v>17920</v>
       </c>
     </row>
     <row r="34">
@@ -1937,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
     </row>
     <row r="35">
@@ -1970,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="36">
@@ -2003,10 +2003,10 @@
         <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="37">
@@ -2036,19 +2036,19 @@
         <v>2</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>18444</v>
+        <v>18160</v>
       </c>
     </row>
     <row r="38">
@@ -2069,10 +2069,10 @@
         <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="39">
@@ -2102,10 +2102,10 @@
         <v>1</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="40">
@@ -2135,10 +2135,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="41">
@@ -2168,19 +2168,19 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>18688</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="42">
@@ -2201,19 +2201,19 @@
         <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>18688</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="43">
@@ -2234,19 +2234,19 @@
         <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="44">
@@ -2267,10 +2267,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="45">
@@ -2300,10 +2300,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="46">
@@ -2333,10 +2333,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="47">
@@ -2366,19 +2366,19 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>18688</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="48">
@@ -2399,10 +2399,10 @@
         <v>3</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>22425</v>
+        <v>22080</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>22425</v>
+        <v>22080</v>
       </c>
     </row>
     <row r="49">
@@ -2432,10 +2432,10 @@
         <v>1</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>0</v>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="50">
@@ -2465,10 +2465,10 @@
         <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="51">
@@ -2498,10 +2498,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="52">
@@ -2531,10 +2531,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="53">
@@ -2564,19 +2564,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="54">
@@ -2597,10 +2597,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="55">
@@ -2630,19 +2630,19 @@
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="56">
@@ -2663,19 +2663,19 @@
         <v>2</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>18931</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="57">
@@ -2696,19 +2696,19 @@
         <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>18931</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="58">
@@ -2729,19 +2729,19 @@
         <v>1</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="59">
@@ -2762,19 +2762,19 @@
         <v>2</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>18931</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="60">
@@ -2795,19 +2795,19 @@
         <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="61">
@@ -2828,10 +2828,10 @@
         <v>2</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="62">
@@ -2861,19 +2861,19 @@
         <v>2</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>18931</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="63">
@@ -2894,19 +2894,19 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="64">
@@ -2927,10 +2927,10 @@
         <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>0</v>
@@ -2939,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="65">
@@ -2960,10 +2960,10 @@
         <v>2</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="66">
@@ -2993,10 +2993,10 @@
         <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="67">
@@ -3026,19 +3026,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="68">
@@ -3059,19 +3059,19 @@
         <v>1</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="69">
@@ -3092,19 +3092,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="70">
@@ -3125,10 +3125,10 @@
         <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>0</v>
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="71">
@@ -3158,19 +3158,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="72">
@@ -3191,19 +3191,19 @@
         <v>1</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="73">
@@ -3224,19 +3224,19 @@
         <v>2</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>22717</v>
+        <v>22368</v>
       </c>
     </row>
     <row r="74">
@@ -3257,10 +3257,10 @@
         <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="75">
@@ -3290,19 +3290,19 @@
         <v>2</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H75" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>18931</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="76">
@@ -3323,19 +3323,19 @@
         <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="77">
@@ -3356,10 +3356,10 @@
         <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="78">
@@ -3389,19 +3389,19 @@
         <v>2</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H78" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>18931</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="79">
@@ -3422,19 +3422,19 @@
         <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="80">
@@ -3455,10 +3455,10 @@
         <v>2</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="81">
@@ -3488,19 +3488,19 @@
         <v>2</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="H81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>22717</v>
+        <v>22368</v>
       </c>
     </row>
     <row r="82">
@@ -3521,10 +3521,10 @@
         <v>2</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="83">
@@ -3554,10 +3554,10 @@
         <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>0</v>
@@ -3566,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="84">
@@ -3587,10 +3587,10 @@
         <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="85">
@@ -3620,19 +3620,19 @@
         <v>1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="86">
@@ -3653,10 +3653,10 @@
         <v>1</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="87">
@@ -3686,10 +3686,10 @@
         <v>1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="88">
@@ -3719,10 +3719,10 @@
         <v>1</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="89">
@@ -3752,19 +3752,19 @@
         <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="90">
@@ -3785,19 +3785,19 @@
         <v>2</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>22426</v>
+        <v>22080</v>
       </c>
     </row>
     <row r="91">
@@ -3818,19 +3818,19 @@
         <v>2</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>22426</v>
+        <v>22080</v>
       </c>
     </row>
     <row r="92">
@@ -3851,19 +3851,19 @@
         <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="93">
@@ -3884,19 +3884,19 @@
         <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="94">
@@ -3917,19 +3917,19 @@
         <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="95">
@@ -3950,19 +3950,19 @@
         <v>1</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="96">
@@ -3983,19 +3983,19 @@
         <v>3</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>22425</v>
+        <v>22080</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>26163</v>
+        <v>25760</v>
       </c>
     </row>
     <row r="97">
@@ -4016,19 +4016,19 @@
         <v>2</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>18688</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="98">
@@ -4049,19 +4049,19 @@
         <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="99">
@@ -4082,19 +4082,19 @@
         <v>1</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="100">
@@ -4115,10 +4115,10 @@
         <v>2</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="101">
@@ -4148,10 +4148,10 @@
         <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="102">
@@ -4181,19 +4181,19 @@
         <v>2</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>18688</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="103">
@@ -4214,10 +4214,10 @@
         <v>2</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="104">
@@ -4247,19 +4247,19 @@
         <v>1</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="105">
@@ -4280,10 +4280,10 @@
         <v>1</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="106">
@@ -4313,10 +4313,10 @@
         <v>2</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="107">
@@ -4346,19 +4346,19 @@
         <v>1</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="108">
@@ -4379,10 +4379,10 @@
         <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="109">
@@ -4412,19 +4412,19 @@
         <v>2</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>18444</v>
+        <v>18160</v>
       </c>
     </row>
     <row r="110">
@@ -4445,10 +4445,10 @@
         <v>1</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>0</v>
@@ -4457,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="111">
@@ -4478,19 +4478,19 @@
         <v>1</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="112">
@@ -4511,19 +4511,19 @@
         <v>2</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G112" s="6" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="6" t="n">
-        <v>22133</v>
+        <v>21792</v>
       </c>
     </row>
   </sheetData>
@@ -4653,10 +4653,10 @@
       </c>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="3">
@@ -4695,10 +4695,10 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="4">
@@ -4737,10 +4737,10 @@
       </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="5">
@@ -4779,10 +4779,10 @@
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="6">
@@ -4821,10 +4821,10 @@
       </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="7">
@@ -4863,10 +4863,10 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="8">
@@ -4905,10 +4905,10 @@
       </c>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="9">
@@ -4947,10 +4947,10 @@
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="10">
@@ -4989,10 +4989,10 @@
       </c>
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="11">
@@ -5031,10 +5031,10 @@
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="12">
@@ -5073,10 +5073,10 @@
       </c>
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="13">
@@ -5115,10 +5115,10 @@
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="14">
@@ -5157,10 +5157,10 @@
       </c>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="15">
@@ -5199,10 +5199,10 @@
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="16">
@@ -5241,10 +5241,10 @@
       </c>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="17">
@@ -5283,10 +5283,10 @@
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="18">
@@ -5325,10 +5325,10 @@
       </c>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="19">
@@ -5367,10 +5367,10 @@
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="20">
@@ -5409,10 +5409,10 @@
       </c>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="21">
@@ -5451,10 +5451,10 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="22">
@@ -5493,10 +5493,10 @@
       </c>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="23">
@@ -5535,10 +5535,10 @@
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="24">
@@ -5577,10 +5577,10 @@
       </c>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="25">
@@ -5619,10 +5619,10 @@
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="26">
@@ -5661,10 +5661,10 @@
       </c>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="27">
@@ -5703,10 +5703,10 @@
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="28">
@@ -5745,10 +5745,10 @@
       </c>
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="29">
@@ -5787,10 +5787,10 @@
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="30">
@@ -5829,10 +5829,10 @@
       </c>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="31">
@@ -5871,10 +5871,10 @@
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="32">
@@ -5913,10 +5913,10 @@
       </c>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="33">
@@ -5955,10 +5955,10 @@
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="34">
@@ -5997,10 +5997,10 @@
       </c>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="35">
@@ -6039,10 +6039,10 @@
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="36">
@@ -6081,10 +6081,10 @@
       </c>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="37">
@@ -6123,10 +6123,10 @@
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="38">
@@ -6165,10 +6165,10 @@
       </c>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="39">
@@ -6207,10 +6207,10 @@
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="40">
@@ -6249,10 +6249,10 @@
       </c>
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="41">
@@ -6291,10 +6291,10 @@
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="42">
@@ -6333,10 +6333,10 @@
       </c>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="43">
@@ -6375,10 +6375,10 @@
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="44">
@@ -6417,10 +6417,10 @@
       </c>
       <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="45">
@@ -6459,10 +6459,10 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="46">
@@ -6501,10 +6501,10 @@
       </c>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="47">
@@ -6543,10 +6543,10 @@
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="48">
@@ -6585,10 +6585,10 @@
       </c>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="49">
@@ -6627,10 +6627,10 @@
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="50">
@@ -6669,10 +6669,10 @@
       </c>
       <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="51">
@@ -6711,10 +6711,10 @@
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="52">
@@ -6753,10 +6753,10 @@
       </c>
       <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="53">
@@ -6795,10 +6795,10 @@
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="54">
@@ -6837,10 +6837,10 @@
       </c>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="55">
@@ -6879,10 +6879,10 @@
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="56">
@@ -6921,10 +6921,10 @@
       </c>
       <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="57">
@@ -6963,10 +6963,10 @@
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="58">
@@ -7005,10 +7005,10 @@
       </c>
       <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="59">
@@ -7047,10 +7047,10 @@
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="60">
@@ -7089,10 +7089,10 @@
       </c>
       <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="61">
@@ -7131,10 +7131,10 @@
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="62">
@@ -7173,10 +7173,10 @@
       </c>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="63">
@@ -7215,10 +7215,10 @@
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="64">
@@ -7257,10 +7257,10 @@
       </c>
       <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="65">
@@ -7299,10 +7299,10 @@
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="66">
@@ -7341,10 +7341,10 @@
       </c>
       <c r="J66" s="5" t="inlineStr"/>
       <c r="K66" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="67">
@@ -7383,10 +7383,10 @@
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="68">
@@ -7425,10 +7425,10 @@
       </c>
       <c r="J68" s="5" t="inlineStr"/>
       <c r="K68" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="69">
@@ -7467,10 +7467,10 @@
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="70">
@@ -7509,10 +7509,10 @@
       </c>
       <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="71">
@@ -7551,10 +7551,10 @@
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="72">
@@ -7593,10 +7593,10 @@
       </c>
       <c r="J72" s="5" t="inlineStr"/>
       <c r="K72" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="73">
@@ -7635,10 +7635,10 @@
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="74">
@@ -7677,10 +7677,10 @@
       </c>
       <c r="J74" s="5" t="inlineStr"/>
       <c r="K74" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="75">
@@ -7719,10 +7719,10 @@
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
   </sheetData>
@@ -7952,7 +7952,7 @@
         <v>13.11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>1147055</v>
+        <v>1129408</v>
       </c>
     </row>
     <row r="3">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>275659</v>
+        <v>271408</v>
       </c>
     </row>
     <row r="6">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1425964</v>
+        <v>1404066</v>
       </c>
     </row>
   </sheetData>
@@ -8643,19 +8643,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -8681,19 +8681,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
@@ -8719,19 +8719,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -8757,19 +8757,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
@@ -8795,19 +8795,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -8833,19 +8833,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
@@ -8871,19 +8871,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -8909,19 +8909,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -8947,19 +8947,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -8985,19 +8985,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
@@ -9023,19 +9023,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -9061,19 +9061,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
@@ -9099,19 +9099,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -9137,19 +9137,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -9175,10 +9175,10 @@
         <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -9213,10 +9213,10 @@
         <v>2</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
@@ -9225,7 +9225,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -9251,19 +9251,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -9289,19 +9289,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
@@ -9327,10 +9327,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0</v>
@@ -9339,7 +9339,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -9365,19 +9365,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
@@ -9403,19 +9403,19 @@
         <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -9441,19 +9441,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -9479,10 +9479,10 @@
         <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -9491,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -9517,10 +9517,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0</v>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -9555,19 +9555,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -9593,19 +9593,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -9631,19 +9631,19 @@
         <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -9669,19 +9669,19 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
@@ -9707,19 +9707,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -9745,10 +9745,10 @@
         <v>2</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>0</v>
@@ -9757,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
@@ -9783,19 +9783,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -9821,10 +9821,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>0</v>
@@ -9833,7 +9833,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
@@ -9859,10 +9859,10 @@
         <v>2</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>0</v>
@@ -9871,7 +9871,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -9897,10 +9897,10 @@
         <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>0</v>
@@ -9909,7 +9909,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
@@ -9935,19 +9935,19 @@
         <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="H37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>10920</v>
+        <v>10752</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -9973,19 +9973,19 @@
         <v>1</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -10011,10 +10011,10 @@
         <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>14560</v>
+        <v>14336</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -10049,10 +10049,10 @@
         <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -10061,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -10087,10 +10087,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>0</v>
@@ -10099,7 +10099,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -10125,10 +10125,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -10137,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -10163,19 +10163,19 @@
         <v>1</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -10201,10 +10201,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>0</v>
@@ -10213,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
@@ -10239,19 +10239,19 @@
         <v>1</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -10277,19 +10277,19 @@
         <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -10315,10 +10315,10 @@
         <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
@@ -10327,7 +10327,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -10353,10 +10353,10 @@
         <v>2</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0</v>
@@ -10365,7 +10365,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -10391,10 +10391,10 @@
         <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -10429,19 +10429,19 @@
         <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -10467,10 +10467,10 @@
         <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>0</v>
@@ -10479,7 +10479,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -10505,10 +10505,10 @@
         <v>2</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -10517,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
@@ -10543,19 +10543,19 @@
         <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -10581,10 +10581,10 @@
         <v>2</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>0</v>
@@ -10593,7 +10593,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
@@ -10619,10 +10619,10 @@
         <v>2</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
@@ -10631,7 +10631,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -10657,19 +10657,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
@@ -10695,19 +10695,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -10733,19 +10733,19 @@
         <v>1</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
@@ -10771,19 +10771,19 @@
         <v>1</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -10809,19 +10809,19 @@
         <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
@@ -10847,10 +10847,10 @@
         <v>2</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -10885,19 +10885,19 @@
         <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
@@ -10923,10 +10923,10 @@
         <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>0</v>
@@ -10935,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -10961,19 +10961,19 @@
         <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
@@ -10999,10 +10999,10 @@
         <v>3</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>22717.5</v>
+        <v>22368</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="7" t="n">
-        <v>22717.5</v>
+        <v>22368</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -11037,19 +11037,19 @@
         <v>1</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
@@ -11075,19 +11075,19 @@
         <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -11113,19 +11113,19 @@
         <v>1</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
@@ -11151,10 +11151,10 @@
         <v>2</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -11189,19 +11189,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
@@ -11227,19 +11227,19 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -11265,10 +11265,10 @@
         <v>2</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
@@ -11277,7 +11277,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
@@ -11303,19 +11303,19 @@
         <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -11341,19 +11341,19 @@
         <v>1</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H74" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
@@ -11379,19 +11379,19 @@
         <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H75" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         <v>2</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>0</v>
@@ -11429,7 +11429,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
@@ -11455,19 +11455,19 @@
         <v>1</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -11493,19 +11493,19 @@
         <v>1</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H78" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
@@ -11531,19 +11531,19 @@
         <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -11569,10 +11569,10 @@
         <v>2</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>0</v>
@@ -11581,7 +11581,7 @@
         <v>0</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
@@ -11607,19 +11607,19 @@
         <v>1</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -11645,19 +11645,19 @@
         <v>1</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
@@ -11683,10 +11683,10 @@
         <v>2</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>0</v>
@@ -11695,7 +11695,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -11721,19 +11721,19 @@
         <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H84" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
@@ -11759,10 +11759,10 @@
         <v>2</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -11797,10 +11797,10 @@
         <v>2</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
@@ -11835,10 +11835,10 @@
         <v>2</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>0</v>
@@ -11847,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>15145</v>
+        <v>14912</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -11873,19 +11873,19 @@
         <v>1</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>11358.5</v>
+        <v>11184</v>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
@@ -11911,19 +11911,19 @@
         <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -11949,19 +11949,19 @@
         <v>1</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
@@ -11987,19 +11987,19 @@
         <v>1</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -12025,19 +12025,19 @@
         <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
@@ -12063,19 +12063,19 @@
         <v>1</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -12101,19 +12101,19 @@
         <v>1</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H94" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
@@ -12139,19 +12139,19 @@
         <v>1</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -12177,19 +12177,19 @@
         <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
@@ -12215,19 +12215,19 @@
         <v>1</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -12253,19 +12253,19 @@
         <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
@@ -12291,19 +12291,19 @@
         <v>1</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -12329,10 +12329,10 @@
         <v>2</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>0</v>
@@ -12341,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
@@ -12367,10 +12367,10 @@
         <v>2</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -12405,19 +12405,19 @@
         <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
@@ -12443,19 +12443,19 @@
         <v>1</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H103" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -12481,10 +12481,10 @@
         <v>2</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>0</v>
@@ -12493,7 +12493,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
@@ -12519,10 +12519,10 @@
         <v>2</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>0</v>
@@ -12531,7 +12531,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="7" t="n">
-        <v>14950</v>
+        <v>14720</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -12557,19 +12557,19 @@
         <v>1</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G106" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H106" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I106" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
@@ -12595,10 +12595,10 @@
         <v>3</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>22425</v>
+        <v>22080</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>22425</v>
+        <v>22080</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -12633,19 +12633,19 @@
         <v>1</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="G108" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="H108" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>11213</v>
+        <v>11040</v>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
@@ -12671,10 +12671,10 @@
         <v>2</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>0</v>
@@ -12683,7 +12683,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -12709,10 +12709,10 @@
         <v>2</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>0</v>
@@ -12721,7 +12721,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="6" t="n">
-        <v>14755</v>
+        <v>14528</v>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
@@ -12747,19 +12747,19 @@
         <v>1</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -12785,19 +12785,19 @@
         <v>1</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G112" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
@@ -12823,19 +12823,19 @@
         <v>1</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H113" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I113" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -12861,19 +12861,19 @@
         <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G114" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H114" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
@@ -12899,19 +12899,19 @@
         <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>11066.5</v>
+        <v>10896</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -13167,10 +13167,10 @@
         <v>1</v>
       </c>
       <c r="V2" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W2" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X2" s="6" t="n">
         <v>0</v>
@@ -13255,10 +13255,10 @@
         <v>1</v>
       </c>
       <c r="V3" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X3" s="7" t="n">
         <v>0</v>
@@ -13343,10 +13343,10 @@
         <v>1</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X4" s="6" t="n">
         <v>0</v>
@@ -13431,10 +13431,10 @@
         <v>1</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X5" s="7" t="n">
         <v>0</v>
@@ -13519,10 +13519,10 @@
         <v>1</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X6" s="6" t="n">
         <v>0</v>
@@ -13607,10 +13607,10 @@
         <v>1</v>
       </c>
       <c r="V7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X7" s="7" t="n">
         <v>0</v>
@@ -13695,10 +13695,10 @@
         <v>1</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="X8" s="6" t="n">
         <v>0</v>
@@ -13783,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="V9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>0</v>
@@ -13871,10 +13871,10 @@
         <v>1</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X10" s="6" t="n">
         <v>0</v>
@@ -13959,10 +13959,10 @@
         <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>0</v>
@@ -14047,10 +14047,10 @@
         <v>1</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X12" s="6" t="n">
         <v>0</v>
@@ -14135,10 +14135,10 @@
         <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
@@ -14223,10 +14223,10 @@
         <v>1</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X14" s="6" t="n">
         <v>0</v>
@@ -14311,7 +14311,7 @@
         <v>1</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W15" s="7" t="n">
         <v>0</v>
@@ -14399,10 +14399,10 @@
         <v>1</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X16" s="6" t="n">
         <v>0</v>
@@ -14487,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W17" s="7" t="n">
         <v>0</v>
@@ -14575,10 +14575,10 @@
         <v>1</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X18" s="6" t="n">
         <v>0</v>
@@ -14663,10 +14663,10 @@
         <v>1</v>
       </c>
       <c r="V19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>0</v>
@@ -14751,7 +14751,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W20" s="6" t="n">
         <v>0</v>
@@ -14839,7 +14839,7 @@
         <v>1</v>
       </c>
       <c r="V21" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W21" s="7" t="n">
         <v>0</v>
@@ -14927,10 +14927,10 @@
         <v>1</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X22" s="6" t="n">
         <v>0</v>
@@ -15015,7 +15015,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W23" s="7" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>1</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="X24" s="6" t="n">
         <v>0</v>
@@ -15191,7 +15191,7 @@
         <v>1</v>
       </c>
       <c r="V25" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W25" s="7" t="n">
         <v>0</v>
@@ -15279,7 +15279,7 @@
         <v>1</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W26" s="6" t="n">
         <v>0</v>
@@ -15367,7 +15367,7 @@
         <v>1</v>
       </c>
       <c r="V27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W27" s="7" t="n">
         <v>0</v>
@@ -15455,10 +15455,10 @@
         <v>1</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="X28" s="6" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>1</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>0</v>
@@ -15631,7 +15631,7 @@
         <v>1</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W30" s="6" t="n">
         <v>0</v>
@@ -15719,10 +15719,10 @@
         <v>1</v>
       </c>
       <c r="V31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="X31" s="7" t="n">
         <v>0</v>
@@ -15807,7 +15807,7 @@
         <v>1</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W32" s="6" t="n">
         <v>0</v>
@@ -15895,10 +15895,10 @@
         <v>1</v>
       </c>
       <c r="V33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="X33" s="7" t="n">
         <v>0</v>
@@ -15983,7 +15983,7 @@
         <v>1</v>
       </c>
       <c r="V34" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W34" s="6" t="n">
         <v>0</v>
@@ -16071,7 +16071,7 @@
         <v>1</v>
       </c>
       <c r="V35" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>1</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W36" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="X36" s="6" t="n">
         <v>0</v>
@@ -16247,7 +16247,7 @@
         <v>1</v>
       </c>
       <c r="V37" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W37" s="7" t="n">
         <v>0</v>
@@ -16335,7 +16335,7 @@
         <v>1</v>
       </c>
       <c r="V38" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W38" s="6" t="n">
         <v>0</v>
@@ -16423,7 +16423,7 @@
         <v>1</v>
       </c>
       <c r="V39" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W39" s="7" t="n">
         <v>0</v>
@@ -16511,7 +16511,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W40" s="6" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W41" s="7" t="n">
         <v>0</v>
@@ -16687,10 +16687,10 @@
         <v>1</v>
       </c>
       <c r="V42" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W42" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="X42" s="6" t="n">
         <v>0</v>
@@ -16775,7 +16775,7 @@
         <v>1</v>
       </c>
       <c r="V43" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W43" s="7" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W44" s="6" t="n">
         <v>0</v>
@@ -16951,7 +16951,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W45" s="7" t="n">
         <v>0</v>
@@ -17039,7 +17039,7 @@
         <v>1</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W46" s="6" t="n">
         <v>0</v>
@@ -17127,7 +17127,7 @@
         <v>1</v>
       </c>
       <c r="V47" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W47" s="7" t="n">
         <v>0</v>
@@ -17215,10 +17215,10 @@
         <v>1</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W48" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X48" s="6" t="n">
         <v>0</v>
@@ -17303,7 +17303,7 @@
         <v>1</v>
       </c>
       <c r="V49" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W49" s="7" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>1</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="W50" s="6" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W51" s="7" t="n">
         <v>0</v>
@@ -17571,7 +17571,7 @@
         <v>1</v>
       </c>
       <c r="V52" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W52" s="6" t="n">
         <v>0</v>
@@ -17659,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="V53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W53" s="7" t="n">
         <v>0</v>
@@ -17747,7 +17747,7 @@
         <v>1</v>
       </c>
       <c r="V54" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W54" s="6" t="n">
         <v>0</v>
@@ -17835,10 +17835,10 @@
         <v>1</v>
       </c>
       <c r="V55" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W55" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X55" s="7" t="n">
         <v>0</v>
@@ -17923,7 +17923,7 @@
         <v>1</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W56" s="6" t="n">
         <v>0</v>
@@ -18011,10 +18011,10 @@
         <v>1</v>
       </c>
       <c r="V57" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W57" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X57" s="7" t="n">
         <v>0</v>
@@ -18099,7 +18099,7 @@
         <v>1</v>
       </c>
       <c r="V58" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W58" s="6" t="n">
         <v>0</v>
@@ -18187,10 +18187,10 @@
         <v>1</v>
       </c>
       <c r="V59" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W59" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X59" s="7" t="n">
         <v>0</v>
@@ -18275,7 +18275,7 @@
         <v>1</v>
       </c>
       <c r="V60" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W60" s="6" t="n">
         <v>0</v>
@@ -18363,7 +18363,7 @@
         <v>1</v>
       </c>
       <c r="V61" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W61" s="7" t="n">
         <v>0</v>
@@ -18451,7 +18451,7 @@
         <v>1</v>
       </c>
       <c r="V62" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W62" s="6" t="n">
         <v>0</v>
@@ -18539,7 +18539,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W63" s="7" t="n">
         <v>0</v>
@@ -18627,10 +18627,10 @@
         <v>1</v>
       </c>
       <c r="V64" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W64" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X64" s="6" t="n">
         <v>0</v>
@@ -18715,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W65" s="7" t="n">
         <v>0</v>
@@ -18803,7 +18803,7 @@
         <v>1</v>
       </c>
       <c r="V66" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W66" s="6" t="n">
         <v>0</v>
@@ -18891,7 +18891,7 @@
         <v>1</v>
       </c>
       <c r="V67" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W67" s="7" t="n">
         <v>0</v>
@@ -18979,7 +18979,7 @@
         <v>1</v>
       </c>
       <c r="V68" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W68" s="6" t="n">
         <v>0</v>
@@ -19067,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="V69" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W69" s="7" t="n">
         <v>0</v>
@@ -19155,7 +19155,7 @@
         <v>1</v>
       </c>
       <c r="V70" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W70" s="6" t="n">
         <v>0</v>
@@ -19243,7 +19243,7 @@
         <v>1</v>
       </c>
       <c r="V71" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W71" s="7" t="n">
         <v>0</v>
@@ -19331,7 +19331,7 @@
         <v>1</v>
       </c>
       <c r="V72" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W72" s="6" t="n">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>1</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W73" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X73" s="7" t="n">
         <v>0</v>
@@ -19507,7 +19507,7 @@
         <v>1</v>
       </c>
       <c r="V74" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W74" s="6" t="n">
         <v>0</v>
@@ -19595,10 +19595,10 @@
         <v>1</v>
       </c>
       <c r="V75" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W75" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X75" s="7" t="n">
         <v>0</v>
@@ -19683,10 +19683,10 @@
         <v>1</v>
       </c>
       <c r="V76" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W76" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X76" s="6" t="n">
         <v>0</v>
@@ -19771,7 +19771,7 @@
         <v>1</v>
       </c>
       <c r="V77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W77" s="7" t="n">
         <v>0</v>
@@ -19859,10 +19859,10 @@
         <v>1</v>
       </c>
       <c r="V78" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W78" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X78" s="6" t="n">
         <v>0</v>
@@ -19947,7 +19947,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W79" s="7" t="n">
         <v>0</v>
@@ -20035,10 +20035,10 @@
         <v>1</v>
       </c>
       <c r="V80" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W80" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X80" s="6" t="n">
         <v>0</v>
@@ -20123,10 +20123,10 @@
         <v>1</v>
       </c>
       <c r="V81" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W81" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X81" s="7" t="n">
         <v>0</v>
@@ -20211,7 +20211,7 @@
         <v>1</v>
       </c>
       <c r="V82" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W82" s="6" t="n">
         <v>0</v>
@@ -20299,10 +20299,10 @@
         <v>1</v>
       </c>
       <c r="V83" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W83" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X83" s="7" t="n">
         <v>0</v>
@@ -20387,7 +20387,7 @@
         <v>1</v>
       </c>
       <c r="V84" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W84" s="6" t="n">
         <v>0</v>
@@ -20475,7 +20475,7 @@
         <v>1</v>
       </c>
       <c r="V85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W85" s="7" t="n">
         <v>0</v>
@@ -20563,10 +20563,10 @@
         <v>1</v>
       </c>
       <c r="V86" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W86" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X86" s="6" t="n">
         <v>0</v>
@@ -20651,7 +20651,7 @@
         <v>1</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W87" s="7" t="n">
         <v>0</v>
@@ -20739,10 +20739,10 @@
         <v>1</v>
       </c>
       <c r="V88" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W88" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X88" s="6" t="n">
         <v>0</v>
@@ -20827,7 +20827,7 @@
         <v>1</v>
       </c>
       <c r="V89" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W89" s="7" t="n">
         <v>0</v>
@@ -20915,7 +20915,7 @@
         <v>1</v>
       </c>
       <c r="V90" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W90" s="6" t="n">
         <v>0</v>
@@ -21003,7 +21003,7 @@
         <v>1</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W91" s="7" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
         <v>1</v>
       </c>
       <c r="V92" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W92" s="6" t="n">
         <v>0</v>
@@ -21179,10 +21179,10 @@
         <v>1</v>
       </c>
       <c r="V93" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W93" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X93" s="7" t="n">
         <v>0</v>
@@ -21267,10 +21267,10 @@
         <v>1</v>
       </c>
       <c r="V94" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W94" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X94" s="6" t="n">
         <v>0</v>
@@ -21355,10 +21355,10 @@
         <v>1</v>
       </c>
       <c r="V95" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W95" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X95" s="7" t="n">
         <v>0</v>
@@ -21443,7 +21443,7 @@
         <v>1</v>
       </c>
       <c r="V96" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W96" s="6" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>1</v>
       </c>
       <c r="V97" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W97" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X97" s="7" t="n">
         <v>0</v>
@@ -21619,10 +21619,10 @@
         <v>1</v>
       </c>
       <c r="V98" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W98" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X98" s="6" t="n">
         <v>0</v>
@@ -21707,10 +21707,10 @@
         <v>1</v>
       </c>
       <c r="V99" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W99" s="7" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="X99" s="7" t="n">
         <v>0</v>
@@ -21795,7 +21795,7 @@
         <v>1</v>
       </c>
       <c r="V100" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W100" s="6" t="n">
         <v>0</v>
@@ -21883,7 +21883,7 @@
         <v>1</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W101" s="7" t="n">
         <v>0</v>
@@ -21971,10 +21971,10 @@
         <v>1</v>
       </c>
       <c r="V102" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W102" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X102" s="6" t="n">
         <v>0</v>
@@ -22059,7 +22059,7 @@
         <v>1</v>
       </c>
       <c r="V103" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W103" s="7" t="n">
         <v>0</v>
@@ -22147,10 +22147,10 @@
         <v>1</v>
       </c>
       <c r="V104" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W104" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X104" s="6" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>1</v>
       </c>
       <c r="V105" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W105" s="7" t="n">
         <v>0</v>
@@ -22323,10 +22323,10 @@
         <v>1</v>
       </c>
       <c r="V106" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W106" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X106" s="6" t="n">
         <v>0</v>
@@ -22411,7 +22411,7 @@
         <v>1</v>
       </c>
       <c r="V107" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W107" s="7" t="n">
         <v>0</v>
@@ -22499,10 +22499,10 @@
         <v>1</v>
       </c>
       <c r="V108" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W108" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X108" s="6" t="n">
         <v>0</v>
@@ -22587,7 +22587,7 @@
         <v>1</v>
       </c>
       <c r="V109" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W109" s="7" t="n">
         <v>0</v>
@@ -22675,7 +22675,7 @@
         <v>1</v>
       </c>
       <c r="V110" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W110" s="6" t="n">
         <v>0</v>
@@ -22763,10 +22763,10 @@
         <v>1</v>
       </c>
       <c r="V111" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W111" s="7" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="X111" s="7" t="n">
         <v>0</v>
@@ -22851,7 +22851,7 @@
         <v>1</v>
       </c>
       <c r="V112" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W112" s="6" t="n">
         <v>0</v>
@@ -22939,7 +22939,7 @@
         <v>1</v>
       </c>
       <c r="V113" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W113" s="7" t="n">
         <v>0</v>
@@ -23027,7 +23027,7 @@
         <v>1</v>
       </c>
       <c r="V114" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W114" s="6" t="n">
         <v>0</v>
@@ -23115,7 +23115,7 @@
         <v>1</v>
       </c>
       <c r="V115" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W115" s="7" t="n">
         <v>0</v>
@@ -23203,7 +23203,7 @@
         <v>1</v>
       </c>
       <c r="V116" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W116" s="6" t="n">
         <v>0</v>
@@ -23291,10 +23291,10 @@
         <v>1</v>
       </c>
       <c r="V117" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W117" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="X117" s="7" t="n">
         <v>0</v>
@@ -23379,7 +23379,7 @@
         <v>1</v>
       </c>
       <c r="V118" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W118" s="6" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
         <v>1</v>
       </c>
       <c r="V119" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W119" s="7" t="n">
         <v>0</v>
@@ -23559,7 +23559,7 @@
         <v>1</v>
       </c>
       <c r="V120" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W120" s="6" t="n">
         <v>0</v>
@@ -23647,10 +23647,10 @@
         <v>1</v>
       </c>
       <c r="V121" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W121" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X121" s="7" t="n">
         <v>0</v>
@@ -23735,10 +23735,10 @@
         <v>1</v>
       </c>
       <c r="V122" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W122" s="6" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="X122" s="6" t="n">
         <v>0</v>
@@ -23823,7 +23823,7 @@
         <v>1</v>
       </c>
       <c r="V123" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W123" s="7" t="n">
         <v>0</v>
@@ -23911,10 +23911,10 @@
         <v>1</v>
       </c>
       <c r="V124" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="W124" s="6" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="X124" s="6" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="V125" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W125" s="7" t="n">
         <v>0</v>
@@ -24087,10 +24087,10 @@
         <v>1</v>
       </c>
       <c r="V126" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W126" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X126" s="6" t="n">
         <v>0</v>
@@ -24175,10 +24175,10 @@
         <v>1</v>
       </c>
       <c r="V127" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W127" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X127" s="7" t="n">
         <v>0</v>
@@ -24263,10 +24263,10 @@
         <v>1</v>
       </c>
       <c r="V128" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W128" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X128" s="6" t="n">
         <v>0</v>
@@ -24351,10 +24351,10 @@
         <v>1</v>
       </c>
       <c r="V129" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W129" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X129" s="7" t="n">
         <v>0</v>
@@ -24439,10 +24439,10 @@
         <v>1</v>
       </c>
       <c r="V130" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W130" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X130" s="6" t="n">
         <v>0</v>
@@ -24527,7 +24527,7 @@
         <v>1</v>
       </c>
       <c r="V131" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W131" s="7" t="n">
         <v>0</v>
@@ -24615,7 +24615,7 @@
         <v>1</v>
       </c>
       <c r="V132" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W132" s="6" t="n">
         <v>0</v>
@@ -24703,10 +24703,10 @@
         <v>1</v>
       </c>
       <c r="V133" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W133" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X133" s="7" t="n">
         <v>0</v>
@@ -24791,7 +24791,7 @@
         <v>1</v>
       </c>
       <c r="V134" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W134" s="6" t="n">
         <v>0</v>
@@ -24883,10 +24883,10 @@
         <v>1</v>
       </c>
       <c r="V135" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W135" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X135" s="7" t="n">
         <v>0</v>
@@ -24971,10 +24971,10 @@
         <v>1</v>
       </c>
       <c r="V136" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W136" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X136" s="6" t="n">
         <v>0</v>
@@ -25059,7 +25059,7 @@
         <v>1</v>
       </c>
       <c r="V137" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W137" s="7" t="n">
         <v>0</v>
@@ -25147,7 +25147,7 @@
         <v>1</v>
       </c>
       <c r="V138" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W138" s="6" t="n">
         <v>0</v>
@@ -25235,7 +25235,7 @@
         <v>1</v>
       </c>
       <c r="V139" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W139" s="7" t="n">
         <v>0</v>
@@ -25323,10 +25323,10 @@
         <v>1</v>
       </c>
       <c r="V140" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W140" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X140" s="6" t="n">
         <v>0</v>
@@ -25411,7 +25411,7 @@
         <v>1</v>
       </c>
       <c r="V141" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W141" s="7" t="n">
         <v>0</v>
@@ -25499,7 +25499,7 @@
         <v>1</v>
       </c>
       <c r="V142" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W142" s="6" t="n">
         <v>0</v>
@@ -25587,7 +25587,7 @@
         <v>1</v>
       </c>
       <c r="V143" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W143" s="7" t="n">
         <v>0</v>
@@ -25675,10 +25675,10 @@
         <v>1</v>
       </c>
       <c r="V144" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W144" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="X144" s="6" t="n">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>1</v>
       </c>
       <c r="V145" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W145" s="7" t="n">
         <v>0</v>
@@ -25855,7 +25855,7 @@
         <v>1</v>
       </c>
       <c r="V146" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W146" s="6" t="n">
         <v>0</v>
@@ -25943,7 +25943,7 @@
         <v>1</v>
       </c>
       <c r="V147" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W147" s="7" t="n">
         <v>0</v>
@@ -26031,10 +26031,10 @@
         <v>1</v>
       </c>
       <c r="V148" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W148" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X148" s="6" t="n">
         <v>0</v>
@@ -26119,7 +26119,7 @@
         <v>1</v>
       </c>
       <c r="V149" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="W149" s="7" t="n">
         <v>0</v>
@@ -26207,10 +26207,10 @@
         <v>1</v>
       </c>
       <c r="V150" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W150" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X150" s="6" t="n">
         <v>0</v>
@@ -26295,7 +26295,7 @@
         <v>1</v>
       </c>
       <c r="V151" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W151" s="7" t="n">
         <v>0</v>
@@ -26383,7 +26383,7 @@
         <v>1</v>
       </c>
       <c r="V152" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W152" s="6" t="n">
         <v>0</v>
@@ -26471,10 +26471,10 @@
         <v>1</v>
       </c>
       <c r="V153" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W153" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="X153" s="7" t="n">
         <v>0</v>
@@ -26559,10 +26559,10 @@
         <v>1</v>
       </c>
       <c r="V154" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W154" s="6" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="X154" s="6" t="n">
         <v>0</v>
@@ -26647,7 +26647,7 @@
         <v>1</v>
       </c>
       <c r="V155" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="W155" s="7" t="n">
         <v>0</v>
@@ -26733,10 +26733,10 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>0</v>
@@ -26758,10 +26758,10 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>0</v>
@@ -26783,10 +26783,10 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
@@ -26808,10 +26808,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -26833,10 +26833,10 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -26858,10 +26858,10 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -26883,10 +26883,10 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0</v>
@@ -26908,7 +26908,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -26933,10 +26933,10 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>0</v>
@@ -26958,10 +26958,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
@@ -26983,10 +26983,10 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -27008,10 +27008,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -27033,10 +27033,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
@@ -27058,7 +27058,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
@@ -27083,10 +27083,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>0</v>
@@ -27133,10 +27133,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -27158,10 +27158,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -27183,7 +27183,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0</v>
@@ -27208,7 +27208,7 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>0</v>
@@ -27233,10 +27233,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0</v>
@@ -27258,7 +27258,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>0</v>
@@ -27283,10 +27283,10 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>0</v>
@@ -27308,7 +27308,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
@@ -27333,7 +27333,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>0</v>
@@ -27358,7 +27358,7 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
@@ -27383,10 +27383,10 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>0</v>
@@ -27408,10 +27408,10 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>0</v>
@@ -27458,10 +27458,10 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -27483,7 +27483,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>0</v>
@@ -27508,10 +27508,10 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -27533,7 +27533,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>0</v>
@@ -27558,7 +27558,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -27583,10 +27583,10 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>0</v>
@@ -27608,7 +27608,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -27633,7 +27633,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0</v>
@@ -27658,7 +27658,7 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>0</v>
@@ -27683,7 +27683,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>0</v>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>0</v>
@@ -27733,10 +27733,10 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>0</v>
@@ -27758,7 +27758,7 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>0</v>
@@ -27808,7 +27808,7 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>0</v>
@@ -27833,7 +27833,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>0</v>
@@ -27858,7 +27858,7 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
@@ -27883,10 +27883,10 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>0</v>
@@ -27908,7 +27908,7 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>0</v>
@@ -27933,7 +27933,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>0</v>
@@ -27983,7 +27983,7 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D52" s="6" t="n">
         <v>0</v>
@@ -28008,7 +28008,7 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>0</v>
@@ -28033,7 +28033,7 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D54" s="6" t="n">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0</v>
@@ -28083,7 +28083,7 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D56" s="6" t="n">
         <v>0</v>
@@ -28108,10 +28108,10 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>0</v>
@@ -28133,7 +28133,7 @@
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D58" s="6" t="n">
         <v>0</v>
@@ -28158,10 +28158,10 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>0</v>
@@ -28183,7 +28183,7 @@
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>0</v>
@@ -28208,7 +28208,7 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>0</v>
@@ -28233,7 +28233,7 @@
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -28258,7 +28258,7 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>0</v>
@@ -28283,10 +28283,10 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>0</v>
@@ -28308,7 +28308,7 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D66" s="6" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>0</v>
@@ -28383,7 +28383,7 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>0</v>
@@ -28408,7 +28408,7 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>0</v>
@@ -28433,7 +28433,7 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -28458,7 +28458,7 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>0</v>
@@ -28483,7 +28483,7 @@
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D72" s="6" t="n">
         <v>0</v>
@@ -28508,10 +28508,10 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>0</v>
@@ -28533,7 +28533,7 @@
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>0</v>
@@ -28558,10 +28558,10 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E75" s="7" t="n">
         <v>0</v>
@@ -28583,10 +28583,10 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>0</v>
@@ -28608,7 +28608,7 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -28633,10 +28633,10 @@
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E78" s="6" t="n">
         <v>0</v>
@@ -28658,7 +28658,7 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>0</v>
@@ -28683,10 +28683,10 @@
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>0</v>
@@ -28708,10 +28708,10 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>0</v>
@@ -28733,7 +28733,7 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>0</v>
@@ -28758,10 +28758,10 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>0</v>
@@ -28783,7 +28783,7 @@
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D84" s="6" t="n">
         <v>0</v>
@@ -28808,7 +28808,7 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
@@ -28833,10 +28833,10 @@
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>0</v>
@@ -28858,7 +28858,7 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>0</v>
@@ -28883,10 +28883,10 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>0</v>
@@ -28908,7 +28908,7 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>0</v>
@@ -28933,7 +28933,7 @@
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D90" s="6" t="n">
         <v>0</v>
@@ -28958,7 +28958,7 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>0</v>
@@ -28983,7 +28983,7 @@
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D92" s="6" t="n">
         <v>0</v>
@@ -29008,10 +29008,10 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>0</v>
@@ -29033,10 +29033,10 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E94" s="6" t="n">
         <v>0</v>
@@ -29058,10 +29058,10 @@
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>0</v>
@@ -29083,7 +29083,7 @@
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>0</v>
@@ -29108,10 +29108,10 @@
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>0</v>
@@ -29133,10 +29133,10 @@
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E98" s="6" t="n">
         <v>0</v>
@@ -29158,10 +29158,10 @@
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D100" s="6" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D101" s="7" t="n">
         <v>0</v>
@@ -29233,10 +29233,10 @@
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E102" s="6" t="n">
         <v>0</v>
@@ -29258,7 +29258,7 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D103" s="7" t="n">
         <v>0</v>
@@ -29283,10 +29283,10 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E104" s="6" t="n">
         <v>0</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D105" s="7" t="n">
         <v>0</v>
@@ -29333,10 +29333,10 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E106" s="6" t="n">
         <v>0</v>
@@ -29358,7 +29358,7 @@
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D107" s="7" t="n">
         <v>0</v>
@@ -29383,10 +29383,10 @@
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E108" s="6" t="n">
         <v>0</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="C109" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D109" s="7" t="n">
         <v>0</v>
@@ -29433,7 +29433,7 @@
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D110" s="6" t="n">
         <v>0</v>
@@ -29458,10 +29458,10 @@
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>7572</v>
+        <v>7456</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>0</v>
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D112" s="6" t="n">
         <v>0</v>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="C113" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>0</v>
@@ -29533,7 +29533,7 @@
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D114" s="6" t="n">
         <v>0</v>
@@ -29558,7 +29558,7 @@
         </is>
       </c>
       <c r="C115" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>0</v>
@@ -29583,7 +29583,7 @@
         </is>
       </c>
       <c r="C116" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D116" s="6" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         </is>
       </c>
       <c r="C117" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>0</v>
@@ -29633,7 +29633,7 @@
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D118" s="6" t="n">
         <v>0</v>
@@ -29658,7 +29658,7 @@
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>0</v>
@@ -29683,7 +29683,7 @@
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D120" s="6" t="n">
         <v>0</v>
@@ -29708,10 +29708,10 @@
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E121" s="7" t="n">
         <v>0</v>
@@ -29733,10 +29733,10 @@
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="E122" s="6" t="n">
         <v>0</v>
@@ -29758,7 +29758,7 @@
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D123" s="7" t="n">
         <v>0</v>
@@ -29783,10 +29783,10 @@
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>7476</v>
+        <v>7360</v>
       </c>
       <c r="E124" s="6" t="n">
         <v>0</v>
@@ -29808,7 +29808,7 @@
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D125" s="7" t="n">
         <v>0</v>
@@ -29833,10 +29833,10 @@
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E126" s="6" t="n">
         <v>0</v>
@@ -29858,10 +29858,10 @@
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E127" s="7" t="n">
         <v>0</v>
@@ -29883,10 +29883,10 @@
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E128" s="6" t="n">
         <v>0</v>
@@ -29908,10 +29908,10 @@
         </is>
       </c>
       <c r="C129" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E129" s="7" t="n">
         <v>0</v>
@@ -29933,10 +29933,10 @@
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E130" s="6" t="n">
         <v>0</v>
@@ -29958,7 +29958,7 @@
         </is>
       </c>
       <c r="C131" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D131" s="7" t="n">
         <v>0</v>
@@ -29983,7 +29983,7 @@
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D132" s="6" t="n">
         <v>0</v>
@@ -30008,10 +30008,10 @@
         </is>
       </c>
       <c r="C133" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E133" s="7" t="n">
         <v>0</v>
@@ -30033,7 +30033,7 @@
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D134" s="6" t="n">
         <v>0</v>
@@ -30058,10 +30058,10 @@
         </is>
       </c>
       <c r="C135" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E135" s="7" t="n">
         <v>0</v>
@@ -30083,10 +30083,10 @@
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E136" s="6" t="n">
         <v>0</v>
@@ -30108,7 +30108,7 @@
         </is>
       </c>
       <c r="C137" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>0</v>
@@ -30133,7 +30133,7 @@
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D138" s="6" t="n">
         <v>0</v>
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D139" s="7" t="n">
         <v>0</v>
@@ -30183,10 +30183,10 @@
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E140" s="6" t="n">
         <v>0</v>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="C141" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D141" s="7" t="n">
         <v>0</v>
@@ -30233,7 +30233,7 @@
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D142" s="6" t="n">
         <v>0</v>
@@ -30258,7 +30258,7 @@
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>0</v>
@@ -30283,10 +30283,10 @@
         </is>
       </c>
       <c r="C144" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
       <c r="E144" s="6" t="n">
         <v>0</v>
@@ -30308,7 +30308,7 @@
         </is>
       </c>
       <c r="C145" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D145" s="7" t="n">
         <v>0</v>
@@ -30333,7 +30333,7 @@
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D146" s="6" t="n">
         <v>0</v>
@@ -30358,7 +30358,7 @@
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D147" s="7" t="n">
         <v>0</v>
@@ -30383,10 +30383,10 @@
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E148" s="6" t="n">
         <v>0</v>
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="C149" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="D149" s="7" t="n">
         <v>0</v>
@@ -30433,10 +30433,10 @@
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E150" s="6" t="n">
         <v>0</v>
@@ -30458,7 +30458,7 @@
         </is>
       </c>
       <c r="C151" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D151" s="7" t="n">
         <v>0</v>
@@ -30483,7 +30483,7 @@
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D152" s="6" t="n">
         <v>0</v>
@@ -30508,10 +30508,10 @@
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
@@ -30533,10 +30533,10 @@
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>7378</v>
+        <v>7264</v>
       </c>
       <c r="E154" s="6" t="n">
         <v>0</v>
@@ -30558,7 +30558,7 @@
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="D155" s="7" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>
@@ -14427,7 +14427,7 @@
         <v>3632</v>
       </c>
       <c r="X3" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y3" s="7" t="n">
         <v>0</v>
@@ -14515,7 +14515,7 @@
         <v>3632</v>
       </c>
       <c r="X4" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y4" s="6" t="n">
         <v>0</v>
@@ -14603,7 +14603,7 @@
         <v>3632</v>
       </c>
       <c r="X5" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y5" s="7" t="n">
         <v>0</v>
@@ -14691,7 +14691,7 @@
         <v>3632</v>
       </c>
       <c r="X6" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y6" s="6" t="n">
         <v>0</v>
@@ -15747,7 +15747,7 @@
         <v>3584</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="Y18" s="6" t="n">
         <v>0</v>
@@ -20591,7 +20591,7 @@
         <v>3680</v>
       </c>
       <c r="X73" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y73" s="7" t="n">
         <v>0</v>
@@ -25171,7 +25171,7 @@
         <v>3680</v>
       </c>
       <c r="X125" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y125" s="7" t="n">
         <v>0</v>
@@ -25347,7 +25347,7 @@
         <v>3680</v>
       </c>
       <c r="X127" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y127" s="7" t="n">
         <v>0</v>
@@ -25523,7 +25523,7 @@
         <v>3680</v>
       </c>
       <c r="X129" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y129" s="7" t="n">
         <v>0</v>
@@ -27930,7 +27930,7 @@
         <v>3632</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>3632</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0</v>
@@ -27980,7 +27980,7 @@
         <v>3632</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
@@ -28005,7 +28005,7 @@
         <v>3632</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0</v>
@@ -28305,7 +28305,7 @@
         <v>3584</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>0</v>
@@ -29680,7 +29680,7 @@
         <v>3680</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F73" s="7" t="n">
         <v>0</v>
@@ -30980,7 +30980,7 @@
         <v>3680</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F125" s="7" t="n">
         <v>0</v>
@@ -31030,7 +31030,7 @@
         <v>3680</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F127" s="7" t="n">
         <v>0</v>
@@ -31080,7 +31080,7 @@
         <v>3680</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F129" s="7" t="n">
         <v>0</v>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -36,7 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manual_Extra_Trips'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'NoWork_Outbound_50pct'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Phantom_Trip_Candidates'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Hints_DoubleOrigin'!$A$1:$D$1</definedName>
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:37</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3250</v>
+        <v>32690</v>
       </c>
     </row>
     <row r="16">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1469970</v>
+        <v>1499410</v>
       </c>
     </row>
   </sheetData>
@@ -923,10 +923,10 @@
         <v>3632</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="4">
@@ -1946,10 +1946,10 @@
         <v>3584</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="35">
@@ -2045,10 +2045,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>14336</v>
+        <v>17920</v>
       </c>
     </row>
     <row r="38">
@@ -3068,10 +3068,10 @@
         <v>3728</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="69">
@@ -3101,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="70">
@@ -3167,10 +3167,10 @@
         <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="72">
@@ -3233,10 +3233,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="74">
@@ -3497,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="82">
@@ -8587,13 +8587,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8636,8 +8636,152 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="9" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>3632</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ตีเปล่าไป P&amp;G 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3584</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>3584</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8853,7 +8997,7 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>3250</v>
+        <v>32690</v>
       </c>
     </row>
     <row r="4">
@@ -8913,7 +9057,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1469970</v>
+        <v>1499410</v>
       </c>
     </row>
   </sheetData>
@@ -9438,14 +9582,14 @@
         <v>3632</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
         </is>
       </c>
     </row>
@@ -10616,14 +10760,14 @@
         <v>3584</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -10730,14 +10874,14 @@
         <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>14336</v>
+        <v>17920</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -11908,14 +12052,14 @@
         <v>3728</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -11946,14 +12090,14 @@
         <v>0</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12022,14 +12166,14 @@
         <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12098,14 +12242,14 @@
         <v>0</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12402,14 +12546,14 @@
         <v>0</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -14345,7 +14489,7 @@
         <v>0</v>
       </c>
       <c r="Z2" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="3">
@@ -17249,7 +17393,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="36">
@@ -17601,7 +17745,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="40">
@@ -21477,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="Z83" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="84">
@@ -21565,7 +21709,7 @@
         <v>0</v>
       </c>
       <c r="Z84" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="85">
@@ -21917,7 +22061,7 @@
         <v>0</v>
       </c>
       <c r="Z88" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="89">
@@ -22093,7 +22237,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="91">
@@ -22885,7 +23029,7 @@
         <v>0</v>
       </c>
       <c r="Z99" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="100">
@@ -27911,7 +28055,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="3">
@@ -28736,7 +28880,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="36">
@@ -28836,7 +28980,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="40">
@@ -29936,7 +30080,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="84">
@@ -29961,7 +30105,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="85">
@@ -30061,7 +30205,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="89">
@@ -30111,7 +30255,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="91">
@@ -30336,7 +30480,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="100">

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:37</t>
+          <t>2026-06-08 18:47</t>
         </is>
       </c>
     </row>
@@ -9544,14 +9544,14 @@
         <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+0.00฿)</t>
+          <t>ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -25,18 +25,18 @@
     <sheet name="Hints_DoubleOrigin" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Customer_Trips_Per_Day'!$A$1:$C$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Audit_Log'!$A$1:$J$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$155</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trips_Pricing_All'!$A$1:$G$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trips_Pricing_All'!$A$1:$G$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched_Log'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Daily_Activity'!$A$1:$I$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Daily_Time_24h_Check'!$A$1:$M$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manual_Extra_Trips'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'NoWork_Outbound_50pct'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Phantom_Trip_Candidates'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Hints_DoubleOrigin'!$A$1:$D$1</definedName>
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:47</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1129408</v>
+        <v>1121952</v>
       </c>
     </row>
     <row r="14">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>32690</v>
+        <v>40146</v>
       </c>
     </row>
     <row r="16">
@@ -920,10 +920,10 @@
         <v>7264</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>14528</v>
@@ -3065,10 +3065,10 @@
         <v>7456</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3728</v>
+        <v>7456</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
         <v>14912</v>
@@ -3122,19 +3122,19 @@
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I70" s="6" t="n">
         <v>14912</v>
@@ -8587,7 +8587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -8740,17 +8740,17 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
@@ -8764,11 +8764,11 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -8776,12 +8776,48 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3728</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D10"/>
+  <autoFilter ref="A1:D12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8945,7 +8981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8982,7 +9018,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>1129408</v>
+        <v>1121952</v>
       </c>
     </row>
     <row r="3">
@@ -8993,75 +9029,90 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ค่าขนส่งขากลับ (manual_return_trips — ไม่เพิ่มจำนวน matched)</t>
+          <t>ค่าขนส่งขากลับ (manual_return_trips kind=backhaul — ไม่เพิ่มจำนวน matched)</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>32690</v>
+        <v>29058</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Rd</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
+          <t>ค่าตีเปล่า (manual_return_trips kind=deadhead — ไม่เพิ่มจำนวน matched)</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0</v>
+        <v>11088</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
+          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>337312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
+          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>337312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Grand (A+C+D+R)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Grand (A+C+D+R+Rd)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
         <v>1499410</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C7"/>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9311,7 +9362,7 @@
         <v>46162</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>5</v>
@@ -9579,17 +9630,17 @@
         <v>7264</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>14528</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
         </is>
       </c>
     </row>
@@ -12049,17 +12100,17 @@
         <v>7456</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3728</v>
+        <v>7456</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
         <v>14912</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับเพิ่ม 50% (base คิด ตีเปล่า+BH#1 = 1 เที่ยวแล้ว) (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12116,26 +12167,26 @@
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I70" s="6" t="n">
         <v>14912</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>ไม่เก็บ [override: exclude_50] — ตัด 1 เที่ยวว่าง(ตีเปล่า)ออกจาก base แล้ว → เหลือ 1 เที่ยว แต่ไม่เก็บ +50% (วันนั้นวิ่งจริง 2 เที่ยว) — คู่กับ remove_matched_trips ใน oatside_config.json | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -14241,7 +14292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z155"/>
+  <dimension ref="A1:Z154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14486,10 +14537,10 @@
         <v>0</v>
       </c>
       <c r="Y2" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="Z2" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -21618,10 +21669,10 @@
         <v>0</v>
       </c>
       <c r="Y83" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="Z83" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -21882,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="Y86" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="Z86" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="87">
@@ -21893,7 +21944,7 @@
         <v>46162</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="C87" s="9" t="n">
         <v>46162</v>
@@ -21905,56 +21956,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="I87" s="11" t="n">
-        <v>46162.82657407408</v>
+        <v>46161.7365625</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>46162.88215277778</v>
+        <v>46161.9807175926</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.33</v>
+        <v>5.86</v>
       </c>
       <c r="L87" s="11" t="n">
-        <v>46162.95986111111</v>
+        <v>46162.07633101852</v>
       </c>
       <c r="M87" s="11" t="n">
-        <v>46163.12930555556</v>
+        <v>46162.73322916667</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>4.07</v>
+        <v>15.77</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>4.07</v>
+        <v>15.77</v>
       </c>
       <c r="Q87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R87" s="2" t="n">
-        <v>7.27</v>
+        <v>23.92</v>
       </c>
       <c r="S87" s="2" t="n">
-        <v>7.27</v>
+        <v>23.92</v>
       </c>
       <c r="T87" s="2" t="n"/>
       <c r="U87" s="2" t="n">
@@ -21964,7 +22015,7 @@
         <v>7456</v>
       </c>
       <c r="W87" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X87" s="7" t="n">
         <v>0</v>
@@ -21973,7 +22024,7 @@
         <v>0</v>
       </c>
       <c r="Z87" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="88">
@@ -21988,61 +22039,61 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I88" s="10" t="n">
-        <v>46161.7365625</v>
+        <v>46161.87398148148</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>46161.9807175926</v>
+        <v>46162.10988425926</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>5.86</v>
+        <v>5.66</v>
       </c>
       <c r="L88" s="10" t="n">
-        <v>46162.07633101852</v>
+        <v>46162.1790625</v>
       </c>
       <c r="M88" s="10" t="n">
-        <v>46162.73322916667</v>
+        <v>46162.81619212963</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>15.77</v>
+        <v>15.29</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>15.77</v>
+        <v>15.29</v>
       </c>
       <c r="Q88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R88" s="5" t="n">
-        <v>23.92</v>
+        <v>22.61</v>
       </c>
       <c r="S88" s="5" t="n">
-        <v>23.92</v>
+        <v>22.61</v>
       </c>
       <c r="T88" s="5" t="n"/>
       <c r="U88" s="5" t="n">
@@ -22061,76 +22112,76 @@
         <v>0</v>
       </c>
       <c r="Z88" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="C89" s="9" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="I89" s="11" t="n">
-        <v>46161.87398148148</v>
+        <v>46163.30872685185</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>46162.10988425926</v>
+        <v>46163.44234953704</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>5.66</v>
+        <v>3.21</v>
       </c>
       <c r="L89" s="11" t="n">
-        <v>46162.1790625</v>
+        <v>46163.52873842593</v>
       </c>
       <c r="M89" s="11" t="n">
-        <v>46162.81619212963</v>
+        <v>46163.65899305556</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>1.66</v>
+        <v>2.07</v>
       </c>
       <c r="O89" s="2" t="n">
-        <v>15.29</v>
+        <v>3.13</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>15.29</v>
+        <v>3.13</v>
       </c>
       <c r="Q89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R89" s="2" t="n">
-        <v>22.61</v>
+        <v>8.41</v>
       </c>
       <c r="S89" s="2" t="n">
-        <v>22.61</v>
+        <v>8.41</v>
       </c>
       <c r="T89" s="2" t="n"/>
       <c r="U89" s="2" t="n">
@@ -22140,16 +22191,16 @@
         <v>7456</v>
       </c>
       <c r="W89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="7" t="n">
         <v>3728</v>
-      </c>
-      <c r="X89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -22179,46 +22230,46 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="I90" s="10" t="n">
-        <v>46163.30872685185</v>
+        <v>46163.74399305556</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>46163.44234953704</v>
+        <v>46163.8228125</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>3.21</v>
+        <v>1.89</v>
       </c>
       <c r="L90" s="10" t="n">
-        <v>46163.52873842593</v>
+        <v>46163.93035879629</v>
       </c>
       <c r="M90" s="10" t="n">
-        <v>46163.65899305556</v>
+        <v>46164.02392361111</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>2.07</v>
+        <v>2.58</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>3.13</v>
+        <v>2.25</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>3.13</v>
+        <v>2.25</v>
       </c>
       <c r="Q90" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R90" s="5" t="n">
-        <v>8.41</v>
+        <v>6.72</v>
       </c>
       <c r="S90" s="5" t="n">
-        <v>8.41</v>
+        <v>6.72</v>
       </c>
       <c r="T90" s="5" t="n"/>
       <c r="U90" s="5" t="n">
@@ -22237,7 +22288,7 @@
         <v>0</v>
       </c>
       <c r="Z90" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -22245,7 +22296,7 @@
         <v>46163</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="C91" s="9" t="n">
         <v>46163</v>
@@ -22257,56 +22308,56 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="I91" s="11" t="n">
-        <v>46163.74399305556</v>
+        <v>46162.90394675926</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>46163.8228125</v>
+        <v>46163.22884259259</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.89</v>
+        <v>7.8</v>
       </c>
       <c r="L91" s="11" t="n">
-        <v>46163.93035879629</v>
+        <v>46163.36399305556</v>
       </c>
       <c r="M91" s="11" t="n">
-        <v>46164.02392361111</v>
+        <v>46163.43064814815</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>2.58</v>
+        <v>3.24</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R91" s="2" t="n">
-        <v>6.72</v>
+        <v>12.64</v>
       </c>
       <c r="S91" s="2" t="n">
-        <v>6.72</v>
+        <v>12.64</v>
       </c>
       <c r="T91" s="2" t="n"/>
       <c r="U91" s="2" t="n">
@@ -22316,7 +22367,7 @@
         <v>7456</v>
       </c>
       <c r="W91" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X91" s="7" t="n">
         <v>0</v>
@@ -22333,7 +22384,7 @@
         <v>46163</v>
       </c>
       <c r="B92" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C92" s="8" t="n">
         <v>46163</v>
@@ -22345,56 +22396,56 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="I92" s="10" t="n">
-        <v>46162.90394675926</v>
+        <v>46163.28854166667</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>46163.22884259259</v>
+        <v>46163.53840277778</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="L92" s="10" t="n">
-        <v>46163.36399305556</v>
+        <v>46163.66119212963</v>
       </c>
       <c r="M92" s="10" t="n">
-        <v>46163.43064814815</v>
+        <v>46163.89697916667</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>1.6</v>
+        <v>5.66</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>1.6</v>
+        <v>5.66</v>
       </c>
       <c r="Q92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R92" s="5" t="n">
-        <v>12.64</v>
+        <v>14.6</v>
       </c>
       <c r="S92" s="5" t="n">
-        <v>12.64</v>
+        <v>14.6</v>
       </c>
       <c r="T92" s="5" t="n"/>
       <c r="U92" s="5" t="n">
@@ -22421,7 +22472,7 @@
         <v>46163</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="C93" s="9" t="n">
         <v>46163</v>
@@ -22433,56 +22484,56 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="I93" s="11" t="n">
-        <v>46163.28854166667</v>
+        <v>46162.81313657408</v>
       </c>
       <c r="J93" s="11" t="n">
-        <v>46163.53840277778</v>
+        <v>46162.96394675926</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="L93" s="11" t="n">
-        <v>46163.66119212963</v>
+        <v>46163.05145833334</v>
       </c>
       <c r="M93" s="11" t="n">
-        <v>46163.89697916667</v>
+        <v>46163.60020833334</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>5.66</v>
+        <v>13.17</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>5.66</v>
+        <v>13.17</v>
       </c>
       <c r="Q93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R93" s="2" t="n">
-        <v>14.6</v>
+        <v>18.89</v>
       </c>
       <c r="S93" s="2" t="n">
-        <v>14.6</v>
+        <v>18.89</v>
       </c>
       <c r="T93" s="2" t="n"/>
       <c r="U93" s="2" t="n">
@@ -22516,61 +22567,61 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="I94" s="10" t="n">
-        <v>46162.81313657408</v>
+        <v>46162.88491898148</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>46162.96394675926</v>
+        <v>46163.71251157407</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>3.62</v>
+        <v>19.86</v>
       </c>
       <c r="L94" s="10" t="n">
-        <v>46163.05145833334</v>
+        <v>46163.81291666667</v>
       </c>
       <c r="M94" s="10" t="n">
-        <v>46163.60020833334</v>
+        <v>46164.01258101852</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>13.17</v>
+        <v>4.79</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>13.17</v>
+        <v>4.79</v>
       </c>
       <c r="Q94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R94" s="5" t="n">
-        <v>18.89</v>
+        <v>27.06</v>
       </c>
       <c r="S94" s="5" t="n">
-        <v>18.89</v>
+        <v>27.06</v>
       </c>
       <c r="T94" s="5" t="n"/>
       <c r="U94" s="5" t="n">
@@ -22594,71 +22645,71 @@
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C95" s="9" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="I95" s="11" t="n">
-        <v>46162.88491898148</v>
+        <v>46164.38288194445</v>
       </c>
       <c r="J95" s="11" t="n">
-        <v>46163.71251157407</v>
+        <v>46164.46175925926</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>19.86</v>
+        <v>1.89</v>
       </c>
       <c r="L95" s="11" t="n">
-        <v>46163.81291666667</v>
+        <v>46164.67049768518</v>
       </c>
       <c r="M95" s="11" t="n">
-        <v>46164.01258101852</v>
+        <v>46164.77396990741</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>2.41</v>
+        <v>5.01</v>
       </c>
       <c r="O95" s="2" t="n">
-        <v>4.79</v>
+        <v>2.48</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>4.79</v>
+        <v>2.48</v>
       </c>
       <c r="Q95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R95" s="2" t="n">
-        <v>27.06</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="S95" s="2" t="n">
-        <v>27.06</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="T95" s="2" t="n"/>
       <c r="U95" s="2" t="n">
@@ -22697,56 +22748,56 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="I96" s="10" t="n">
-        <v>46164.38288194445</v>
+        <v>46164.60027777778</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>46164.46175925926</v>
+        <v>46164.77232638889</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>1.89</v>
+        <v>4.13</v>
       </c>
       <c r="L96" s="10" t="n">
-        <v>46164.67049768518</v>
+        <v>46164.87579861111</v>
       </c>
       <c r="M96" s="10" t="n">
-        <v>46164.77396990741</v>
+        <v>46165.00855324074</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>5.01</v>
+        <v>2.48</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="Q96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R96" s="5" t="n">
-        <v>9.390000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S96" s="5" t="n">
-        <v>9.390000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T96" s="5" t="n"/>
       <c r="U96" s="5" t="n">
@@ -22785,56 +22836,56 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="I97" s="11" t="n">
-        <v>46164.60027777778</v>
+        <v>46164.23960648148</v>
       </c>
       <c r="J97" s="11" t="n">
-        <v>46164.77232638889</v>
+        <v>46164.39332175926</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>4.13</v>
+        <v>3.69</v>
       </c>
       <c r="L97" s="11" t="n">
-        <v>46164.87579861111</v>
+        <v>46164.48960648148</v>
       </c>
       <c r="M97" s="11" t="n">
-        <v>46165.00855324074</v>
+        <v>46164.76618055555</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>3.19</v>
+        <v>6.64</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>3.19</v>
+        <v>6.64</v>
       </c>
       <c r="Q97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R97" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>12.64</v>
       </c>
       <c r="S97" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>12.64</v>
       </c>
       <c r="T97" s="2" t="n"/>
       <c r="U97" s="2" t="n">
@@ -22861,7 +22912,7 @@
         <v>46164</v>
       </c>
       <c r="B98" s="8" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="C98" s="8" t="n">
         <v>46164</v>
@@ -22873,56 +22924,56 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="I98" s="10" t="n">
-        <v>46164.23960648148</v>
+        <v>46163.80703703704</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>46164.39332175926</v>
+        <v>46163.98831018519</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>3.69</v>
+        <v>4.35</v>
       </c>
       <c r="L98" s="10" t="n">
-        <v>46164.48960648148</v>
+        <v>46164.06736111111</v>
       </c>
       <c r="M98" s="10" t="n">
-        <v>46164.76618055555</v>
+        <v>46164.46622685185</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>6.64</v>
+        <v>9.57</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>6.64</v>
+        <v>9.57</v>
       </c>
       <c r="Q98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R98" s="5" t="n">
-        <v>12.64</v>
+        <v>15.82</v>
       </c>
       <c r="S98" s="5" t="n">
-        <v>12.64</v>
+        <v>15.82</v>
       </c>
       <c r="T98" s="5" t="n"/>
       <c r="U98" s="5" t="n">
@@ -22932,16 +22983,16 @@
         <v>7456</v>
       </c>
       <c r="W98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="6" t="n">
         <v>3728</v>
-      </c>
-      <c r="X98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z98" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -22949,7 +23000,7 @@
         <v>46164</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C99" s="9" t="n">
         <v>46164</v>
@@ -22971,46 +23022,46 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="I99" s="11" t="n">
-        <v>46163.80703703704</v>
+        <v>46164.53945601852</v>
       </c>
       <c r="J99" s="11" t="n">
-        <v>46163.98831018519</v>
+        <v>46164.71108796296</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>4.35</v>
+        <v>4.12</v>
       </c>
       <c r="L99" s="11" t="n">
-        <v>46164.06736111111</v>
+        <v>46164.80984953704</v>
       </c>
       <c r="M99" s="11" t="n">
-        <v>46164.46622685185</v>
+        <v>46164.98965277777</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="O99" s="2" t="n">
-        <v>9.57</v>
+        <v>4.32</v>
       </c>
       <c r="P99" s="2" t="n">
-        <v>9.57</v>
+        <v>4.32</v>
       </c>
       <c r="Q99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R99" s="2" t="n">
-        <v>15.82</v>
+        <v>10.8</v>
       </c>
       <c r="S99" s="2" t="n">
-        <v>15.82</v>
+        <v>10.8</v>
       </c>
       <c r="T99" s="2" t="n"/>
       <c r="U99" s="2" t="n">
@@ -23029,7 +23080,7 @@
         <v>0</v>
       </c>
       <c r="Z99" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -23044,61 +23095,61 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I100" s="10" t="n">
-        <v>46164.53945601852</v>
+        <v>46164.079375</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>46164.71108796296</v>
+        <v>46164.15428240741</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>4.12</v>
+        <v>1.8</v>
       </c>
       <c r="L100" s="10" t="n">
-        <v>46164.80984953704</v>
+        <v>46164.22637731482</v>
       </c>
       <c r="M100" s="10" t="n">
-        <v>46164.98965277777</v>
+        <v>46164.61162037037</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>4.32</v>
+        <v>9.25</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>4.32</v>
+        <v>9.25</v>
       </c>
       <c r="Q100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R100" s="5" t="n">
-        <v>10.8</v>
+        <v>12.77</v>
       </c>
       <c r="S100" s="5" t="n">
-        <v>10.8</v>
+        <v>12.77</v>
       </c>
       <c r="T100" s="5" t="n"/>
       <c r="U100" s="5" t="n">
@@ -23108,7 +23159,7 @@
         <v>7456</v>
       </c>
       <c r="W100" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X100" s="6" t="n">
         <v>0</v>
@@ -23122,71 +23173,71 @@
     </row>
     <row r="101">
       <c r="A101" s="9" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B101" s="9" t="n">
         <v>46164</v>
       </c>
       <c r="C101" s="9" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="I101" s="11" t="n">
-        <v>46164.079375</v>
+        <v>46164.87059027778</v>
       </c>
       <c r="J101" s="11" t="n">
-        <v>46164.15428240741</v>
+        <v>46165.14693287037</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.8</v>
+        <v>6.63</v>
       </c>
       <c r="L101" s="11" t="n">
-        <v>46164.22637731482</v>
+        <v>46165.22105324074</v>
       </c>
       <c r="M101" s="11" t="n">
-        <v>46164.61162037037</v>
+        <v>46165.45586805556</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>9.25</v>
+        <v>5.64</v>
       </c>
       <c r="P101" s="2" t="n">
-        <v>9.25</v>
+        <v>5.64</v>
       </c>
       <c r="Q101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R101" s="2" t="n">
-        <v>12.77</v>
+        <v>14.05</v>
       </c>
       <c r="S101" s="2" t="n">
-        <v>12.77</v>
+        <v>14.05</v>
       </c>
       <c r="T101" s="2" t="n"/>
       <c r="U101" s="2" t="n">
@@ -23196,7 +23247,7 @@
         <v>7456</v>
       </c>
       <c r="W101" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X101" s="7" t="n">
         <v>0</v>
@@ -23213,7 +23264,7 @@
         <v>46165</v>
       </c>
       <c r="B102" s="8" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="C102" s="8" t="n">
         <v>46165</v>
@@ -23235,46 +23286,46 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="I102" s="10" t="n">
-        <v>46164.87059027778</v>
+        <v>46165.62391203704</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>46165.14693287037</v>
+        <v>46165.71038194445</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>6.63</v>
+        <v>2.08</v>
       </c>
       <c r="L102" s="10" t="n">
-        <v>46165.22105324074</v>
+        <v>46165.80432870371</v>
       </c>
       <c r="M102" s="10" t="n">
-        <v>46165.45586805556</v>
+        <v>46166.12329861111</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>5.64</v>
+        <v>7.66</v>
       </c>
       <c r="P102" s="5" t="n">
-        <v>5.64</v>
+        <v>7.66</v>
       </c>
       <c r="Q102" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R102" s="5" t="n">
-        <v>14.05</v>
+        <v>11.99</v>
       </c>
       <c r="S102" s="5" t="n">
-        <v>14.05</v>
+        <v>11.99</v>
       </c>
       <c r="T102" s="5" t="n"/>
       <c r="U102" s="5" t="n">
@@ -23313,56 +23364,56 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="I103" s="11" t="n">
-        <v>46165.62391203704</v>
+        <v>46165.28190972222</v>
       </c>
       <c r="J103" s="11" t="n">
-        <v>46165.71038194445</v>
+        <v>46165.42890046296</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2.08</v>
+        <v>3.53</v>
       </c>
       <c r="L103" s="11" t="n">
-        <v>46165.80432870371</v>
+        <v>46165.49708333334</v>
       </c>
       <c r="M103" s="11" t="n">
-        <v>46166.12329861111</v>
+        <v>46165.93899305556</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="O103" s="2" t="n">
-        <v>7.66</v>
+        <v>10.61</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>7.66</v>
+        <v>10.61</v>
       </c>
       <c r="Q103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R103" s="2" t="n">
-        <v>11.99</v>
+        <v>15.77</v>
       </c>
       <c r="S103" s="2" t="n">
-        <v>11.99</v>
+        <v>15.77</v>
       </c>
       <c r="T103" s="2" t="n"/>
       <c r="U103" s="2" t="n">
@@ -23372,7 +23423,7 @@
         <v>7456</v>
       </c>
       <c r="W103" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X103" s="7" t="n">
         <v>0</v>
@@ -23401,56 +23452,56 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="I104" s="10" t="n">
-        <v>46165.28190972222</v>
+        <v>46165.085</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>46165.42890046296</v>
+        <v>46165.3</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>3.53</v>
+        <v>5.16</v>
       </c>
       <c r="L104" s="10" t="n">
-        <v>46165.49708333334</v>
+        <v>46165.36947916666</v>
       </c>
       <c r="M104" s="10" t="n">
-        <v>46165.93899305556</v>
+        <v>46165.67659722222</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>10.61</v>
+        <v>7.37</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>10.61</v>
+        <v>7.37</v>
       </c>
       <c r="Q104" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R104" s="5" t="n">
-        <v>15.77</v>
+        <v>14.2</v>
       </c>
       <c r="S104" s="5" t="n">
-        <v>15.77</v>
+        <v>14.2</v>
       </c>
       <c r="T104" s="5" t="n"/>
       <c r="U104" s="5" t="n">
@@ -23477,68 +23528,68 @@
         <v>46165</v>
       </c>
       <c r="B105" s="9" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="C105" s="9" t="n">
         <v>46165</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="I105" s="11" t="n">
-        <v>46165.085</v>
+        <v>46164.68181712963</v>
       </c>
       <c r="J105" s="11" t="n">
-        <v>46165.3</v>
+        <v>46165.11505787037</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>5.16</v>
+        <v>10.4</v>
       </c>
       <c r="L105" s="11" t="n">
-        <v>46165.36947916666</v>
+        <v>46165.22395833334</v>
       </c>
       <c r="M105" s="11" t="n">
-        <v>46165.67659722222</v>
+        <v>46165.57903935185</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>1.67</v>
+        <v>2.61</v>
       </c>
       <c r="O105" s="2" t="n">
-        <v>7.37</v>
+        <v>8.52</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>7.37</v>
+        <v>8.52</v>
       </c>
       <c r="Q105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R105" s="2" t="n">
-        <v>14.2</v>
+        <v>21.53</v>
       </c>
       <c r="S105" s="2" t="n">
-        <v>14.2</v>
+        <v>21.53</v>
       </c>
       <c r="T105" s="2" t="n"/>
       <c r="U105" s="2" t="n">
@@ -23562,10 +23613,10 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B106" s="8" t="n">
         <v>46165</v>
-      </c>
-      <c r="B106" s="8" t="n">
-        <v>46164</v>
       </c>
       <c r="C106" s="8" t="n">
         <v>46165</v>
@@ -23587,46 +23638,46 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
           <t>2.31</t>
         </is>
       </c>
-      <c r="H106" s="5" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
       <c r="I106" s="10" t="n">
-        <v>46164.68181712963</v>
+        <v>46165.6528587963</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>46165.11505787037</v>
+        <v>46165.92780092593</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>10.4</v>
+        <v>6.6</v>
       </c>
       <c r="L106" s="10" t="n">
-        <v>46165.22395833334</v>
+        <v>46165.9957175926</v>
       </c>
       <c r="M106" s="10" t="n">
-        <v>46165.57903935185</v>
+        <v>46166.38497685185</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>2.61</v>
+        <v>1.63</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>8.52</v>
+        <v>9.34</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>8.52</v>
+        <v>9.34</v>
       </c>
       <c r="Q106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R106" s="5" t="n">
-        <v>21.53</v>
+        <v>17.57</v>
       </c>
       <c r="S106" s="5" t="n">
-        <v>21.53</v>
+        <v>17.57</v>
       </c>
       <c r="T106" s="5" t="n"/>
       <c r="U106" s="5" t="n">
@@ -23636,7 +23687,7 @@
         <v>7456</v>
       </c>
       <c r="W106" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X106" s="6" t="n">
         <v>0</v>
@@ -23653,68 +23704,68 @@
         <v>46166</v>
       </c>
       <c r="B107" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C107" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="I107" s="11" t="n">
-        <v>46165.6528587963</v>
+        <v>46166.1890625</v>
       </c>
       <c r="J107" s="11" t="n">
-        <v>46165.92780092593</v>
+        <v>46166.41642361111</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>6.6</v>
+        <v>5.46</v>
       </c>
       <c r="L107" s="11" t="n">
-        <v>46165.9957175926</v>
+        <v>46166.48547453704</v>
       </c>
       <c r="M107" s="11" t="n">
-        <v>46166.38497685185</v>
+        <v>46166.63261574074</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>9.34</v>
+        <v>3.53</v>
       </c>
       <c r="P107" s="2" t="n">
-        <v>9.34</v>
+        <v>3.53</v>
       </c>
       <c r="Q107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R107" s="2" t="n">
-        <v>17.57</v>
+        <v>10.65</v>
       </c>
       <c r="S107" s="2" t="n">
-        <v>17.57</v>
+        <v>10.65</v>
       </c>
       <c r="T107" s="2" t="n"/>
       <c r="U107" s="2" t="n">
@@ -23724,7 +23775,7 @@
         <v>7456</v>
       </c>
       <c r="W107" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X107" s="7" t="n">
         <v>0</v>
@@ -23753,56 +23804,56 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="I108" s="10" t="n">
-        <v>46166.1890625</v>
+        <v>46166.01222222222</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>46166.41642361111</v>
+        <v>46166.27747685185</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>5.46</v>
+        <v>6.37</v>
       </c>
       <c r="L108" s="10" t="n">
-        <v>46166.48547453704</v>
+        <v>46166.34541666666</v>
       </c>
       <c r="M108" s="10" t="n">
-        <v>46166.63261574074</v>
+        <v>46166.42417824074</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>3.53</v>
+        <v>1.89</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>3.53</v>
+        <v>1.89</v>
       </c>
       <c r="Q108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R108" s="5" t="n">
-        <v>10.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S108" s="5" t="n">
-        <v>10.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="T108" s="5" t="n"/>
       <c r="U108" s="5" t="n">
@@ -23812,7 +23863,7 @@
         <v>7456</v>
       </c>
       <c r="W108" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X108" s="6" t="n">
         <v>0</v>
@@ -23851,46 +23902,46 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="I109" s="11" t="n">
-        <v>46166.01222222222</v>
+        <v>46166.50324074074</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>46166.27747685185</v>
+        <v>46166.72085648148</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>6.37</v>
+        <v>5.22</v>
       </c>
       <c r="L109" s="11" t="n">
-        <v>46166.34541666666</v>
+        <v>46166.81292824074</v>
       </c>
       <c r="M109" s="11" t="n">
-        <v>46166.42417824074</v>
+        <v>46166.92396990741</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="O109" s="2" t="n">
-        <v>1.89</v>
+        <v>2.67</v>
       </c>
       <c r="P109" s="2" t="n">
-        <v>1.89</v>
+        <v>2.67</v>
       </c>
       <c r="Q109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R109" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="S109" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="T109" s="2" t="n"/>
       <c r="U109" s="2" t="n">
@@ -23914,10 +23965,10 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="B110" s="8" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="C110" s="8" t="n">
         <v>46166</v>
@@ -23929,56 +23980,56 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="I110" s="10" t="n">
-        <v>46166.50324074074</v>
+        <v>46165.97453703704</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>46166.72085648148</v>
+        <v>46165.97988425926</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>5.22</v>
+        <v>0.13</v>
       </c>
       <c r="L110" s="10" t="n">
-        <v>46166.81292824074</v>
+        <v>46166.05300925926</v>
       </c>
       <c r="M110" s="10" t="n">
-        <v>46166.92396990741</v>
+        <v>46166.17</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="Q110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R110" s="5" t="n">
-        <v>10.1</v>
+        <v>4.69</v>
       </c>
       <c r="S110" s="5" t="n">
-        <v>10.1</v>
+        <v>4.69</v>
       </c>
       <c r="T110" s="5" t="n"/>
       <c r="U110" s="5" t="n">
@@ -23988,7 +24039,7 @@
         <v>7456</v>
       </c>
       <c r="W110" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X110" s="6" t="n">
         <v>0</v>
@@ -24002,10 +24053,10 @@
     </row>
     <row r="111">
       <c r="A111" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B111" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C111" s="9" t="n">
         <v>46166</v>
@@ -24027,46 +24078,46 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="I111" s="11" t="n">
-        <v>46165.97453703704</v>
+        <v>46166.34086805556</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>46165.97988425926</v>
+        <v>46166.50527777777</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.13</v>
+        <v>3.95</v>
       </c>
       <c r="L111" s="11" t="n">
-        <v>46166.05300925926</v>
+        <v>46166.61885416666</v>
       </c>
       <c r="M111" s="11" t="n">
-        <v>46166.17</v>
+        <v>46166.65587962963</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>1.75</v>
+        <v>2.73</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>2.81</v>
+        <v>0.89</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>2.81</v>
+        <v>0.89</v>
       </c>
       <c r="Q111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R111" s="2" t="n">
-        <v>4.69</v>
+        <v>7.56</v>
       </c>
       <c r="S111" s="2" t="n">
-        <v>4.69</v>
+        <v>7.56</v>
       </c>
       <c r="T111" s="2" t="n"/>
       <c r="U111" s="2" t="n">
@@ -24093,7 +24144,7 @@
         <v>46166</v>
       </c>
       <c r="B112" s="8" t="n">
-        <v>46166</v>
+        <v>46165</v>
       </c>
       <c r="C112" s="8" t="n">
         <v>46166</v>
@@ -24105,56 +24156,56 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I112" s="10" t="n">
-        <v>46166.34086805556</v>
+        <v>46165.76631944445</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>46166.50527777777</v>
+        <v>46166.12497685185</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>3.95</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L112" s="10" t="n">
-        <v>46166.61885416666</v>
+        <v>46166.20672453703</v>
       </c>
       <c r="M112" s="10" t="n">
-        <v>46166.65587962963</v>
+        <v>46166.40715277778</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>2.73</v>
+        <v>1.96</v>
       </c>
       <c r="O112" s="5" t="n">
-        <v>0.89</v>
+        <v>4.81</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.89</v>
+        <v>4.81</v>
       </c>
       <c r="Q112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R112" s="5" t="n">
-        <v>7.56</v>
+        <v>15.38</v>
       </c>
       <c r="S112" s="5" t="n">
-        <v>7.56</v>
+        <v>15.38</v>
       </c>
       <c r="T112" s="5" t="n"/>
       <c r="U112" s="5" t="n">
@@ -24164,7 +24215,7 @@
         <v>7456</v>
       </c>
       <c r="W112" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X112" s="6" t="n">
         <v>0</v>
@@ -24181,7 +24232,7 @@
         <v>46166</v>
       </c>
       <c r="B113" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C113" s="9" t="n">
         <v>46166</v>
@@ -24203,46 +24254,46 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="I113" s="11" t="n">
-        <v>46165.76631944445</v>
+        <v>46166.49901620371</v>
       </c>
       <c r="J113" s="11" t="n">
-        <v>46166.12497685185</v>
+        <v>46166.6827662037</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>8.609999999999999</v>
+        <v>4.41</v>
       </c>
       <c r="L113" s="11" t="n">
-        <v>46166.20672453703</v>
+        <v>46166.75684027778</v>
       </c>
       <c r="M113" s="11" t="n">
-        <v>46166.40715277778</v>
+        <v>46166.78159722222</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>4.81</v>
+        <v>0.59</v>
       </c>
       <c r="P113" s="2" t="n">
-        <v>4.81</v>
+        <v>0.59</v>
       </c>
       <c r="Q113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R113" s="2" t="n">
-        <v>15.38</v>
+        <v>6.78</v>
       </c>
       <c r="S113" s="2" t="n">
-        <v>15.38</v>
+        <v>6.78</v>
       </c>
       <c r="T113" s="2" t="n"/>
       <c r="U113" s="2" t="n">
@@ -24276,61 +24327,61 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I114" s="10" t="n">
-        <v>46166.49901620371</v>
+        <v>46166.45078703704</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>46166.6827662037</v>
+        <v>46166.65200231481</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>4.41</v>
+        <v>4.83</v>
       </c>
       <c r="L114" s="10" t="n">
-        <v>46166.75684027778</v>
+        <v>46166.72008101852</v>
       </c>
       <c r="M114" s="10" t="n">
-        <v>46166.78159722222</v>
+        <v>46166.76737268519</v>
       </c>
       <c r="N114" s="5" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="Q114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R114" s="5" t="n">
-        <v>6.78</v>
+        <v>7.6</v>
       </c>
       <c r="S114" s="5" t="n">
-        <v>6.78</v>
+        <v>7.6</v>
       </c>
       <c r="T114" s="5" t="n"/>
       <c r="U114" s="5" t="n">
@@ -24354,71 +24405,71 @@
     </row>
     <row r="115">
       <c r="A115" s="9" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B115" s="9" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="C115" s="9" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="I115" s="11" t="n">
-        <v>46166.45078703704</v>
+        <v>46167.03607638889</v>
       </c>
       <c r="J115" s="11" t="n">
-        <v>46166.65200231481</v>
+        <v>46167.16278935185</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>4.83</v>
+        <v>3.04</v>
       </c>
       <c r="L115" s="11" t="n">
-        <v>46166.72008101852</v>
+        <v>46167.27425925926</v>
       </c>
       <c r="M115" s="11" t="n">
-        <v>46166.76737268519</v>
+        <v>46167.59642361111</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>1.63</v>
+        <v>2.68</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>1.14</v>
+        <v>7.73</v>
       </c>
       <c r="P115" s="2" t="n">
-        <v>1.14</v>
+        <v>7.73</v>
       </c>
       <c r="Q115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R115" s="2" t="n">
-        <v>7.6</v>
+        <v>13.45</v>
       </c>
       <c r="S115" s="2" t="n">
-        <v>7.6</v>
+        <v>13.45</v>
       </c>
       <c r="T115" s="2" t="n"/>
       <c r="U115" s="2" t="n">
@@ -24428,7 +24479,7 @@
         <v>7456</v>
       </c>
       <c r="W115" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="X115" s="7" t="n">
         <v>0</v>
@@ -24457,56 +24508,56 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="I116" s="10" t="n">
-        <v>46167.03607638889</v>
+        <v>46167.58994212963</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>46167.16278935185</v>
+        <v>46167.64440972222</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>3.04</v>
+        <v>1.31</v>
       </c>
       <c r="L116" s="10" t="n">
-        <v>46167.27425925926</v>
+        <v>46167.79445601852</v>
       </c>
       <c r="M116" s="10" t="n">
-        <v>46167.59642361111</v>
+        <v>46168.14833333333</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>7.73</v>
+        <v>8.49</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>7.73</v>
+        <v>8.49</v>
       </c>
       <c r="Q116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R116" s="5" t="n">
-        <v>13.45</v>
+        <v>13.4</v>
       </c>
       <c r="S116" s="5" t="n">
-        <v>13.45</v>
+        <v>13.4</v>
       </c>
       <c r="T116" s="5" t="n"/>
       <c r="U116" s="5" t="n">
@@ -24533,7 +24584,7 @@
         <v>46167</v>
       </c>
       <c r="B117" s="9" t="n">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="C117" s="9" t="n">
         <v>46167</v>
@@ -24545,56 +24596,56 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="I117" s="11" t="n">
-        <v>46167.58994212963</v>
+        <v>46166.89329861111</v>
       </c>
       <c r="J117" s="11" t="n">
-        <v>46167.64440972222</v>
+        <v>46167.12024305556</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.31</v>
+        <v>5.45</v>
       </c>
       <c r="L117" s="11" t="n">
-        <v>46167.79445601852</v>
+        <v>46167.41954861111</v>
       </c>
       <c r="M117" s="11" t="n">
-        <v>46168.14833333333</v>
+        <v>46167.78295138889</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>3.6</v>
+        <v>7.18</v>
       </c>
       <c r="O117" s="2" t="n">
-        <v>8.49</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="P117" s="2" t="n">
-        <v>8.49</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Q117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R117" s="2" t="n">
-        <v>13.4</v>
+        <v>21.35</v>
       </c>
       <c r="S117" s="2" t="n">
-        <v>13.4</v>
+        <v>21.35</v>
       </c>
       <c r="T117" s="2" t="n"/>
       <c r="U117" s="2" t="n">
@@ -24628,63 +24679,67 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I118" s="10" t="n">
-        <v>46166.89329861111</v>
+        <v>46166.86069444445</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>46167.12024305556</v>
+        <v>46167.01652777778</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>5.45</v>
+        <v>3.74</v>
       </c>
       <c r="L118" s="10" t="n">
-        <v>46167.41954861111</v>
+        <v>46167.49322916667</v>
       </c>
       <c r="M118" s="10" t="n">
-        <v>46167.78295138889</v>
+        <v>46167.80994212963</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>7.18</v>
+        <v>11.44</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>8.720000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>8.720000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Q118" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R118" s="5" t="n">
-        <v>21.35</v>
+        <v>22.78</v>
       </c>
       <c r="S118" s="5" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="T118" s="5" t="n"/>
+        <v>22.78</v>
+      </c>
+      <c r="T118" s="5" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U118" s="5" t="n">
         <v>1</v>
       </c>
@@ -24692,7 +24747,7 @@
         <v>7456</v>
       </c>
       <c r="W118" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="X118" s="6" t="n">
         <v>0</v>
@@ -24706,85 +24761,81 @@
     </row>
     <row r="119">
       <c r="A119" s="9" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B119" s="9" t="n">
         <v>46167</v>
       </c>
-      <c r="B119" s="9" t="n">
-        <v>46166</v>
-      </c>
       <c r="C119" s="9" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="I119" s="11" t="n">
-        <v>46166.86069444445</v>
+        <v>46167.72461805555</v>
       </c>
       <c r="J119" s="11" t="n">
-        <v>46167.01652777778</v>
+        <v>46168.19608796296</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>3.74</v>
+        <v>11.32</v>
       </c>
       <c r="L119" s="11" t="n">
-        <v>46167.49322916667</v>
+        <v>46168.27104166667</v>
       </c>
       <c r="M119" s="11" t="n">
-        <v>46167.80994212963</v>
+        <v>46168.69186342593</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>11.44</v>
+        <v>1.8</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="Q119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R119" s="2" t="n">
-        <v>22.78</v>
+        <v>23.21</v>
       </c>
       <c r="S119" s="2" t="n">
-        <v>22.78</v>
-      </c>
-      <c r="T119" s="2" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>23.21</v>
+      </c>
+      <c r="T119" s="2" t="n"/>
       <c r="U119" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V119" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="W119" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X119" s="7" t="n">
         <v>0</v>
@@ -24801,7 +24852,7 @@
         <v>46168</v>
       </c>
       <c r="B120" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C120" s="8" t="n">
         <v>46168</v>
@@ -24813,56 +24864,56 @@
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8005 สมัย หัวลาก10W</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="H120" s="5" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="I120" s="10" t="n">
-        <v>46167.72461805555</v>
+        <v>46168.23354166667</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>46168.19608796296</v>
+        <v>46168.34030092593</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>11.32</v>
+        <v>2.56</v>
       </c>
       <c r="L120" s="10" t="n">
-        <v>46168.27104166667</v>
+        <v>46168.41813657407</v>
       </c>
       <c r="M120" s="10" t="n">
-        <v>46168.69186342593</v>
+        <v>46168.79332175926</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="P120" s="5" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="Q120" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R120" s="5" t="n">
-        <v>23.21</v>
+        <v>13.43</v>
       </c>
       <c r="S120" s="5" t="n">
-        <v>23.21</v>
+        <v>13.43</v>
       </c>
       <c r="T120" s="5" t="n"/>
       <c r="U120" s="5" t="n">
@@ -24889,7 +24940,7 @@
         <v>46168</v>
       </c>
       <c r="B121" s="9" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="C121" s="9" t="n">
         <v>46168</v>
@@ -24901,56 +24952,56 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>71-8005 สมัย หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="I121" s="11" t="n">
-        <v>46168.23354166667</v>
+        <v>46167.8870949074</v>
       </c>
       <c r="J121" s="11" t="n">
-        <v>46168.34030092593</v>
+        <v>46167.96597222222</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2.56</v>
+        <v>1.89</v>
       </c>
       <c r="L121" s="11" t="n">
-        <v>46168.41813657407</v>
+        <v>46168.04552083334</v>
       </c>
       <c r="M121" s="11" t="n">
-        <v>46168.79332175926</v>
+        <v>46168.3191087963</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>9</v>
+        <v>6.57</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>9</v>
+        <v>6.57</v>
       </c>
       <c r="Q121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R121" s="2" t="n">
-        <v>13.43</v>
+        <v>10.37</v>
       </c>
       <c r="S121" s="2" t="n">
-        <v>13.43</v>
+        <v>10.37</v>
       </c>
       <c r="T121" s="2" t="n"/>
       <c r="U121" s="2" t="n">
@@ -24974,10 +25025,10 @@
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B122" s="8" t="n">
         <v>46168</v>
-      </c>
-      <c r="B122" s="8" t="n">
-        <v>46167</v>
       </c>
       <c r="C122" s="8" t="n">
         <v>46168</v>
@@ -24999,46 +25050,46 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="I122" s="10" t="n">
-        <v>46167.8870949074</v>
+        <v>46168.39633101852</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>46167.96597222222</v>
+        <v>46168.57978009259</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>1.89</v>
+        <v>4.4</v>
       </c>
       <c r="L122" s="10" t="n">
-        <v>46168.04552083334</v>
+        <v>46168.65016203704</v>
       </c>
       <c r="M122" s="10" t="n">
-        <v>46168.3191087963</v>
+        <v>46169.98444444445</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>6.57</v>
+        <v>32.02</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>6.57</v>
+        <v>32.02</v>
       </c>
       <c r="Q122" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R122" s="5" t="n">
-        <v>10.37</v>
+        <v>38.11</v>
       </c>
       <c r="S122" s="5" t="n">
-        <v>10.37</v>
+        <v>38.11</v>
       </c>
       <c r="T122" s="5" t="n"/>
       <c r="U122" s="5" t="n">
@@ -25062,81 +25113,81 @@
     </row>
     <row r="123">
       <c r="A123" s="9" t="n">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B123" s="9" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="C123" s="9" t="n">
         <v>46168</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I123" s="11" t="n">
-        <v>46168.39633101852</v>
+        <v>46167.88145833334</v>
       </c>
       <c r="J123" s="11" t="n">
-        <v>46168.57978009259</v>
+        <v>46167.93736111111</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>4.4</v>
+        <v>1.34</v>
       </c>
       <c r="L123" s="11" t="n">
-        <v>46168.65016203704</v>
+        <v>46168.00524305556</v>
       </c>
       <c r="M123" s="11" t="n">
-        <v>46169.98444444445</v>
+        <v>46168.24994212963</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>32.02</v>
+        <v>5.87</v>
       </c>
       <c r="P123" s="2" t="n">
-        <v>32.02</v>
+        <v>5.87</v>
       </c>
       <c r="Q123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R123" s="2" t="n">
-        <v>38.11</v>
+        <v>8.84</v>
       </c>
       <c r="S123" s="2" t="n">
-        <v>38.11</v>
+        <v>8.84</v>
       </c>
       <c r="T123" s="2" t="n"/>
       <c r="U123" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V123" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="W123" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X123" s="7" t="n">
         <v>0</v>
@@ -25150,10 +25201,10 @@
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="B124" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C124" s="8" t="n">
         <v>46168</v>
@@ -25175,59 +25226,59 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="H124" s="5" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
       <c r="I124" s="10" t="n">
-        <v>46167.88145833334</v>
+        <v>46168.34814814815</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>46167.93736111111</v>
+        <v>46168.47204861111</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>1.34</v>
+        <v>2.97</v>
       </c>
       <c r="L124" s="10" t="n">
-        <v>46168.00524305556</v>
+        <v>46168.54461805556</v>
       </c>
       <c r="M124" s="10" t="n">
-        <v>46168.24994212963</v>
+        <v>46169.68572916667</v>
       </c>
       <c r="N124" s="5" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>5.87</v>
+        <v>27.39</v>
       </c>
       <c r="P124" s="5" t="n">
-        <v>5.87</v>
+        <v>27.39</v>
       </c>
       <c r="Q124" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R124" s="5" t="n">
-        <v>8.84</v>
+        <v>32.1</v>
       </c>
       <c r="S124" s="5" t="n">
-        <v>8.84</v>
+        <v>32.1</v>
       </c>
       <c r="T124" s="5" t="n"/>
       <c r="U124" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V124" s="6" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="W124" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X124" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y124" s="6" t="n">
         <v>0</v>
@@ -25244,65 +25295,65 @@
         <v>46168</v>
       </c>
       <c r="C125" s="9" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="I125" s="11" t="n">
-        <v>46168.34814814815</v>
+        <v>46168.79240740741</v>
       </c>
       <c r="J125" s="11" t="n">
-        <v>46168.47204861111</v>
+        <v>46169.13828703704</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>2.97</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L125" s="11" t="n">
-        <v>46168.54461805556</v>
+        <v>46169.20743055556</v>
       </c>
       <c r="M125" s="11" t="n">
-        <v>46169.68572916667</v>
+        <v>46169.67351851852</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>27.39</v>
+        <v>11.19</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>27.39</v>
+        <v>11.19</v>
       </c>
       <c r="Q125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R125" s="2" t="n">
-        <v>32.1</v>
+        <v>21.15</v>
       </c>
       <c r="S125" s="2" t="n">
-        <v>32.1</v>
+        <v>21.15</v>
       </c>
       <c r="T125" s="2" t="n"/>
       <c r="U125" s="2" t="n">
@@ -25315,7 +25366,7 @@
         <v>3680</v>
       </c>
       <c r="X125" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="Y125" s="7" t="n">
         <v>0</v>
@@ -25341,56 +25392,56 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="I126" s="10" t="n">
-        <v>46168.79240740741</v>
+        <v>46168.95151620371</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>46169.13828703704</v>
+        <v>46169.36881944445</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>8.300000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="L126" s="10" t="n">
-        <v>46169.20743055556</v>
+        <v>46169.45774305556</v>
       </c>
       <c r="M126" s="10" t="n">
-        <v>46169.67351851852</v>
+        <v>46169.6916550926</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="O126" s="5" t="n">
-        <v>11.19</v>
+        <v>5.61</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>11.19</v>
+        <v>5.61</v>
       </c>
       <c r="Q126" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R126" s="5" t="n">
-        <v>21.15</v>
+        <v>17.76</v>
       </c>
       <c r="S126" s="5" t="n">
-        <v>21.15</v>
+        <v>17.76</v>
       </c>
       <c r="T126" s="5" t="n"/>
       <c r="U126" s="5" t="n">
@@ -25403,7 +25454,7 @@
         <v>3680</v>
       </c>
       <c r="X126" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y126" s="6" t="n">
         <v>0</v>
@@ -25414,71 +25465,71 @@
     </row>
     <row r="127">
       <c r="A127" s="9" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B127" s="9" t="n">
         <v>46169</v>
-      </c>
-      <c r="B127" s="9" t="n">
-        <v>46168</v>
       </c>
       <c r="C127" s="9" t="n">
         <v>46169</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I127" s="11" t="n">
-        <v>46168.95151620371</v>
+        <v>46169.77158564814</v>
       </c>
       <c r="J127" s="11" t="n">
-        <v>46169.36881944445</v>
+        <v>46169.9080787037</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>10.02</v>
+        <v>3.28</v>
       </c>
       <c r="L127" s="11" t="n">
-        <v>46169.45774305556</v>
+        <v>46169.97532407408</v>
       </c>
       <c r="M127" s="11" t="n">
-        <v>46169.6916550926</v>
+        <v>46170.45916666667</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>2.13</v>
+        <v>1.61</v>
       </c>
       <c r="O127" s="2" t="n">
-        <v>5.61</v>
+        <v>11.61</v>
       </c>
       <c r="P127" s="2" t="n">
-        <v>5.61</v>
+        <v>11.61</v>
       </c>
       <c r="Q127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R127" s="2" t="n">
-        <v>17.76</v>
+        <v>16.5</v>
       </c>
       <c r="S127" s="2" t="n">
-        <v>17.76</v>
+        <v>16.5</v>
       </c>
       <c r="T127" s="2" t="n"/>
       <c r="U127" s="2" t="n">
@@ -25491,7 +25542,7 @@
         <v>3680</v>
       </c>
       <c r="X127" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="Y127" s="7" t="n">
         <v>0</v>
@@ -25508,65 +25559,65 @@
         <v>46169</v>
       </c>
       <c r="C128" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="I128" s="10" t="n">
-        <v>46169.77158564814</v>
+        <v>46169.71230324074</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>46169.9080787037</v>
+        <v>46170.50636574074</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>3.28</v>
+        <v>19.06</v>
       </c>
       <c r="L128" s="10" t="n">
-        <v>46169.97532407408</v>
+        <v>46170.58515046296</v>
       </c>
       <c r="M128" s="10" t="n">
-        <v>46170.45916666667</v>
+        <v>46171.03496527778</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="O128" s="5" t="n">
-        <v>11.61</v>
+        <v>10.8</v>
       </c>
       <c r="P128" s="5" t="n">
-        <v>11.61</v>
+        <v>10.8</v>
       </c>
       <c r="Q128" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R128" s="5" t="n">
-        <v>16.5</v>
+        <v>31.74</v>
       </c>
       <c r="S128" s="5" t="n">
-        <v>16.5</v>
+        <v>31.74</v>
       </c>
       <c r="T128" s="5" t="n"/>
       <c r="U128" s="5" t="n">
@@ -25579,7 +25630,7 @@
         <v>3680</v>
       </c>
       <c r="X128" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="Y128" s="6" t="n">
         <v>0</v>
@@ -25605,56 +25656,56 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>71-8001 มานพ หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="I129" s="11" t="n">
-        <v>46169.71230324074</v>
+        <v>46169.76866898148</v>
       </c>
       <c r="J129" s="11" t="n">
-        <v>46170.50636574074</v>
+        <v>46169.92724537037</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>19.06</v>
+        <v>3.81</v>
       </c>
       <c r="L129" s="11" t="n">
-        <v>46170.58515046296</v>
+        <v>46170.0078587963</v>
       </c>
       <c r="M129" s="11" t="n">
-        <v>46171.03496527778</v>
+        <v>46170.40075231482</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O129" s="2" t="n">
-        <v>10.8</v>
+        <v>9.43</v>
       </c>
       <c r="P129" s="2" t="n">
-        <v>10.8</v>
+        <v>9.43</v>
       </c>
       <c r="Q129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R129" s="2" t="n">
-        <v>31.74</v>
+        <v>15.17</v>
       </c>
       <c r="S129" s="2" t="n">
-        <v>31.74</v>
+        <v>15.17</v>
       </c>
       <c r="T129" s="2" t="n"/>
       <c r="U129" s="2" t="n">
@@ -25664,10 +25715,10 @@
         <v>7360</v>
       </c>
       <c r="W129" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X129" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="Y129" s="7" t="n">
         <v>0</v>
@@ -25681,7 +25732,7 @@
         <v>46170</v>
       </c>
       <c r="B130" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C130" s="8" t="n">
         <v>46170</v>
@@ -25703,46 +25754,46 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="I130" s="10" t="n">
-        <v>46169.76866898148</v>
+        <v>46170.58152777778</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>46169.92724537037</v>
+        <v>46170.66003472222</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>3.81</v>
+        <v>1.88</v>
       </c>
       <c r="L130" s="10" t="n">
-        <v>46170.0078587963</v>
+        <v>46170.72534722222</v>
       </c>
       <c r="M130" s="10" t="n">
-        <v>46170.40075231482</v>
+        <v>46170.76195601852</v>
       </c>
       <c r="N130" s="5" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="O130" s="5" t="n">
-        <v>9.43</v>
+        <v>0.88</v>
       </c>
       <c r="P130" s="5" t="n">
-        <v>9.43</v>
+        <v>0.88</v>
       </c>
       <c r="Q130" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R130" s="5" t="n">
-        <v>15.17</v>
+        <v>4.33</v>
       </c>
       <c r="S130" s="5" t="n">
-        <v>15.17</v>
+        <v>4.33</v>
       </c>
       <c r="T130" s="5" t="n"/>
       <c r="U130" s="5" t="n">
@@ -25766,7 +25817,7 @@
     </row>
     <row r="131">
       <c r="A131" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B131" s="9" t="n">
         <v>46170</v>
@@ -25791,46 +25842,46 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="I131" s="11" t="n">
-        <v>46170.58152777778</v>
+        <v>46170.87883101852</v>
       </c>
       <c r="J131" s="11" t="n">
-        <v>46170.66003472222</v>
+        <v>46170.92953703704</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="L131" s="11" t="n">
-        <v>46170.72534722222</v>
+        <v>46170.99549768519</v>
       </c>
       <c r="M131" s="11" t="n">
-        <v>46170.76195601852</v>
+        <v>46171.26299768518</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O131" s="2" t="n">
-        <v>0.88</v>
+        <v>6.42</v>
       </c>
       <c r="P131" s="2" t="n">
-        <v>0.88</v>
+        <v>6.42</v>
       </c>
       <c r="Q131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R131" s="2" t="n">
-        <v>4.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="S131" s="2" t="n">
-        <v>4.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="T131" s="2" t="n"/>
       <c r="U131" s="2" t="n">
@@ -25854,10 +25905,10 @@
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B132" s="8" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C132" s="8" t="n">
         <v>46170</v>
@@ -25869,56 +25920,56 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="I132" s="10" t="n">
-        <v>46170.87883101852</v>
+        <v>46169.78903935185</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>46170.92953703704</v>
+        <v>46169.98337962963</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>1.22</v>
+        <v>4.66</v>
       </c>
       <c r="L132" s="10" t="n">
-        <v>46170.99549768519</v>
+        <v>46170.07542824074</v>
       </c>
       <c r="M132" s="10" t="n">
-        <v>46171.26299768518</v>
+        <v>46170.40826388889</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>1.58</v>
+        <v>2.21</v>
       </c>
       <c r="O132" s="5" t="n">
-        <v>6.42</v>
+        <v>7.99</v>
       </c>
       <c r="P132" s="5" t="n">
-        <v>6.42</v>
+        <v>7.99</v>
       </c>
       <c r="Q132" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R132" s="5" t="n">
-        <v>9.220000000000001</v>
+        <v>14.86</v>
       </c>
       <c r="S132" s="5" t="n">
-        <v>9.220000000000001</v>
+        <v>14.86</v>
       </c>
       <c r="T132" s="5" t="n"/>
       <c r="U132" s="5" t="n">
@@ -25945,7 +25996,7 @@
         <v>46170</v>
       </c>
       <c r="B133" s="9" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C133" s="9" t="n">
         <v>46170</v>
@@ -25967,46 +26018,46 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="I133" s="11" t="n">
-        <v>46169.78903935185</v>
+        <v>46170.5037037037</v>
       </c>
       <c r="J133" s="11" t="n">
-        <v>46169.98337962963</v>
+        <v>46170.62738425926</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>4.66</v>
+        <v>2.97</v>
       </c>
       <c r="L133" s="11" t="n">
-        <v>46170.07542824074</v>
+        <v>46170.72587962963</v>
       </c>
       <c r="M133" s="11" t="n">
-        <v>46170.40826388889</v>
+        <v>46170.7800462963</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="O133" s="2" t="n">
-        <v>7.99</v>
+        <v>1.3</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>7.99</v>
+        <v>1.3</v>
       </c>
       <c r="Q133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R133" s="2" t="n">
-        <v>14.86</v>
+        <v>6.63</v>
       </c>
       <c r="S133" s="2" t="n">
-        <v>14.86</v>
+        <v>6.63</v>
       </c>
       <c r="T133" s="2" t="n"/>
       <c r="U133" s="2" t="n">
@@ -26045,58 +26096,62 @@
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="I134" s="10" t="n">
-        <v>46170.5037037037</v>
+        <v>46170.11607638889</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>46170.62738425926</v>
+        <v>46170.26921296296</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>2.97</v>
+        <v>3.68</v>
       </c>
       <c r="L134" s="10" t="n">
-        <v>46170.72587962963</v>
+        <v>46170.83622685185</v>
       </c>
       <c r="M134" s="10" t="n">
-        <v>46170.7800462963</v>
+        <v>46170.9013425926</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>2.36</v>
+        <v>13.61</v>
       </c>
       <c r="O134" s="5" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q134" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R134" s="5" t="n">
-        <v>6.63</v>
+        <v>18.85</v>
       </c>
       <c r="S134" s="5" t="n">
-        <v>6.63</v>
-      </c>
-      <c r="T134" s="5" t="n"/>
+        <v>18.85</v>
+      </c>
+      <c r="T134" s="5" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U134" s="5" t="n">
         <v>1</v>
       </c>
@@ -26104,7 +26159,7 @@
         <v>7360</v>
       </c>
       <c r="W134" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="X134" s="6" t="n">
         <v>0</v>
@@ -26118,7 +26173,7 @@
     </row>
     <row r="135">
       <c r="A135" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B135" s="9" t="n">
         <v>46170</v>
@@ -26128,67 +26183,63 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I135" s="11" t="n">
-        <v>46170.11607638889</v>
+        <v>46170.58722222222</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>46170.26921296296</v>
+        <v>46170.89265046296</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>3.68</v>
+        <v>7.33</v>
       </c>
       <c r="L135" s="11" t="n">
-        <v>46170.83622685185</v>
+        <v>46170.96063657408</v>
       </c>
       <c r="M135" s="11" t="n">
-        <v>46170.9013425926</v>
+        <v>46171.30994212963</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>13.61</v>
+        <v>1.63</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Q135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>18.85</v>
+        <v>17.35</v>
       </c>
       <c r="S135" s="2" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="T135" s="2" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>17.35</v>
+      </c>
+      <c r="T135" s="2" t="n"/>
       <c r="U135" s="2" t="n">
         <v>1</v>
       </c>
@@ -26213,68 +26264,68 @@
         <v>46171</v>
       </c>
       <c r="B136" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C136" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I136" s="10" t="n">
-        <v>46170.58722222222</v>
+        <v>46171.16535879629</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>46170.89265046296</v>
+        <v>46171.27927083334</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>7.33</v>
+        <v>2.73</v>
       </c>
       <c r="L136" s="10" t="n">
-        <v>46170.96063657408</v>
+        <v>46171.37247685185</v>
       </c>
       <c r="M136" s="10" t="n">
-        <v>46171.30994212963</v>
+        <v>46171.61934027778</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O136" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="P136" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="Q136" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R136" s="5" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="S136" s="5" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="T136" s="5" t="n"/>
       <c r="U136" s="5" t="n">
@@ -26284,7 +26335,7 @@
         <v>7360</v>
       </c>
       <c r="W136" s="6" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X136" s="6" t="n">
         <v>0</v>
@@ -26323,46 +26374,46 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I137" s="11" t="n">
-        <v>46171.16535879629</v>
+        <v>46171.78201388889</v>
       </c>
       <c r="J137" s="11" t="n">
-        <v>46171.27927083334</v>
+        <v>46171.89481481481</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="L137" s="11" t="n">
-        <v>46171.37247685185</v>
+        <v>46171.96677083334</v>
       </c>
       <c r="M137" s="11" t="n">
-        <v>46171.61934027778</v>
+        <v>46172.09275462963</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="O137" s="2" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="Q137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R137" s="2" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="S137" s="2" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="T137" s="2" t="n"/>
       <c r="U137" s="2" t="n">
@@ -26401,56 +26452,56 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I138" s="10" t="n">
-        <v>46171.78201388889</v>
+        <v>46171.33181712963</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>46171.89481481481</v>
+        <v>46171.60032407408</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>2.71</v>
+        <v>6.44</v>
       </c>
       <c r="L138" s="10" t="n">
-        <v>46171.96677083334</v>
+        <v>46171.67759259259</v>
       </c>
       <c r="M138" s="10" t="n">
-        <v>46172.09275462963</v>
+        <v>46171.70689814815</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="O138" s="5" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="Q138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R138" s="5" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="S138" s="5" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="T138" s="5" t="n"/>
       <c r="U138" s="5" t="n">
@@ -26477,7 +26528,7 @@
         <v>46171</v>
       </c>
       <c r="B139" s="9" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="C139" s="9" t="n">
         <v>46171</v>
@@ -26489,56 +26540,56 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="I139" s="11" t="n">
-        <v>46171.33181712963</v>
+        <v>46170.99238425926</v>
       </c>
       <c r="J139" s="11" t="n">
-        <v>46171.60032407408</v>
+        <v>46171.28165509259</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>6.44</v>
+        <v>6.94</v>
       </c>
       <c r="L139" s="11" t="n">
-        <v>46171.67759259259</v>
+        <v>46171.3696875</v>
       </c>
       <c r="M139" s="11" t="n">
-        <v>46171.70689814815</v>
+        <v>46171.59075231481</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="P139" s="2" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="Q139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R139" s="2" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="S139" s="2" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="T139" s="2" t="n"/>
       <c r="U139" s="2" t="n">
@@ -26565,7 +26616,7 @@
         <v>46171</v>
       </c>
       <c r="B140" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C140" s="8" t="n">
         <v>46171</v>
@@ -26587,46 +26638,46 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="I140" s="10" t="n">
-        <v>46170.99238425926</v>
+        <v>46171.66229166667</v>
       </c>
       <c r="J140" s="10" t="n">
-        <v>46171.28165509259</v>
+        <v>46171.72710648148</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>6.94</v>
+        <v>1.56</v>
       </c>
       <c r="L140" s="10" t="n">
-        <v>46171.3696875</v>
+        <v>46171.82959490741</v>
       </c>
       <c r="M140" s="10" t="n">
-        <v>46171.59075231481</v>
+        <v>46171.94225694444</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="O140" s="5" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="P140" s="5" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="Q140" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R140" s="5" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="S140" s="5" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="T140" s="5" t="n"/>
       <c r="U140" s="5" t="n">
@@ -26665,56 +26716,56 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I141" s="11" t="n">
-        <v>46171.66229166667</v>
+        <v>46171.00243055556</v>
       </c>
       <c r="J141" s="11" t="n">
-        <v>46171.72710648148</v>
+        <v>46171.46831018518</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>1.56</v>
+        <v>11.18</v>
       </c>
       <c r="L141" s="11" t="n">
-        <v>46171.82959490741</v>
+        <v>46171.54582175926</v>
       </c>
       <c r="M141" s="11" t="n">
-        <v>46171.94225694444</v>
+        <v>46171.60834490741</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R141" s="2" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="S141" s="2" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="T141" s="2" t="n"/>
       <c r="U141" s="2" t="n">
@@ -26763,46 +26814,46 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I142" s="10" t="n">
-        <v>46171.00243055556</v>
+        <v>46171.67638888889</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>46171.46831018518</v>
+        <v>46171.7416087963</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>11.18</v>
+        <v>1.57</v>
       </c>
       <c r="L142" s="10" t="n">
-        <v>46171.54582175926</v>
+        <v>46171.82641203704</v>
       </c>
       <c r="M142" s="10" t="n">
-        <v>46171.60834490741</v>
+        <v>46171.875625</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="O142" s="5" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="P142" s="5" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="Q142" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R142" s="5" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="S142" s="5" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="T142" s="5" t="n"/>
       <c r="U142" s="5" t="n">
@@ -26826,7 +26877,7 @@
     </row>
     <row r="143">
       <c r="A143" s="9" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B143" s="9" t="n">
         <v>46171</v>
@@ -26836,68 +26887,68 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I143" s="11" t="n">
-        <v>46171.67638888889</v>
+        <v>46171.72065972222</v>
       </c>
       <c r="J143" s="11" t="n">
-        <v>46171.7416087963</v>
+        <v>46171.87474537037</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="L143" s="11" t="n">
-        <v>46171.82641203704</v>
+        <v>46171.94614583333</v>
       </c>
       <c r="M143" s="11" t="n">
-        <v>46171.875625</v>
+        <v>46172.63309027778</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="O143" s="2" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="P143" s="2" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="Q143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R143" s="2" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="S143" s="2" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="T143" s="2" t="n"/>
       <c r="U143" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V143" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="W143" s="7" t="n">
         <v>0</v>
@@ -26917,68 +26968,68 @@
         <v>46172</v>
       </c>
       <c r="B144" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C144" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I144" s="10" t="n">
-        <v>46171.72065972222</v>
+        <v>46172.32059027778</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>46171.87474537037</v>
+        <v>46172.47302083333</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="L144" s="10" t="n">
-        <v>46171.94614583333</v>
+        <v>46172.56171296296</v>
       </c>
       <c r="M144" s="10" t="n">
-        <v>46172.63309027778</v>
+        <v>46172.81743055556</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="O144" s="5" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="P144" s="5" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="Q144" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R144" s="5" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="S144" s="5" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="T144" s="5" t="n"/>
       <c r="U144" s="5" t="n">
@@ -26988,7 +27039,7 @@
         <v>7264</v>
       </c>
       <c r="W144" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X144" s="6" t="n">
         <v>0</v>
@@ -27005,7 +27056,7 @@
         <v>46172</v>
       </c>
       <c r="B145" s="9" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C145" s="9" t="n">
         <v>46172</v>
@@ -27017,58 +27068,62 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="I145" s="11" t="n">
-        <v>46172.32059027778</v>
+        <v>46171.82071759259</v>
       </c>
       <c r="J145" s="11" t="n">
-        <v>46172.47302083333</v>
+        <v>46171.92391203704</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>3.66</v>
+        <v>2.48</v>
       </c>
       <c r="L145" s="11" t="n">
-        <v>46172.56171296296</v>
+        <v>46172.29966435185</v>
       </c>
       <c r="M145" s="11" t="n">
-        <v>46172.81743055556</v>
+        <v>46172.37111111111</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>2.13</v>
+        <v>9.02</v>
       </c>
       <c r="O145" s="2" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="P145" s="2" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="Q145" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R145" s="2" t="n">
-        <v>11.92</v>
+        <v>13.21</v>
       </c>
       <c r="S145" s="2" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="T145" s="2" t="n"/>
+        <v>13.21</v>
+      </c>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U145" s="2" t="n">
         <v>1</v>
       </c>
@@ -27076,7 +27131,7 @@
         <v>7264</v>
       </c>
       <c r="W145" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X145" s="7" t="n">
         <v>0</v>
@@ -27093,7 +27148,7 @@
         <v>46172</v>
       </c>
       <c r="B146" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C146" s="8" t="n">
         <v>46172</v>
@@ -27115,52 +27170,48 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="I146" s="10" t="n">
-        <v>46171.82071759259</v>
+        <v>46172.43083333333</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>46171.92391203704</v>
+        <v>46172.52552083333</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="L146" s="10" t="n">
-        <v>46172.29966435185</v>
+        <v>46172.61280092593</v>
       </c>
       <c r="M146" s="10" t="n">
-        <v>46172.37111111111</v>
+        <v>46172.86035879629</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>9.02</v>
+        <v>2.09</v>
       </c>
       <c r="O146" s="5" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="P146" s="5" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="Q146" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R146" s="5" t="n">
-        <v>13.21</v>
+        <v>10.31</v>
       </c>
       <c r="S146" s="5" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="T146" s="5" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>10.31</v>
+      </c>
+      <c r="T146" s="5" t="n"/>
       <c r="U146" s="5" t="n">
         <v>1</v>
       </c>
@@ -27197,56 +27248,56 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="I147" s="11" t="n">
-        <v>46172.43083333333</v>
+        <v>46172.03034722222</v>
       </c>
       <c r="J147" s="11" t="n">
-        <v>46172.52552083333</v>
+        <v>46172.28571759259</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>2.27</v>
+        <v>6.13</v>
       </c>
       <c r="L147" s="11" t="n">
-        <v>46172.61280092593</v>
+        <v>46172.36446759259</v>
       </c>
       <c r="M147" s="11" t="n">
-        <v>46172.86035879629</v>
+        <v>46172.49165509259</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="O147" s="2" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="P147" s="2" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R147" s="2" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="S147" s="2" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="T147" s="2" t="n"/>
       <c r="U147" s="2" t="n">
@@ -27256,7 +27307,7 @@
         <v>7264</v>
       </c>
       <c r="W147" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X147" s="7" t="n">
         <v>0</v>
@@ -27273,7 +27324,7 @@
         <v>46172</v>
       </c>
       <c r="B148" s="8" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C148" s="8" t="n">
         <v>46172</v>
@@ -27285,56 +27336,56 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I148" s="10" t="n">
-        <v>46172.03034722222</v>
+        <v>46171.99543981482</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>46172.28571759259</v>
+        <v>46172.2858449074</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>6.13</v>
+        <v>6.97</v>
       </c>
       <c r="L148" s="10" t="n">
-        <v>46172.36446759259</v>
+        <v>46172.40947916666</v>
       </c>
       <c r="M148" s="10" t="n">
-        <v>46172.49165509259</v>
+        <v>46172.62247685185</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>1.89</v>
+        <v>2.97</v>
       </c>
       <c r="O148" s="5" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="P148" s="5" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="Q148" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R148" s="5" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="S148" s="5" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="T148" s="5" t="n"/>
       <c r="U148" s="5" t="n">
@@ -27358,13 +27409,13 @@
     </row>
     <row r="149">
       <c r="A149" s="9" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B149" s="9" t="n">
         <v>46172</v>
       </c>
-      <c r="B149" s="9" t="n">
-        <v>46171</v>
-      </c>
       <c r="C149" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
@@ -27373,56 +27424,56 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I149" s="11" t="n">
-        <v>46171.99543981482</v>
+        <v>46172.945</v>
       </c>
       <c r="J149" s="11" t="n">
-        <v>46172.2858449074</v>
+        <v>46173.25171296296</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>6.97</v>
+        <v>7.36</v>
       </c>
       <c r="L149" s="11" t="n">
-        <v>46172.40947916666</v>
+        <v>46173.33864583333</v>
       </c>
       <c r="M149" s="11" t="n">
-        <v>46172.62247685185</v>
+        <v>46173.38333333333</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>2.97</v>
+        <v>2.09</v>
       </c>
       <c r="O149" s="2" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="P149" s="2" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="Q149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R149" s="2" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="S149" s="2" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="T149" s="2" t="n"/>
       <c r="U149" s="2" t="n">
@@ -27432,7 +27483,7 @@
         <v>7264</v>
       </c>
       <c r="W149" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X149" s="7" t="n">
         <v>0</v>
@@ -27449,7 +27500,7 @@
         <v>46173</v>
       </c>
       <c r="B150" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C150" s="8" t="n">
         <v>46173</v>
@@ -27471,46 +27522,46 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="I150" s="10" t="n">
-        <v>46172.945</v>
+        <v>46173.50255787037</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>46173.25171296296</v>
+        <v>46173.72892361111</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>7.36</v>
+        <v>5.43</v>
       </c>
       <c r="L150" s="10" t="n">
-        <v>46173.33864583333</v>
+        <v>46173.81170138889</v>
       </c>
       <c r="M150" s="10" t="n">
-        <v>46173.38333333333</v>
+        <v>46173.91047453704</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="O150" s="5" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="P150" s="5" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="Q150" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R150" s="5" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="S150" s="5" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="T150" s="5" t="n"/>
       <c r="U150" s="5" t="n">
@@ -27537,7 +27588,7 @@
         <v>46173</v>
       </c>
       <c r="B151" s="9" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="C151" s="9" t="n">
         <v>46173</v>
@@ -27549,56 +27600,56 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="I151" s="11" t="n">
-        <v>46173.50255787037</v>
+        <v>46172.96576388889</v>
       </c>
       <c r="J151" s="11" t="n">
-        <v>46173.72892361111</v>
+        <v>46173.20033564815</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>5.43</v>
+        <v>5.63</v>
       </c>
       <c r="L151" s="11" t="n">
-        <v>46173.81170138889</v>
+        <v>46173.26480324074</v>
       </c>
       <c r="M151" s="11" t="n">
-        <v>46173.91047453704</v>
+        <v>46173.38116898148</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="P151" s="2" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="Q151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R151" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S151" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="T151" s="2" t="n"/>
       <c r="U151" s="2" t="n">
@@ -27608,7 +27659,7 @@
         <v>7264</v>
       </c>
       <c r="W151" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X151" s="7" t="n">
         <v>0</v>
@@ -27637,56 +27688,56 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I152" s="10" t="n">
-        <v>46172.96576388889</v>
+        <v>46172.97828703704</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>46173.20033564815</v>
+        <v>46173.5018287037</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>5.63</v>
+        <v>12.56</v>
       </c>
       <c r="L152" s="10" t="n">
-        <v>46173.26480324074</v>
+        <v>46173.57653935185</v>
       </c>
       <c r="M152" s="10" t="n">
-        <v>46173.38116898148</v>
+        <v>46173.62144675926</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="O152" s="5" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="P152" s="5" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="Q152" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R152" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="S152" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="T152" s="5" t="n"/>
       <c r="U152" s="5" t="n">
@@ -27710,7 +27761,7 @@
     </row>
     <row r="153">
       <c r="A153" s="9" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="B153" s="9" t="n">
         <v>46172</v>
@@ -27720,61 +27771,61 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I153" s="11" t="n">
-        <v>46172.97828703704</v>
+        <v>46172.75962962963</v>
       </c>
       <c r="J153" s="11" t="n">
-        <v>46173.5018287037</v>
+        <v>46173.02157407408</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>12.56</v>
+        <v>6.29</v>
       </c>
       <c r="L153" s="11" t="n">
-        <v>46173.57653935185</v>
+        <v>46173.09358796296</v>
       </c>
       <c r="M153" s="11" t="n">
-        <v>46173.62144675926</v>
+        <v>46173.18756944445</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="P153" s="2" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="Q153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R153" s="2" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="S153" s="2" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="T153" s="2" t="n"/>
       <c r="U153" s="2" t="n">
@@ -27784,7 +27835,7 @@
         <v>7264</v>
       </c>
       <c r="W153" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X153" s="7" t="n">
         <v>0</v>
@@ -27798,10 +27849,10 @@
     </row>
     <row r="154">
       <c r="A154" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B154" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C154" s="8" t="n">
         <v>46173</v>
@@ -27823,46 +27874,46 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="H154" s="5" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="I154" s="10" t="n">
-        <v>46172.75962962963</v>
+        <v>46173.25349537037</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>46173.02157407408</v>
+        <v>46173.31078703704</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>6.29</v>
+        <v>1.38</v>
       </c>
       <c r="L154" s="10" t="n">
-        <v>46173.09358796296</v>
+        <v>46173.385625</v>
       </c>
       <c r="M154" s="10" t="n">
-        <v>46173.18756944445</v>
+        <v>46173.41065972222</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O154" s="5" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="P154" s="5" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="Q154" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R154" s="5" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="S154" s="5" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="T154" s="5" t="n"/>
       <c r="U154" s="5" t="n">
@@ -27872,7 +27923,7 @@
         <v>7264</v>
       </c>
       <c r="W154" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X154" s="6" t="n">
         <v>0</v>
@@ -27884,96 +27935,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="9" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B155" s="9" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C155" s="9" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="I155" s="11" t="n">
-        <v>46173.25349537037</v>
-      </c>
-      <c r="J155" s="11" t="n">
-        <v>46173.31078703704</v>
-      </c>
-      <c r="K155" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L155" s="11" t="n">
-        <v>46173.385625</v>
-      </c>
-      <c r="M155" s="11" t="n">
-        <v>46173.41065972222</v>
-      </c>
-      <c r="N155" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O155" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P155" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" s="2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="S155" s="2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="T155" s="2" t="n"/>
-      <c r="U155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V155" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="W155" s="7" t="n">
-        <v>3632</v>
-      </c>
-      <c r="X155" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y155" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z155" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z155"/>
+  <autoFilter ref="A1:Z154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27984,7 +27947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28052,10 +28015,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -30077,10 +30040,10 @@
         <v>0</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -30152,10 +30115,10 @@
         <v>0</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="G86" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="87">
@@ -30164,14 +30127,14 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C87" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>0</v>
@@ -30180,7 +30143,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="88">
@@ -30189,7 +30152,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
@@ -30205,32 +30168,32 @@
         <v>0</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C89" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="7" t="n">
         <v>3728</v>
-      </c>
-      <c r="E89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -30255,7 +30218,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -30264,14 +30227,14 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C91" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>0</v>
@@ -30289,7 +30252,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
@@ -30314,7 +30277,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C93" s="7" t="n">
@@ -30339,7 +30302,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
@@ -30360,11 +30323,11 @@
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
@@ -30389,7 +30352,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
@@ -30414,7 +30377,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C97" s="7" t="n">
@@ -30439,23 +30402,23 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="D98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="6" t="n">
         <v>3728</v>
-      </c>
-      <c r="E98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -30480,7 +30443,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -30489,14 +30452,14 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>0</v>
@@ -30510,18 +30473,18 @@
     </row>
     <row r="101">
       <c r="A101" s="9" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>0</v>
@@ -30564,14 +30527,14 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C103" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>0</v>
@@ -30589,7 +30552,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
@@ -30614,7 +30577,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C105" s="7" t="n">
@@ -30646,7 +30609,7 @@
         <v>7456</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E106" s="6" t="n">
         <v>0</v>
@@ -30660,18 +30623,18 @@
     </row>
     <row r="107">
       <c r="A107" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C107" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>0</v>
@@ -30689,14 +30652,14 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E108" s="6" t="n">
         <v>0</v>
@@ -30739,14 +30702,14 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C110" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E110" s="6" t="n">
         <v>0</v>
@@ -30789,14 +30752,14 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C112" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E112" s="6" t="n">
         <v>0</v>
@@ -30839,7 +30802,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C114" s="6" t="n">
@@ -30860,18 +30823,18 @@
     </row>
     <row r="115">
       <c r="A115" s="9" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C115" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>0</v>
@@ -30889,7 +30852,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C116" s="6" t="n">
@@ -30914,7 +30877,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C117" s="7" t="n">
@@ -30939,14 +30902,14 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C118" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="E118" s="6" t="n">
         <v>0</v>
@@ -30960,18 +30923,18 @@
     </row>
     <row r="119">
       <c r="A119" s="9" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C119" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>0</v>
@@ -30989,7 +30952,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C120" s="6" t="n">
@@ -31014,7 +30977,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C121" s="7" t="n">
@@ -31064,14 +31027,14 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>0</v>
@@ -31093,13 +31056,13 @@
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E124" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>0</v>
@@ -31110,11 +31073,11 @@
     </row>
     <row r="125">
       <c r="A125" s="9" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C125" s="7" t="n">
@@ -31124,7 +31087,7 @@
         <v>3680</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="F125" s="7" t="n">
         <v>0</v>
@@ -31139,7 +31102,7 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
@@ -31149,7 +31112,7 @@
         <v>3680</v>
       </c>
       <c r="E126" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>0</v>
@@ -31164,7 +31127,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C127" s="7" t="n">
@@ -31174,7 +31137,7 @@
         <v>3680</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="F127" s="7" t="n">
         <v>0</v>
@@ -31185,11 +31148,11 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C128" s="6" t="n">
@@ -31199,7 +31162,7 @@
         <v>3680</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>0</v>
@@ -31214,17 +31177,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C129" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="F129" s="7" t="n">
         <v>0</v>
@@ -31289,7 +31252,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C132" s="6" t="n">
@@ -31339,14 +31302,14 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="E134" s="6" t="n">
         <v>0</v>
@@ -31364,7 +31327,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C135" s="7" t="n">
@@ -31385,18 +31348,18 @@
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C136" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E136" s="6" t="n">
         <v>0</v>
@@ -31439,7 +31402,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
@@ -31464,7 +31427,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C139" s="7" t="n">
@@ -31514,7 +31477,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C141" s="7" t="n">
@@ -31564,11 +31527,11 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="D143" s="7" t="n">
         <v>0</v>
@@ -31585,18 +31548,18 @@
     </row>
     <row r="144">
       <c r="A144" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E144" s="6" t="n">
         <v>0</v>
@@ -31614,14 +31577,14 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C145" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E145" s="7" t="n">
         <v>0</v>
@@ -31664,14 +31627,14 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C147" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D147" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E147" s="7" t="n">
         <v>0</v>
@@ -31689,7 +31652,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
@@ -31710,18 +31673,18 @@
     </row>
     <row r="149">
       <c r="A149" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C149" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E149" s="7" t="n">
         <v>0</v>
@@ -31764,14 +31727,14 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E151" s="7" t="n">
         <v>0</v>
@@ -31789,7 +31752,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
@@ -31814,14 +31777,14 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C153" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
@@ -31846,7 +31809,7 @@
         <v>7264</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E154" s="6" t="n">
         <v>0</v>
@@ -31858,33 +31821,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="9" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="D155" s="7" t="n">
-        <v>3632</v>
-      </c>
-      <c r="E155" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G155"/>
+  <autoFilter ref="A1:G154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33286,19 +33224,19 @@
         <v>5</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>1</v>
@@ -36795,16 +36733,16 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>26.95</v>
+        <v>19.69</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>7.6</v>
+        <v>6.27</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>15.85</v>
+        <v>11.78</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>3.5</v>
+        <v>1.64</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>0</v>
@@ -36813,16 +36751,16 @@
         <v>0</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7.6</v>
+        <v>6.27</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>15.85</v>
+        <v>11.78</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>26.95</v>
+        <v>19.69</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-2.95</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="68">

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -27,16 +27,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Customer_Trips_Per_Day'!$A$1:$C$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Audit_Log'!$A$1:$J$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Audit_Log'!$A$1:$J$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trips_Pricing_All'!$A$1:$G$154</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched_Log'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Daily_Activity'!$A$1:$I$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Daily_Time_24h_Check'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manual_Extra_Trips'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'NoWork_Outbound_50pct'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Phantom_Trip_Candidates'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Hints_DoubleOrigin'!$A$1:$D$1</definedName>
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>40146</v>
+        <v>36896</v>
       </c>
     </row>
     <row r="16">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1499410</v>
+        <v>1496160</v>
       </c>
     </row>
   </sheetData>
@@ -802,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -865,35 +865,35 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>6500</v>
+        <v>7264</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>3250</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="3">
@@ -902,22 +902,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>7264</v>
@@ -926,21 +926,21 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -968,12 +968,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="7">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1043,55 +1043,55 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>7264</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>3632</v>
-      </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>10896</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="9">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1162,16 +1162,16 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1294,11 +1294,11 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1340,22 +1340,22 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="17">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1393,11 +1393,11 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1459,35 +1459,35 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>14528</v>
+        <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="21">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1505,22 +1505,22 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="22">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1591,35 +1591,35 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>10896</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="25">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1661,31 +1661,31 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="27">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1703,55 +1703,55 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="29">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="30">
@@ -1793,31 +1793,31 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="31">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1855,35 +1855,35 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="33">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1913,10 +1913,10 @@
         <v>3584</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="34">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -1946,24 +1946,24 @@
         <v>3584</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2000,22 +2000,22 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>3584</v>
       </c>
-      <c r="H36" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" s="6" t="n">
-        <v>10752</v>
+        <v>17920</v>
       </c>
     </row>
     <row r="37">
@@ -2024,64 +2024,64 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>17920</v>
+        <v>10752</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
     </row>
     <row r="39">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -2152,35 +2152,35 @@
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>14336</v>
+        <v>7264</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>14336</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="42">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2222,64 +2222,64 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>14528</v>
+        <v>7360</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>14528</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="45">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2297,22 +2297,22 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="46">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -2330,22 +2330,22 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="47">
@@ -2354,64 +2354,64 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="49">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2429,22 +2429,22 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="50">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -2462,22 +2462,22 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="51">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2515,35 +2515,35 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="53">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2581,16 +2581,16 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2627,22 +2627,22 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="56">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2660,22 +2660,22 @@
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
         <v>7360</v>
       </c>
-      <c r="G56" s="6" t="n">
-        <v>3680</v>
-      </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="57">
@@ -2684,45 +2684,45 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2759,22 +2759,22 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="60">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2792,22 +2792,22 @@
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="61">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -2845,35 +2845,35 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>11040</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="63">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="64">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2924,22 +2924,22 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="65">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2981,58 +2981,58 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>7456</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -3056,22 +3056,22 @@
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>7456</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="69">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3089,22 +3089,22 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>3728</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>18640</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="70">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -3167,43 +3167,43 @@
         <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="n">
         <v>3728</v>
       </c>
-      <c r="H72" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="I72" s="6" t="n">
-        <v>11184</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="73">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3221,22 +3221,22 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>18640</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="74">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
@@ -3340,16 +3340,16 @@
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -3452,22 +3452,22 @@
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="6" t="n">
         <v>3728</v>
       </c>
-      <c r="H80" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="I80" s="6" t="n">
-        <v>11184</v>
+        <v>18640</v>
       </c>
     </row>
     <row r="81">
@@ -3476,64 +3476,64 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>18640</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="83">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3551,22 +3551,22 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="84">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -3670,16 +3670,16 @@
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -3716,22 +3716,22 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="89">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3749,22 +3749,22 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="90">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3782,22 +3782,22 @@
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="91">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
@@ -3835,35 +3835,35 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
     </row>
     <row r="93">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -3938,64 +3938,64 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>14912</v>
+        <v>7360</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>14912</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="97">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4013,22 +4013,22 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="7" t="n">
         <v>7360</v>
       </c>
-      <c r="G97" s="7" t="n">
-        <v>3680</v>
-      </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="98">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -4046,22 +4046,22 @@
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="99">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4103,45 +4103,45 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="6" t="n">
         <v>7360</v>
       </c>
-      <c r="G100" s="6" t="n">
-        <v>3680</v>
-      </c>
       <c r="H100" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -4178,22 +4178,22 @@
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="103">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
@@ -4297,16 +4297,16 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4343,22 +4343,22 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="108">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4409,22 +4409,22 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="110">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -4462,35 +4462,35 @@
     </row>
     <row r="111">
       <c r="A111" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="112">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -4598,64 +4598,64 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
       <c r="H116" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>11040</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="117">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4673,22 +4673,22 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="118">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4706,22 +4706,22 @@
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G118" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H118" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="6" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="119">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4763,45 +4763,45 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G120" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H120" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="6" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4838,22 +4838,22 @@
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G122" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H122" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="123">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -4922,41 +4922,8 @@
         <v>10896</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="9" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F125" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="G125" s="7" t="n">
-        <v>3632</v>
-      </c>
-      <c r="H125" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="7" t="n">
-        <v>10896</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I125"/>
+  <autoFilter ref="A1:I124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8587,7 +8554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8620,43 +8587,43 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3250</v>
+        <v>3632</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก</t>
+          <t>ตีเปล่าไป P&amp;G 50%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
-        <v>46143</v>
+        <v>46152</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50%</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -8674,15 +8641,15 @@
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3584</v>
+        <v>3728</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -8696,7 +8663,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
@@ -8704,7 +8671,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8689,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8699,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -8740,7 +8707,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8717,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
@@ -8758,13 +8725,13 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
+          <t>ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -8776,17 +8743,17 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว)</t>
+          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -8798,26 +8765,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>46164</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>71-8009</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>3728</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>BH ขากลับ P&amp;G&gt;บ้านบึง 50%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9033,7 +8982,7 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>29058</v>
+        <v>25808</v>
       </c>
     </row>
     <row r="4">
@@ -9108,7 +9057,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1499410</v>
+        <v>1496160</v>
       </c>
     </row>
   </sheetData>
@@ -9501,7 +9450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9570,39 +9519,39 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>6500</v>
+        <v>7264</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>3250</v>
+        <v>14528</v>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>ขากลับ (manual): ค่าขนส่งงานขากลับ 50% ของราคาเที่ยวหลัก (+3,250.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
         </is>
       </c>
     </row>
@@ -9612,22 +9561,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>7264</v>
@@ -9636,26 +9585,26 @@
         <v>0</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (+3,632.00฿)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
@@ -9688,12 +9637,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -9726,7 +9675,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -9735,26 +9684,26 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9713,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -9773,64 +9722,64 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <v>7264</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>3632</v>
-      </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>10896</v>
+        <v>7264</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -9840,12 +9789,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -9878,7 +9827,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -9912,16 +9861,16 @@
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -9954,12 +9903,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
@@ -9992,7 +9941,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10030,7 +9979,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -10064,11 +10013,11 @@
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10106,7 +10055,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -10115,26 +10064,26 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10144,7 +10093,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10178,11 +10127,11 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -10220,7 +10169,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10254,39 +10203,39 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>14528</v>
+        <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10245,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10305,26 +10254,26 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0</v>
+        <v>7264</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>7264</v>
+        <v>3632</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>7264</v>
+        <v>10896</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10334,12 +10283,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -10372,7 +10321,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10406,35 +10355,35 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>10896</v>
+        <v>10752</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -10448,7 +10397,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10486,35 +10435,35 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10473,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10533,64 +10482,64 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10549,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -10609,26 +10558,26 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10638,35 +10587,35 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10625,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -10710,39 +10659,39 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10701,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -10773,14 +10722,14 @@
         <v>3584</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -10790,12 +10739,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -10811,29 +10760,29 @@
         <v>3584</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>14336</v>
+        <v>10752</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -10866,7 +10815,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -10875,26 +10824,26 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>3584</v>
       </c>
-      <c r="H36" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" s="6" t="n">
-        <v>10752</v>
+        <v>17920</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
         </is>
       </c>
     </row>
@@ -10904,73 +10853,73 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>7168</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>14336</v>
+        <v>7168</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>3584</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>17920</v>
+        <v>10752</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,584.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>7168</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>7168</v>
+        <v>14336</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>3584</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>10752</v>
+        <v>14336</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10929,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11018,12 +10967,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -11052,39 +11001,39 @@
     </row>
     <row r="41">
       <c r="A41" s="9" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>14336</v>
+        <v>7264</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>14336</v>
+        <v>10896</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11043,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -11132,73 +11081,73 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>14528</v>
+        <v>7360</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>14528</v>
+        <v>11040</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11157,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11217,26 +11166,26 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11195,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -11255,26 +11204,26 @@
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11284,73 +11233,73 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11309,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -11369,26 +11318,26 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11347,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -11407,26 +11356,26 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11436,12 +11385,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -11470,39 +11419,39 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11512,12 +11461,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -11546,16 +11495,16 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
@@ -11588,7 +11537,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11597,26 +11546,26 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11575,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -11635,26 +11584,26 @@
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
         <v>7360</v>
       </c>
-      <c r="G56" s="6" t="n">
-        <v>3680</v>
-      </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11664,50 +11613,50 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
@@ -11740,7 +11689,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -11749,26 +11698,26 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11727,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -11787,26 +11736,26 @@
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11816,12 +11765,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -11850,35 +11799,35 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>11040</v>
+        <v>11184</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
@@ -11892,7 +11841,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -11901,26 +11850,26 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11879,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -11939,26 +11888,26 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -11968,7 +11917,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12006,63 +11955,63 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>7456</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
@@ -12072,7 +12021,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12031,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -12091,26 +12040,26 @@
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>7456</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>14912</v>
+        <v>18640</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (วันผสม 2BH+ตีเปล่า, base บิล 1 เที่ยว) (+3,728.00฿)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12069,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12129,26 +12078,26 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H69" s="7" t="n">
         <v>3728</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>18640</v>
+        <v>14912</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>ไม่เก็บ [override: exclude_50] — ตัด 1 เที่ยวว่าง(ตีเปล่า)ออกจาก base แล้ว → เหลือ 1 เที่ยว แต่ไม่เก็บ +50% (วันนั้นวิ่งจริง 2 เที่ยว) — คู่กับ remove_matched_trips ใน oatside_config.json | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12107,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -12186,7 +12135,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บ [override: exclude_50] — ตัด 1 เที่ยวว่าง(ตีเปล่า)ออกจาก base แล้ว → เหลือ 1 เที่ยว แต่ไม่เก็บ +50% (วันนั้นวิ่งจริง 2 เที่ยว) — คู่กับ remove_matched_trips ใน oatside_config.json | ตีเปล่า (manual): ตีเปล่าไป P&amp;G 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (เที่ยวว่าง GPS นับเต็ม → ตัด base 1 เที่ยว แตกเป็นตีเปล่า+ขากลับ) (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12196,12 +12145,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -12217,52 +12166,52 @@
         <v>3728</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="n">
         <v>3728</v>
       </c>
-      <c r="H72" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="I72" s="6" t="n">
-        <v>11184</v>
+        <v>18640</v>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12221,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -12281,26 +12230,26 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>18640</v>
+        <v>11184</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12259,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -12348,7 +12297,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -12386,12 +12335,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
@@ -12420,16 +12369,16 @@
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
@@ -12462,7 +12411,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -12500,7 +12449,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -12538,7 +12487,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -12547,26 +12496,26 @@
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="6" t="n">
         <v>3728</v>
       </c>
-      <c r="H80" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="I80" s="6" t="n">
-        <v>11184</v>
+        <v>18640</v>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
         </is>
       </c>
     </row>
@@ -12576,73 +12525,73 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>18640</v>
+        <v>11184</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว) | ขากลับ (manual): BH ขากลับ P&amp;G&gt;บ้านบึง 50% (+3,728.00฿)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12601,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12661,26 +12610,26 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H83" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12639,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -12728,7 +12677,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12766,12 +12715,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D86" s="5" t="n">
@@ -12800,16 +12749,16 @@
     </row>
     <row r="87">
       <c r="A87" s="9" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
@@ -12842,7 +12791,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -12851,26 +12800,26 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12829,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -12889,26 +12838,26 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -12918,7 +12867,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -12927,26 +12876,26 @@
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -12956,12 +12905,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
@@ -12990,39 +12939,39 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="6" t="n">
         <v>7456</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>14912</v>
+        <v>7456</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>0</v>
+        <v>3728</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>14912</v>
+        <v>11184</v>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13032,7 +12981,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13070,7 +13019,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -13108,73 +13057,73 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>7456</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>7456</v>
+        <v>14912</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>3728</v>
+        <v>0</v>
       </c>
       <c r="H95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>11184</v>
+        <v>14912</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>14912</v>
+        <v>7360</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I96" s="6" t="n">
-        <v>14912</v>
+        <v>11040</v>
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13133,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13193,26 +13142,26 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="7" t="n">
         <v>7360</v>
       </c>
-      <c r="G97" s="7" t="n">
-        <v>3680</v>
-      </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="7" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13171,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -13231,26 +13180,26 @@
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="6" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13260,7 +13209,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13298,50 +13247,50 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="6" t="n">
         <v>7360</v>
       </c>
-      <c r="G100" s="6" t="n">
-        <v>3680</v>
-      </c>
       <c r="H100" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="6" t="n">
-        <v>11040</v>
+        <v>7360</v>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
@@ -13374,7 +13323,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -13383,26 +13332,26 @@
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>0</v>
+        <v>7360</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>7360</v>
+        <v>3680</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I102" s="6" t="n">
-        <v>7360</v>
+        <v>11040</v>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 100% = 1 เรทเต็ม (รถเข้าโรงงานแต่ไม่จบเที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13361,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -13450,7 +13399,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -13488,12 +13437,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
@@ -13522,16 +13471,16 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
@@ -13564,7 +13513,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13573,26 +13522,26 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13551,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -13640,7 +13589,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -13649,26 +13598,26 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13678,12 +13627,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
@@ -13712,39 +13661,39 @@
     </row>
     <row r="111">
       <c r="A111" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="7" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13703,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -13792,7 +13741,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -13830,7 +13779,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -13868,69 +13817,69 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
       <c r="H116" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>11040</v>
+        <v>10896</v>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
@@ -13944,7 +13893,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -13953,26 +13902,26 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13931,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -13991,26 +13940,26 @@
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G118" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H118" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="6" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -14020,7 +13969,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -14058,50 +14007,50 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G120" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H120" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="6" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
@@ -14134,7 +14083,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -14143,26 +14092,26 @@
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G122" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H122" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>ไม่เก็บเพิ่ม (จบ 2 เที่ยว)</t>
+          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14121,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -14210,12 +14159,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
@@ -14242,46 +14191,8 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="9" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F125" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="G125" s="7" t="n">
-        <v>3632</v>
-      </c>
-      <c r="H125" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="7" t="n">
-        <v>10896</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J125"/>
+  <autoFilter ref="A1:J124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -28,13 +28,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer_Summary'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Customer_Trips_Per_Day'!$A$1:$C$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Audit_Log'!$A$1:$J$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trips_Pricing_All'!$A$1:$G$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trip_Detail'!$A$1:$Z$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trips_Pricing_All'!$A$1:$G$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Unmatched_Log'!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Daily_Activity'!$A$1:$I$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Daily_Time_24h_Check'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Daily_Time_24h_Check'!$A$1:$M$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Plate_DestDay'!$A$1:$I$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Surcharge_50pct_1Trip'!$A$1:$L$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Manual_Extra_Trips'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Manual_Return_Trips'!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'NoWork_Outbound_50pct'!$A$1:$G$1</definedName>
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1121952</v>
+        <v>1114592</v>
       </c>
     </row>
     <row r="14">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>337312</v>
+        <v>333632</v>
       </c>
     </row>
     <row r="21">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1496160</v>
+        <v>1485120</v>
       </c>
     </row>
   </sheetData>
@@ -802,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4400,12 +4400,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
@@ -4429,35 +4429,35 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>7360</v>
+        <v>14720</v>
       </c>
       <c r="G110" s="6" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H110" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I110" s="6" t="n">
-        <v>11040</v>
+        <v>14720</v>
       </c>
     </row>
     <row r="111">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4565,64 +4565,64 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
         <v>7360</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>14720</v>
+        <v>7360</v>
       </c>
       <c r="G114" s="6" t="n">
-        <v>0</v>
+        <v>3680</v>
       </c>
       <c r="H114" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>14720</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
       <c r="H115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="7" t="n">
-        <v>11040</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="116">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -4640,22 +4640,22 @@
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H116" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="117">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4673,22 +4673,22 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="7" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="118">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -4730,45 +4730,45 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>7264</v>
+        <v>14528</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="H119" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I119" s="7" t="n">
-        <v>10896</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4805,22 +4805,22 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>14528</v>
+        <v>7264</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="H121" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="7" t="n">
-        <v>14528</v>
+        <v>10896</v>
       </c>
     </row>
     <row r="122">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
@@ -4889,41 +4889,8 @@
         <v>10896</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="6" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F124" s="6" t="n">
-        <v>7264</v>
-      </c>
-      <c r="G124" s="6" t="n">
-        <v>3632</v>
-      </c>
-      <c r="H124" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="6" t="n">
-        <v>10896</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I124"/>
+  <autoFilter ref="A1:I123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4934,7 +4901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8127,12 +8094,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -8165,7 +8132,7 @@
     </row>
     <row r="77">
       <c r="A77" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
@@ -8194,7 +8161,7 @@
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -8207,16 +8174,16 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -8236,15 +8203,15 @@
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr"/>
       <c r="K78" s="6" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="79">
@@ -8253,7 +8220,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -8295,7 +8262,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -8333,11 +8300,11 @@
     </row>
     <row r="81">
       <c r="A81" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -8362,7 +8329,7 @@
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -8379,7 +8346,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -8421,12 +8388,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -8457,50 +8424,8 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>one_trip_billed_day</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="5" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="inlineStr"/>
-      <c r="K84" s="6" t="n">
-        <v>7264</v>
-      </c>
-      <c r="L84" s="6" t="n">
-        <v>3632</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L84"/>
+  <autoFilter ref="A1:L83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8967,7 +8892,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>1121952</v>
+        <v>1114592</v>
       </c>
     </row>
     <row r="3">
@@ -9027,7 +8952,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>337312</v>
+        <v>333632</v>
       </c>
     </row>
     <row r="7">
@@ -9057,7 +8982,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1496160</v>
+        <v>1485120</v>
       </c>
     </row>
   </sheetData>
@@ -9399,10 +9324,10 @@
         <v>46170</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -13598,26 +13523,26 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>7360</v>
+        <v>0</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="H109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I109" s="7" t="n">
-        <v>11040</v>
+        <v>0</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>เก็บ 50% อัตโนมัติ (จบ 1 เที่ยว)</t>
+          <t>ไม่เก็บ [override: exclude_50] — รถไม่ได้วิ่งจริง — ตัดเที่ยวเดียวของวันออกจาก base แล้ว เหลือ 0 เที่ยว แต่ GPS เห็นรถที่โรงงาน → กัน no_finish 100% ลั่น (คู่กับ remove_matched_trips ใน oatside_config.json)</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z154"/>
+  <dimension ref="A1:Z153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25992,7 +25917,7 @@
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B134" s="8" t="n">
         <v>46170</v>
@@ -26002,67 +25927,63 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I134" s="10" t="n">
-        <v>46170.11607638889</v>
+        <v>46170.58722222222</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>46170.26921296296</v>
+        <v>46170.89265046296</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>3.68</v>
+        <v>7.33</v>
       </c>
       <c r="L134" s="10" t="n">
-        <v>46170.83622685185</v>
+        <v>46170.96063657408</v>
       </c>
       <c r="M134" s="10" t="n">
-        <v>46170.9013425926</v>
+        <v>46171.30994212963</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>13.61</v>
+        <v>1.63</v>
       </c>
       <c r="O134" s="5" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>1.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Q134" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R134" s="5" t="n">
-        <v>18.85</v>
+        <v>17.35</v>
       </c>
       <c r="S134" s="5" t="n">
-        <v>18.85</v>
-      </c>
-      <c r="T134" s="5" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>17.35</v>
+      </c>
+      <c r="T134" s="5" t="n"/>
       <c r="U134" s="5" t="n">
         <v>1</v>
       </c>
@@ -26087,68 +26008,68 @@
         <v>46171</v>
       </c>
       <c r="B135" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C135" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I135" s="11" t="n">
-        <v>46170.58722222222</v>
+        <v>46171.16535879629</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>46170.89265046296</v>
+        <v>46171.27927083334</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>7.33</v>
+        <v>2.73</v>
       </c>
       <c r="L135" s="11" t="n">
-        <v>46170.96063657408</v>
+        <v>46171.37247685185</v>
       </c>
       <c r="M135" s="11" t="n">
-        <v>46171.30994212963</v>
+        <v>46171.61934027778</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="Q135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R135" s="2" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="S135" s="2" t="n">
-        <v>17.35</v>
+        <v>10.9</v>
       </c>
       <c r="T135" s="2" t="n"/>
       <c r="U135" s="2" t="n">
@@ -26158,7 +26079,7 @@
         <v>7360</v>
       </c>
       <c r="W135" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="X135" s="7" t="n">
         <v>0</v>
@@ -26197,46 +26118,46 @@
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I136" s="10" t="n">
-        <v>46171.16535879629</v>
+        <v>46171.78201388889</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>46171.27927083334</v>
+        <v>46171.89481481481</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="L136" s="10" t="n">
-        <v>46171.37247685185</v>
+        <v>46171.96677083334</v>
       </c>
       <c r="M136" s="10" t="n">
-        <v>46171.61934027778</v>
+        <v>46172.09275462963</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="O136" s="5" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="P136" s="5" t="n">
-        <v>5.92</v>
+        <v>3.02</v>
       </c>
       <c r="Q136" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R136" s="5" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="S136" s="5" t="n">
-        <v>10.9</v>
+        <v>7.46</v>
       </c>
       <c r="T136" s="5" t="n"/>
       <c r="U136" s="5" t="n">
@@ -26275,56 +26196,56 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I137" s="11" t="n">
-        <v>46171.78201388889</v>
+        <v>46171.33181712963</v>
       </c>
       <c r="J137" s="11" t="n">
-        <v>46171.89481481481</v>
+        <v>46171.60032407408</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>2.71</v>
+        <v>6.44</v>
       </c>
       <c r="L137" s="11" t="n">
-        <v>46171.96677083334</v>
+        <v>46171.67759259259</v>
       </c>
       <c r="M137" s="11" t="n">
-        <v>46172.09275462963</v>
+        <v>46171.70689814815</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="O137" s="2" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>3.02</v>
+        <v>0.7</v>
       </c>
       <c r="Q137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R137" s="2" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="S137" s="2" t="n">
-        <v>7.46</v>
+        <v>9</v>
       </c>
       <c r="T137" s="2" t="n"/>
       <c r="U137" s="2" t="n">
@@ -26351,7 +26272,7 @@
         <v>46171</v>
       </c>
       <c r="B138" s="8" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="C138" s="8" t="n">
         <v>46171</v>
@@ -26363,56 +26284,56 @@
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="I138" s="10" t="n">
-        <v>46171.33181712963</v>
+        <v>46170.99238425926</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>46171.60032407408</v>
+        <v>46171.28165509259</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>6.44</v>
+        <v>6.94</v>
       </c>
       <c r="L138" s="10" t="n">
-        <v>46171.67759259259</v>
+        <v>46171.3696875</v>
       </c>
       <c r="M138" s="10" t="n">
-        <v>46171.70689814815</v>
+        <v>46171.59075231481</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="O138" s="5" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.7</v>
+        <v>5.31</v>
       </c>
       <c r="Q138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R138" s="5" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="S138" s="5" t="n">
-        <v>9</v>
+        <v>14.36</v>
       </c>
       <c r="T138" s="5" t="n"/>
       <c r="U138" s="5" t="n">
@@ -26439,7 +26360,7 @@
         <v>46171</v>
       </c>
       <c r="B139" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C139" s="9" t="n">
         <v>46171</v>
@@ -26461,46 +26382,46 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="I139" s="11" t="n">
-        <v>46170.99238425926</v>
+        <v>46171.66229166667</v>
       </c>
       <c r="J139" s="11" t="n">
-        <v>46171.28165509259</v>
+        <v>46171.72710648148</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>6.94</v>
+        <v>1.56</v>
       </c>
       <c r="L139" s="11" t="n">
-        <v>46171.3696875</v>
+        <v>46171.82959490741</v>
       </c>
       <c r="M139" s="11" t="n">
-        <v>46171.59075231481</v>
+        <v>46171.94225694444</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="O139" s="2" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="P139" s="2" t="n">
-        <v>5.31</v>
+        <v>2.7</v>
       </c>
       <c r="Q139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R139" s="2" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="S139" s="2" t="n">
-        <v>14.36</v>
+        <v>6.72</v>
       </c>
       <c r="T139" s="2" t="n"/>
       <c r="U139" s="2" t="n">
@@ -26539,56 +26460,56 @@
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I140" s="10" t="n">
-        <v>46171.66229166667</v>
+        <v>46171.00243055556</v>
       </c>
       <c r="J140" s="10" t="n">
-        <v>46171.72710648148</v>
+        <v>46171.46831018518</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>1.56</v>
+        <v>11.18</v>
       </c>
       <c r="L140" s="10" t="n">
-        <v>46171.82959490741</v>
+        <v>46171.54582175926</v>
       </c>
       <c r="M140" s="10" t="n">
-        <v>46171.94225694444</v>
+        <v>46171.60834490741</v>
       </c>
       <c r="N140" s="5" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O140" s="5" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="P140" s="5" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q140" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R140" s="5" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="S140" s="5" t="n">
-        <v>6.72</v>
+        <v>14.54</v>
       </c>
       <c r="T140" s="5" t="n"/>
       <c r="U140" s="5" t="n">
@@ -26637,46 +26558,46 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I141" s="11" t="n">
-        <v>46171.00243055556</v>
+        <v>46171.67638888889</v>
       </c>
       <c r="J141" s="11" t="n">
-        <v>46171.46831018518</v>
+        <v>46171.7416087963</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>11.18</v>
+        <v>1.57</v>
       </c>
       <c r="L141" s="11" t="n">
-        <v>46171.54582175926</v>
+        <v>46171.82641203704</v>
       </c>
       <c r="M141" s="11" t="n">
-        <v>46171.60834490741</v>
+        <v>46171.875625</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="P141" s="2" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="Q141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R141" s="2" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="S141" s="2" t="n">
-        <v>14.54</v>
+        <v>4.78</v>
       </c>
       <c r="T141" s="2" t="n"/>
       <c r="U141" s="2" t="n">
@@ -26700,7 +26621,7 @@
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B142" s="8" t="n">
         <v>46171</v>
@@ -26710,68 +26631,68 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I142" s="10" t="n">
-        <v>46171.67638888889</v>
+        <v>46171.72065972222</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>46171.7416087963</v>
+        <v>46171.87474537037</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="L142" s="10" t="n">
-        <v>46171.82641203704</v>
+        <v>46171.94614583333</v>
       </c>
       <c r="M142" s="10" t="n">
-        <v>46171.875625</v>
+        <v>46172.63309027778</v>
       </c>
       <c r="N142" s="5" t="n">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="O142" s="5" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="P142" s="5" t="n">
-        <v>1.18</v>
+        <v>16.49</v>
       </c>
       <c r="Q142" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R142" s="5" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="S142" s="5" t="n">
-        <v>4.78</v>
+        <v>21.9</v>
       </c>
       <c r="T142" s="5" t="n"/>
       <c r="U142" s="5" t="n">
         <v>1</v>
       </c>
       <c r="V142" s="6" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="W142" s="6" t="n">
         <v>0</v>
@@ -26791,68 +26712,68 @@
         <v>46172</v>
       </c>
       <c r="B143" s="9" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C143" s="9" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I143" s="11" t="n">
-        <v>46171.72065972222</v>
+        <v>46172.32059027778</v>
       </c>
       <c r="J143" s="11" t="n">
-        <v>46171.87474537037</v>
+        <v>46172.47302083333</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="L143" s="11" t="n">
-        <v>46171.94614583333</v>
+        <v>46172.56171296296</v>
       </c>
       <c r="M143" s="11" t="n">
-        <v>46172.63309027778</v>
+        <v>46172.81743055556</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="O143" s="2" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="P143" s="2" t="n">
-        <v>16.49</v>
+        <v>6.14</v>
       </c>
       <c r="Q143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R143" s="2" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="S143" s="2" t="n">
-        <v>21.9</v>
+        <v>11.92</v>
       </c>
       <c r="T143" s="2" t="n"/>
       <c r="U143" s="2" t="n">
@@ -26862,7 +26783,7 @@
         <v>7264</v>
       </c>
       <c r="W143" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X143" s="7" t="n">
         <v>0</v>
@@ -26879,7 +26800,7 @@
         <v>46172</v>
       </c>
       <c r="B144" s="8" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C144" s="8" t="n">
         <v>46172</v>
@@ -26891,58 +26812,62 @@
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="I144" s="10" t="n">
-        <v>46172.32059027778</v>
+        <v>46171.82071759259</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>46172.47302083333</v>
+        <v>46171.92391203704</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>3.66</v>
+        <v>2.48</v>
       </c>
       <c r="L144" s="10" t="n">
-        <v>46172.56171296296</v>
+        <v>46172.29966435185</v>
       </c>
       <c r="M144" s="10" t="n">
-        <v>46172.81743055556</v>
+        <v>46172.37111111111</v>
       </c>
       <c r="N144" s="5" t="n">
-        <v>2.13</v>
+        <v>9.02</v>
       </c>
       <c r="O144" s="5" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="P144" s="5" t="n">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="Q144" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R144" s="5" t="n">
-        <v>11.92</v>
+        <v>13.21</v>
       </c>
       <c r="S144" s="5" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="T144" s="5" t="n"/>
+        <v>13.21</v>
+      </c>
+      <c r="T144" s="5" t="inlineStr">
+        <is>
+          <t>ABNORMAL</t>
+        </is>
+      </c>
       <c r="U144" s="5" t="n">
         <v>1</v>
       </c>
@@ -26950,7 +26875,7 @@
         <v>7264</v>
       </c>
       <c r="W144" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X144" s="6" t="n">
         <v>0</v>
@@ -26967,7 +26892,7 @@
         <v>46172</v>
       </c>
       <c r="B145" s="9" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="C145" s="9" t="n">
         <v>46172</v>
@@ -26989,52 +26914,48 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="I145" s="11" t="n">
-        <v>46171.82071759259</v>
+        <v>46172.43083333333</v>
       </c>
       <c r="J145" s="11" t="n">
-        <v>46171.92391203704</v>
+        <v>46172.52552083333</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="L145" s="11" t="n">
-        <v>46172.29966435185</v>
+        <v>46172.61280092593</v>
       </c>
       <c r="M145" s="11" t="n">
-        <v>46172.37111111111</v>
+        <v>46172.86035879629</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>9.02</v>
+        <v>2.09</v>
       </c>
       <c r="O145" s="2" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="P145" s="2" t="n">
-        <v>1.71</v>
+        <v>5.94</v>
       </c>
       <c r="Q145" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R145" s="2" t="n">
-        <v>13.21</v>
+        <v>10.31</v>
       </c>
       <c r="S145" s="2" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="T145" s="2" t="inlineStr">
-        <is>
-          <t>ABNORMAL</t>
-        </is>
-      </c>
+        <v>10.31</v>
+      </c>
+      <c r="T145" s="2" t="n"/>
       <c r="U145" s="2" t="n">
         <v>1</v>
       </c>
@@ -27071,56 +26992,56 @@
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="I146" s="10" t="n">
-        <v>46172.43083333333</v>
+        <v>46172.03034722222</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>46172.52552083333</v>
+        <v>46172.28571759259</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>2.27</v>
+        <v>6.13</v>
       </c>
       <c r="L146" s="10" t="n">
-        <v>46172.61280092593</v>
+        <v>46172.36446759259</v>
       </c>
       <c r="M146" s="10" t="n">
-        <v>46172.86035879629</v>
+        <v>46172.49165509259</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="O146" s="5" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="P146" s="5" t="n">
-        <v>5.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q146" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R146" s="5" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="S146" s="5" t="n">
-        <v>10.31</v>
+        <v>11.07</v>
       </c>
       <c r="T146" s="5" t="n"/>
       <c r="U146" s="5" t="n">
@@ -27130,7 +27051,7 @@
         <v>7264</v>
       </c>
       <c r="W146" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X146" s="6" t="n">
         <v>0</v>
@@ -27147,7 +27068,7 @@
         <v>46172</v>
       </c>
       <c r="B147" s="9" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="C147" s="9" t="n">
         <v>46172</v>
@@ -27159,56 +27080,56 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I147" s="11" t="n">
-        <v>46172.03034722222</v>
+        <v>46171.99543981482</v>
       </c>
       <c r="J147" s="11" t="n">
-        <v>46172.28571759259</v>
+        <v>46172.2858449074</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>6.13</v>
+        <v>6.97</v>
       </c>
       <c r="L147" s="11" t="n">
-        <v>46172.36446759259</v>
+        <v>46172.40947916666</v>
       </c>
       <c r="M147" s="11" t="n">
-        <v>46172.49165509259</v>
+        <v>46172.62247685185</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>1.89</v>
+        <v>2.97</v>
       </c>
       <c r="O147" s="2" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="P147" s="2" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="Q147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R147" s="2" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="S147" s="2" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="T147" s="2" t="n"/>
       <c r="U147" s="2" t="n">
@@ -27232,13 +27153,13 @@
     </row>
     <row r="148">
       <c r="A148" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B148" s="8" t="n">
         <v>46172</v>
       </c>
-      <c r="B148" s="8" t="n">
-        <v>46171</v>
-      </c>
       <c r="C148" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
@@ -27247,56 +27168,56 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I148" s="10" t="n">
-        <v>46171.99543981482</v>
+        <v>46172.945</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>46172.2858449074</v>
+        <v>46173.25171296296</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>6.97</v>
+        <v>7.36</v>
       </c>
       <c r="L148" s="10" t="n">
-        <v>46172.40947916666</v>
+        <v>46173.33864583333</v>
       </c>
       <c r="M148" s="10" t="n">
-        <v>46172.62247685185</v>
+        <v>46173.38333333333</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>2.97</v>
+        <v>2.09</v>
       </c>
       <c r="O148" s="5" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="P148" s="5" t="n">
-        <v>5.11</v>
+        <v>1.07</v>
       </c>
       <c r="Q148" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R148" s="5" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="S148" s="5" t="n">
-        <v>15.05</v>
+        <v>10.52</v>
       </c>
       <c r="T148" s="5" t="n"/>
       <c r="U148" s="5" t="n">
@@ -27306,7 +27227,7 @@
         <v>7264</v>
       </c>
       <c r="W148" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X148" s="6" t="n">
         <v>0</v>
@@ -27323,7 +27244,7 @@
         <v>46173</v>
       </c>
       <c r="B149" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C149" s="9" t="n">
         <v>46173</v>
@@ -27345,46 +27266,46 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="I149" s="11" t="n">
-        <v>46172.945</v>
+        <v>46173.50255787037</v>
       </c>
       <c r="J149" s="11" t="n">
-        <v>46173.25171296296</v>
+        <v>46173.72892361111</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>7.36</v>
+        <v>5.43</v>
       </c>
       <c r="L149" s="11" t="n">
-        <v>46173.33864583333</v>
+        <v>46173.81170138889</v>
       </c>
       <c r="M149" s="11" t="n">
-        <v>46173.38333333333</v>
+        <v>46173.91047453704</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="O149" s="2" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="P149" s="2" t="n">
-        <v>1.07</v>
+        <v>2.37</v>
       </c>
       <c r="Q149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R149" s="2" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="S149" s="2" t="n">
-        <v>10.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="T149" s="2" t="n"/>
       <c r="U149" s="2" t="n">
@@ -27411,7 +27332,7 @@
         <v>46173</v>
       </c>
       <c r="B150" s="8" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="C150" s="8" t="n">
         <v>46173</v>
@@ -27423,56 +27344,56 @@
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>71-5042 ณัชพน หัวลาก10W</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="I150" s="10" t="n">
-        <v>46173.50255787037</v>
+        <v>46172.96576388889</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>46173.72892361111</v>
+        <v>46173.20033564815</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>5.43</v>
+        <v>5.63</v>
       </c>
       <c r="L150" s="10" t="n">
-        <v>46173.81170138889</v>
+        <v>46173.26480324074</v>
       </c>
       <c r="M150" s="10" t="n">
-        <v>46173.91047453704</v>
+        <v>46173.38116898148</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="O150" s="5" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="P150" s="5" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="Q150" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R150" s="5" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S150" s="5" t="n">
-        <v>9.789999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="T150" s="5" t="n"/>
       <c r="U150" s="5" t="n">
@@ -27482,7 +27403,7 @@
         <v>7264</v>
       </c>
       <c r="W150" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X150" s="6" t="n">
         <v>0</v>
@@ -27511,56 +27432,56 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>71-8002 สมประสงค์ หัวลาก10W</t>
+          <t>71-8009 ชรินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I151" s="11" t="n">
-        <v>46172.96576388889</v>
+        <v>46172.97828703704</v>
       </c>
       <c r="J151" s="11" t="n">
-        <v>46173.20033564815</v>
+        <v>46173.5018287037</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>5.63</v>
+        <v>12.56</v>
       </c>
       <c r="L151" s="11" t="n">
-        <v>46173.26480324074</v>
+        <v>46173.57653935185</v>
       </c>
       <c r="M151" s="11" t="n">
-        <v>46173.38116898148</v>
+        <v>46173.62144675926</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="P151" s="2" t="n">
-        <v>2.79</v>
+        <v>1.08</v>
       </c>
       <c r="Q151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R151" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="S151" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>15.44</v>
       </c>
       <c r="T151" s="2" t="n"/>
       <c r="U151" s="2" t="n">
@@ -27584,7 +27505,7 @@
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="B152" s="8" t="n">
         <v>46172</v>
@@ -27594,61 +27515,61 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>71-8009 ชรินทร์ หัวลาก10W</t>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="H152" s="5" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I152" s="10" t="n">
-        <v>46172.97828703704</v>
+        <v>46172.75962962963</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>46173.5018287037</v>
+        <v>46173.02157407408</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>12.56</v>
+        <v>6.29</v>
       </c>
       <c r="L152" s="10" t="n">
-        <v>46173.57653935185</v>
+        <v>46173.09358796296</v>
       </c>
       <c r="M152" s="10" t="n">
-        <v>46173.62144675926</v>
+        <v>46173.18756944445</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O152" s="5" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="P152" s="5" t="n">
-        <v>1.08</v>
+        <v>2.26</v>
       </c>
       <c r="Q152" s="5" t="n">
         <v>0</v>
       </c>
       <c r="R152" s="5" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="S152" s="5" t="n">
-        <v>15.44</v>
+        <v>10.27</v>
       </c>
       <c r="T152" s="5" t="n"/>
       <c r="U152" s="5" t="n">
@@ -27658,7 +27579,7 @@
         <v>7264</v>
       </c>
       <c r="W152" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="X152" s="6" t="n">
         <v>0</v>
@@ -27672,10 +27593,10 @@
     </row>
     <row r="153">
       <c r="A153" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B153" s="9" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="C153" s="9" t="n">
         <v>46173</v>
@@ -27697,46 +27618,46 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
       <c r="I153" s="11" t="n">
-        <v>46172.75962962963</v>
+        <v>46173.25349537037</v>
       </c>
       <c r="J153" s="11" t="n">
-        <v>46173.02157407408</v>
+        <v>46173.31078703704</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>6.29</v>
+        <v>1.38</v>
       </c>
       <c r="L153" s="11" t="n">
-        <v>46173.09358796296</v>
+        <v>46173.385625</v>
       </c>
       <c r="M153" s="11" t="n">
-        <v>46173.18756944445</v>
+        <v>46173.41065972222</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="P153" s="2" t="n">
-        <v>2.26</v>
+        <v>0.6</v>
       </c>
       <c r="Q153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R153" s="2" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="S153" s="2" t="n">
-        <v>10.27</v>
+        <v>3.77</v>
       </c>
       <c r="T153" s="2" t="n"/>
       <c r="U153" s="2" t="n">
@@ -27746,7 +27667,7 @@
         <v>7264</v>
       </c>
       <c r="W153" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="X153" s="7" t="n">
         <v>0</v>
@@ -27758,96 +27679,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B154" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C154" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="H154" s="5" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="I154" s="10" t="n">
-        <v>46173.25349537037</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>46173.31078703704</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L154" s="10" t="n">
-        <v>46173.385625</v>
-      </c>
-      <c r="M154" s="10" t="n">
-        <v>46173.41065972222</v>
-      </c>
-      <c r="N154" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O154" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P154" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q154" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R154" s="5" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="S154" s="5" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="T154" s="5" t="n"/>
-      <c r="U154" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V154" s="6" t="n">
-        <v>7264</v>
-      </c>
-      <c r="W154" s="6" t="n">
-        <v>3632</v>
-      </c>
-      <c r="X154" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y154" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z154" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z154"/>
+  <autoFilter ref="A1:Z153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -27858,7 +27691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -31213,7 +31046,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C134" s="6" t="n">
@@ -31234,18 +31067,18 @@
     </row>
     <row r="135">
       <c r="A135" s="9" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C135" s="7" t="n">
         <v>7360</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>3680</v>
+        <v>0</v>
       </c>
       <c r="E135" s="7" t="n">
         <v>0</v>
@@ -31288,7 +31121,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C137" s="7" t="n">
@@ -31313,7 +31146,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C138" s="6" t="n">
@@ -31363,7 +31196,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C140" s="6" t="n">
@@ -31413,11 +31246,11 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="D142" s="6" t="n">
         <v>0</v>
@@ -31434,18 +31267,18 @@
     </row>
     <row r="143">
       <c r="A143" s="9" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C143" s="7" t="n">
         <v>7264</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E143" s="7" t="n">
         <v>0</v>
@@ -31463,14 +31296,14 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C144" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E144" s="6" t="n">
         <v>0</v>
@@ -31513,14 +31346,14 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E146" s="6" t="n">
         <v>0</v>
@@ -31538,7 +31371,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C147" s="7" t="n">
@@ -31559,18 +31392,18 @@
     </row>
     <row r="148">
       <c r="A148" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C148" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E148" s="6" t="n">
         <v>0</v>
@@ -31613,14 +31446,14 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C150" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E150" s="6" t="n">
         <v>0</v>
@@ -31638,7 +31471,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C151" s="7" t="n">
@@ -31663,14 +31496,14 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C152" s="6" t="n">
         <v>7264</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>3632</v>
+        <v>0</v>
       </c>
       <c r="E152" s="6" t="n">
         <v>0</v>
@@ -31695,7 +31528,7 @@
         <v>7264</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>0</v>
+        <v>3632</v>
       </c>
       <c r="E153" s="7" t="n">
         <v>0</v>
@@ -31707,33 +31540,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="8" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="n">
-        <v>7264</v>
-      </c>
-      <c r="D154" s="6" t="n">
-        <v>3632</v>
-      </c>
-      <c r="E154" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G154"/>
+  <autoFilter ref="A1:G153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33364,22 +33172,22 @@
         <v>46170</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D29" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="E29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>1</v>
@@ -33487,7 +33295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -38421,25 +38229,25 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>18.85</v>
+        <v>16.5</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>1.56</v>
+        <v>11.61</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>13.61</v>
+        <v>1.61</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>0</v>
@@ -38448,45 +38256,45 @@
         <v>0</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.56</v>
+        <v>11.61</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>18.85</v>
+        <v>16.5</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5.15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>16.5</v>
+        <v>18.35</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>3.28</v>
+        <v>5.44</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>11.61</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>1.61</v>
+        <v>3.96</v>
       </c>
       <c r="H106" s="5" t="n">
         <v>0</v>
@@ -38495,16 +38303,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>3.28</v>
+        <v>5.44</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>11.61</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>16.5</v>
+        <v>18.35</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>7.5</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="107">
@@ -38515,7 +38323,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -38524,16 +38332,16 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>18.35</v>
+        <v>18.22</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.44</v>
+        <v>7.66</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>3.96</v>
+        <v>3.44</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>0</v>
@@ -38542,16 +38350,16 @@
         <v>0</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>5.44</v>
+        <v>7.66</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>18.35</v>
+        <v>18.22</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5.65</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="108">
@@ -38562,7 +38370,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -38571,16 +38379,16 @@
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>18.22</v>
+        <v>21.08</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>7.66</v>
+        <v>8.5</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>7.12</v>
+        <v>8.01</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>3.44</v>
+        <v>4.57</v>
       </c>
       <c r="H108" s="5" t="n">
         <v>0</v>
@@ -38589,16 +38397,16 @@
         <v>0</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>7.66</v>
+        <v>8.5</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>7.12</v>
+        <v>8.01</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>18.22</v>
+        <v>21.08</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>5.78</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="109">
@@ -38609,7 +38417,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -38618,16 +38426,16 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>21.08</v>
+        <v>19.32</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>8.5</v>
+        <v>12.75</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>8.01</v>
+        <v>2.68</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>4.57</v>
+        <v>3.9</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>0</v>
@@ -38636,16 +38444,16 @@
         <v>0</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>8.5</v>
+        <v>12.75</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>8.01</v>
+        <v>2.68</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>21.08</v>
+        <v>19.32</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2.92</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="110">
@@ -38656,25 +38464,25 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>19.32</v>
+        <v>17.35</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>12.75</v>
+        <v>7.33</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>2.68</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>3.9</v>
+        <v>1.63</v>
       </c>
       <c r="H110" s="5" t="n">
         <v>0</v>
@@ -38683,45 +38491,45 @@
         <v>0</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>12.75</v>
+        <v>7.33</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>2.68</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>19.32</v>
+        <v>17.35</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>4.68</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>17.35</v>
+        <v>11.92</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>7.33</v>
+        <v>3.66</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>6.14</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>0</v>
@@ -38730,16 +38538,16 @@
         <v>0</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>7.33</v>
+        <v>3.66</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>6.14</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>17.35</v>
+        <v>11.92</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>6.65</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="112">
@@ -38750,7 +38558,7 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -38759,16 +38567,16 @@
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>11.92</v>
+        <v>23.52</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3.66</v>
+        <v>4.75</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>6.14</v>
+        <v>7.66</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>2.13</v>
+        <v>11.11</v>
       </c>
       <c r="H112" s="5" t="n">
         <v>0</v>
@@ -38777,16 +38585,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>3.66</v>
+        <v>4.75</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>6.14</v>
+        <v>7.66</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>11.92</v>
+        <v>23.52</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>12.08</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="113">
@@ -38797,7 +38605,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -38806,34 +38614,34 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>23.52</v>
+        <v>11.07</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>4.75</v>
+        <v>6.13</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>7.66</v>
+        <v>3.05</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>11.11</v>
+        <v>1.89</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="I113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>4.75</v>
+        <v>6.65</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>7.66</v>
+        <v>3.05</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>23.52</v>
+        <v>11.6</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>0.48</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="114">
@@ -38844,7 +38652,7 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -38853,34 +38661,34 @@
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>6.13</v>
+        <v>6.97</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>1.89</v>
+        <v>2.97</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>6.65</v>
+        <v>6.97</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>11.6</v>
+        <v>15.05</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>12.4</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -38891,25 +38699,25 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>15.05</v>
+        <v>32.17</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>6.97</v>
+        <v>9.98</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>5.11</v>
+        <v>18.74</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>0</v>
@@ -38918,63 +38726,63 @@
         <v>0</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>6.97</v>
+        <v>9.98</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>5.11</v>
+        <v>18.74</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>15.05</v>
+        <v>32.17</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>-8.17</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>32.17</v>
+        <v>20.31</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>9.98</v>
+        <v>12.79</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>18.74</v>
+        <v>3.44</v>
       </c>
       <c r="G116" s="5" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="K116" s="5" t="n">
         <v>3.44</v>
       </c>
-      <c r="H116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="5" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="K116" s="5" t="n">
-        <v>18.74</v>
-      </c>
       <c r="L116" s="5" t="n">
-        <v>32.17</v>
+        <v>20.31</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>-8.17</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="117">
@@ -38985,7 +38793,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -38994,34 +38802,34 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>20.31</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>12.79</v>
+        <v>5.63</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>4.07</v>
+        <v>1.55</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>0</v>
+        <v>13.11</v>
       </c>
       <c r="I117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>12.79</v>
+        <v>18.73</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>20.31</v>
+        <v>23.07</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3.69</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="118">
@@ -39032,7 +38840,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -39041,34 +38849,34 @@
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>13.11</v>
+        <v>0.61</v>
       </c>
       <c r="I118" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>18.73</v>
+        <v>0.61</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>23.07</v>
+        <v>0.61</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.93</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="119">
@@ -39079,7 +38887,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -39088,34 +38896,34 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0</v>
+        <v>15.44</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0</v>
+        <v>12.56</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.61</v>
+        <v>12.56</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0.61</v>
+        <v>15.44</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>23.39</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="120">
@@ -39126,94 +38934,47 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>15.44</v>
+        <v>3.77</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>12.56</v>
+        <v>1.38</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="I120" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>12.56</v>
+        <v>6.72</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>15.44</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>8.56</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="M121" s="2" t="n">
         <v>14.88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
+  <autoFilter ref="A1:M120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/00_Full_Workbook.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>
